--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$41</definedName>
@@ -549,7 +549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="46">
     <border/>
     <border>
       <left style="medium">
@@ -971,11 +971,29 @@
         <color rgb="FFD9E2F3"/>
       </bottom>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="396">
+  <cellXfs count="399">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1892,6 +1910,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2371,16 +2394,16 @@
         </is>
       </c>
       <c r="D9" s="323" t="n"/>
-      <c r="E9" s="320" t="inlineStr">
+      <c r="E9" s="396" t="inlineStr">
         <is>
           <t>本账本只登记上列大类；跨域搬运资产须同步主账本《分类与编码》并重跑门禁</t>
         </is>
       </c>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="125" t="n"/>
-      <c r="J9" s="126" t="n"/>
+      <c r="F9" s="397" t="n"/>
+      <c r="G9" s="397" t="n"/>
+      <c r="H9" s="397" t="n"/>
+      <c r="I9" s="397" t="n"/>
+      <c r="J9" s="398" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="301" t="inlineStr">
@@ -3591,7 +3614,7 @@
       </c>
       <c r="O9" s="138" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d_v001.tscn</t>
+          <t>assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P9" s="138" t="inlineStr">
@@ -9308,7 +9331,7 @@
       </c>
       <c r="C25" s="192" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d_v001.tscn</t>
+          <t>assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d.tscn</t>
         </is>
       </c>
       <c r="D25" s="192" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$41</definedName>
@@ -1703,6 +1703,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -2417,7 +2418,7 @@
       </c>
       <c r="P7" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q7" s="70" t="inlineStr">
@@ -2538,7 +2539,7 @@
       </c>
       <c r="P8" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q8" s="70" t="inlineStr">
@@ -2659,7 +2660,7 @@
       </c>
       <c r="P9" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q9" s="70" t="inlineStr">
@@ -2780,7 +2781,7 @@
       </c>
       <c r="P10" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q10" s="70" t="inlineStr">
@@ -2901,7 +2902,7 @@
       </c>
       <c r="P11" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q11" s="70" t="inlineStr">
@@ -3022,7 +3023,7 @@
       </c>
       <c r="P12" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q12" s="70" t="inlineStr">
@@ -5124,7 +5125,7 @@
       </c>
       <c r="P31" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q31" s="70" t="inlineStr">
@@ -5245,7 +5246,7 @@
       </c>
       <c r="P32" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q32" s="70" t="inlineStr">
@@ -5366,7 +5367,7 @@
       </c>
       <c r="P33" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v001.blend</t>
         </is>
       </c>
       <c r="Q33" s="70" t="inlineStr">
@@ -5487,7 +5488,7 @@
       </c>
       <c r="P34" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q34" s="70" t="inlineStr">
@@ -5608,7 +5609,7 @@
       </c>
       <c r="P35" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q35" s="70" t="inlineStr">
@@ -5729,7 +5730,7 @@
       </c>
       <c r="P36" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q36" s="70" t="inlineStr">
@@ -5850,7 +5851,7 @@
       </c>
       <c r="P37" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q37" s="70" t="inlineStr">
@@ -5971,7 +5972,7 @@
       </c>
       <c r="P38" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q38" s="70" t="inlineStr">
@@ -6092,7 +6093,7 @@
       </c>
       <c r="P39" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q39" s="70" t="inlineStr">
@@ -6213,7 +6214,7 @@
       </c>
       <c r="P40" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q40" s="70" t="inlineStr">
@@ -6334,7 +6335,7 @@
       </c>
       <c r="P41" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q41" s="70" t="inlineStr">
@@ -8583,6 +8584,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -2296,7 +2296,7 @@
       </c>
       <c r="P6" s="70" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v003.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>art_source/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v003.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q6" s="70" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="P7" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q7" s="70" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="P8" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q8" s="70" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P9" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q9" s="70" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="P10" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q10" s="70" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="P11" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q11" s="70" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="P12" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v001.blend; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="Q12" s="70" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="P31" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q31" s="70" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="P32" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q32" s="70" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P33" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v001.blend</t>
         </is>
       </c>
       <c r="Q33" s="70" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="P34" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q34" s="70" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="P35" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q35" s="70" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="P36" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q36" s="70" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="P37" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q37" s="70" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P38" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q38" s="70" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="P39" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q39" s="70" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="P40" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v001.blend</t>
         </is>
       </c>
       <c r="Q40" s="70" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="P41" s="70" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v001.blend</t>
         </is>
       </c>
       <c r="Q41" s="70" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E8" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/broom_rifle/wpn_broom_rifle_source_v003.blend</t>
         </is>
       </c>
       <c r="F8" s="86" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="E9" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/camera_blaster/wpn_camera_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F9" s="86" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="E10" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/candy_sniper/wpn_candy_sniper_source_v003.blend</t>
         </is>
       </c>
       <c r="F10" s="86" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="E11" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/crocodile_cannon/wpn_crocodile_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F11" s="86" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="E12" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/double_barrel_cannon/wpn_double_barrel_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F12" s="86" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E13" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/fan_blaster/wpn_fan_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F13" s="86" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E14" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/frying_pan_cannon/wpn_frying_pan_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F14" s="86" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="E15" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/guitar_blaster/wpn_guitar_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F15" s="86" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="E16" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/gumball_cannon/wpn_gumball_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F16" s="86" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="E17" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v003.blend</t>
         </is>
       </c>
       <c r="F17" s="86" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E18" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/megaphone_cannon/wpn_megaphone_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F18" s="86" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="E19" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/popcorn_blaster/wpn_popcorn_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F19" s="86" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="E20" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/scope_cannon/wpn_scope_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F20" s="86" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="E21" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/soda_straw_blaster/wpn_soda_straw_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F21" s="86" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="E22" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/spatula_rifle/wpn_spatula_rifle_source_v003.blend</t>
         </is>
       </c>
       <c r="F22" s="86" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="E23" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/tissue_box_cannon/wpn_tissue_box_cannon_source_v003.blend</t>
         </is>
       </c>
       <c r="F23" s="86" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="E24" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/toaster_launcher/wpn_toaster_launcher_source_v003.blend</t>
         </is>
       </c>
       <c r="F24" s="86" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="E25" s="87" t="inlineStr">
         <is>
-          <t>assets/art/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v003.blend</t>
+          <t>art_source/weapons/weapon_3d/source/water_tank_blaster/wpn_water_tank_blaster_source_v003.blend</t>
         </is>
       </c>
       <c r="F25" s="86" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$41</definedName>
@@ -25,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="35">
     <font>
       <name val="Linux Libertine G"/>
       <family val="2"/>
@@ -240,8 +241,30 @@
       <color rgb="FF1F2937"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001565C0"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00243B53"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -300,6 +323,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F75B5"/>
         <bgColor rgb="FF156082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00243B53"/>
       </patternFill>
     </fill>
   </fills>
@@ -580,7 +608,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -850,6 +878,18 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,6 +1157,32 @@
 </table>
 </file>
 
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeaponInventoryItems" displayName="WeaponInventoryItems" ref="A4:Q30" headerRowCount="1">
+  <autoFilter ref="A4:Q30"/>
+  <tableColumns count="17">
+    <tableColumn id="1" name="内容ID"/>
+    <tableColumn id="2" name="名称"/>
+    <tableColumn id="3" name="种类"/>
+    <tableColumn id="4" name="子类"/>
+    <tableColumn id="5" name="唯一登记账本"/>
+    <tableColumn id="6" name="内容定义入口"/>
+    <tableColumn id="7" name="内容数据库定位"/>
+    <tableColumn id="8" name="怪物掉落来源"/>
+    <tableColumn id="9" name="池声明入口"/>
+    <tableColumn id="10" name="背包接收入口"/>
+    <tableColumn id="11" name="使用/装配入口"/>
+    <tableColumn id="12" name="模型调用入口"/>
+    <tableColumn id="13" name="当前模型表现"/>
+    <tableColumn id="14" name="关联AssetID（引用）"/>
+    <tableColumn id="15" name="资产登记定位（引用）"/>
+    <tableColumn id="16" name="功能模块"/>
+    <tableColumn id="17" name="审查备注"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
   <a:themeElements>
@@ -1703,7 +1769,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -6671,7 +6736,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="46">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -8584,7 +8648,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -8668,4 +8731,2645 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="46" min="1" max="1"/>
+    <col width="28" customWidth="1" style="46" min="2" max="2"/>
+    <col width="28" customWidth="1" style="46" min="3" max="3"/>
+    <col width="28" customWidth="1" style="46" min="4" max="4"/>
+    <col width="46" customWidth="1" style="46" min="5" max="5"/>
+    <col width="46" customWidth="1" style="46" min="6" max="6"/>
+    <col width="46" customWidth="1" style="46" min="7" max="7"/>
+    <col width="46" customWidth="1" style="46" min="8" max="8"/>
+    <col width="46" customWidth="1" style="46" min="9" max="9"/>
+    <col width="46" customWidth="1" style="46" min="10" max="10"/>
+    <col width="46" customWidth="1" style="46" min="11" max="11"/>
+    <col width="46" customWidth="1" style="46" min="12" max="12"/>
+    <col width="46" customWidth="1" style="46" min="13" max="13"/>
+    <col width="46" customWidth="1" style="46" min="14" max="14"/>
+    <col width="46" customWidth="1" style="46" min="15" max="15"/>
+    <col width="46" customWidth="1" style="46" min="16" max="16"/>
+    <col width="46" customWidth="1" style="46" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="46">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>武器账本 · 背包物品调用索引</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="94" t="n"/>
+      <c r="D1" s="94" t="n"/>
+      <c r="E1" s="94" t="n"/>
+      <c r="F1" s="94" t="n"/>
+      <c r="G1" s="94" t="n"/>
+      <c r="H1" s="94" t="n"/>
+      <c r="I1" s="94" t="n"/>
+      <c r="J1" s="94" t="n"/>
+      <c r="K1" s="94" t="n"/>
+      <c r="L1" s="94" t="n"/>
+      <c r="M1" s="94" t="n"/>
+      <c r="N1" s="94" t="n"/>
+      <c r="O1" s="94" t="n"/>
+      <c r="P1" s="94" t="n"/>
+      <c r="Q1" s="94" t="n"/>
+    </row>
+    <row r="2" ht="44" customHeight="1" s="46">
+      <c r="A2" s="94" t="inlineStr">
+        <is>
+          <t>成品武器、子弹模块、通用弹药、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
+        </is>
+      </c>
+      <c r="B2" s="94" t="n"/>
+      <c r="C2" s="94" t="n"/>
+      <c r="D2" s="94" t="n"/>
+      <c r="E2" s="94" t="n"/>
+      <c r="F2" s="94" t="n"/>
+      <c r="G2" s="94" t="n"/>
+      <c r="H2" s="94" t="n"/>
+      <c r="I2" s="94" t="n"/>
+      <c r="J2" s="94" t="n"/>
+      <c r="K2" s="94" t="n"/>
+      <c r="L2" s="94" t="n"/>
+      <c r="M2" s="94" t="n"/>
+      <c r="N2" s="94" t="n"/>
+      <c r="O2" s="94" t="n"/>
+      <c r="P2" s="94" t="n"/>
+      <c r="Q2" s="94" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="94" t="n"/>
+      <c r="B3" s="94" t="n"/>
+      <c r="C3" s="94" t="n"/>
+      <c r="D3" s="94" t="n"/>
+      <c r="E3" s="94" t="n"/>
+      <c r="F3" s="94" t="n"/>
+      <c r="G3" s="94" t="n"/>
+      <c r="H3" s="94" t="n"/>
+      <c r="I3" s="94" t="n"/>
+      <c r="J3" s="94" t="n"/>
+      <c r="K3" s="94" t="n"/>
+      <c r="L3" s="94" t="n"/>
+      <c r="M3" s="94" t="n"/>
+      <c r="N3" s="94" t="n"/>
+      <c r="O3" s="94" t="n"/>
+      <c r="P3" s="94" t="n"/>
+      <c r="Q3" s="94" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1" s="46">
+      <c r="A4" s="93" t="inlineStr">
+        <is>
+          <t>内容ID</t>
+        </is>
+      </c>
+      <c r="B4" s="93" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C4" s="93" t="inlineStr">
+        <is>
+          <t>种类</t>
+        </is>
+      </c>
+      <c r="D4" s="93" t="inlineStr">
+        <is>
+          <t>子类</t>
+        </is>
+      </c>
+      <c r="E4" s="93" t="inlineStr">
+        <is>
+          <t>唯一登记账本</t>
+        </is>
+      </c>
+      <c r="F4" s="93" t="inlineStr">
+        <is>
+          <t>内容定义入口</t>
+        </is>
+      </c>
+      <c r="G4" s="93" t="inlineStr">
+        <is>
+          <t>内容数据库定位</t>
+        </is>
+      </c>
+      <c r="H4" s="93" t="inlineStr">
+        <is>
+          <t>怪物掉落来源</t>
+        </is>
+      </c>
+      <c r="I4" s="93" t="inlineStr">
+        <is>
+          <t>池声明入口</t>
+        </is>
+      </c>
+      <c r="J4" s="93" t="inlineStr">
+        <is>
+          <t>背包接收入口</t>
+        </is>
+      </c>
+      <c r="K4" s="93" t="inlineStr">
+        <is>
+          <t>使用/装配入口</t>
+        </is>
+      </c>
+      <c r="L4" s="93" t="inlineStr">
+        <is>
+          <t>模型调用入口</t>
+        </is>
+      </c>
+      <c r="M4" s="93" t="inlineStr">
+        <is>
+          <t>当前模型表现</t>
+        </is>
+      </c>
+      <c r="N4" s="93" t="inlineStr">
+        <is>
+          <t>关联AssetID（引用）</t>
+        </is>
+      </c>
+      <c r="O4" s="93" t="inlineStr">
+        <is>
+          <t>资产登记定位（引用）</t>
+        </is>
+      </c>
+      <c r="P4" s="93" t="inlineStr">
+        <is>
+          <t>功能模块</t>
+        </is>
+      </c>
+      <c r="Q4" s="93" t="inlineStr">
+        <is>
+          <t>审查备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1" s="46">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>weapon_pistol</t>
+        </is>
+      </c>
+      <c r="B5" s="94" t="inlineStr">
+        <is>
+          <t>豌豆手枪</t>
+        </is>
+      </c>
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E5" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L205</t>
+        </is>
+      </c>
+      <c r="G5" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A33</t>
+        </is>
+      </c>
+      <c r="H5" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行2 / melee_chaser</t>
+        </is>
+      </c>
+      <c r="I5" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L205 / loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J5" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K5" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L5" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M5" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N5" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-PISTOL</t>
+        </is>
+      </c>
+      <c r="O5" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A6</t>
+        </is>
+      </c>
+      <c r="P5" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q5" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1" s="46">
+      <c r="A6" s="94" t="inlineStr">
+        <is>
+          <t>weapon_shotgun</t>
+        </is>
+      </c>
+      <c r="B6" s="94" t="inlineStr">
+        <is>
+          <t>散射喷壶</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D6" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E6" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L224</t>
+        </is>
+      </c>
+      <c r="G6" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A35</t>
+        </is>
+      </c>
+      <c r="H6" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I6" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L224 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J6" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K6" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L6" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M6" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N6" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-SHOTGUN</t>
+        </is>
+      </c>
+      <c r="O6" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A7</t>
+        </is>
+      </c>
+      <c r="P6" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q6" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1" s="46">
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t>weapon_rifle</t>
+        </is>
+      </c>
+      <c r="B7" s="94" t="inlineStr">
+        <is>
+          <t>步枪</t>
+        </is>
+      </c>
+      <c r="C7" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E7" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L244</t>
+        </is>
+      </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A34</t>
+        </is>
+      </c>
+      <c r="H7" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I7" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L244 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J7" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K7" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L7" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M7" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N7" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-RIFLE</t>
+        </is>
+      </c>
+      <c r="O7" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A8</t>
+        </is>
+      </c>
+      <c r="P7" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q7" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1" s="46">
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>weapon_machinegun</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>蜂窝机枪</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D8" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E8" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L273</t>
+        </is>
+      </c>
+      <c r="G8" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A32</t>
+        </is>
+      </c>
+      <c r="H8" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I8" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L273 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J8" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K8" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L8" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M8" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N8" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-MACHINEGUN</t>
+        </is>
+      </c>
+      <c r="O8" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A9</t>
+        </is>
+      </c>
+      <c r="P8" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q8" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1" s="46">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>weapon_sprinkler</t>
+        </is>
+      </c>
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>花洒机枪</t>
+        </is>
+      </c>
+      <c r="C9" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D9" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E9" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L302</t>
+        </is>
+      </c>
+      <c r="G9" s="94" t="inlineStr">
+        <is>
+          <t>缺行</t>
+        </is>
+      </c>
+      <c r="H9" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I9" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L302 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J9" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K9" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L9" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M9" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N9" s="94" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="O9" s="94" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="P9" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q9" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID；无对应资产主表登记，不新增AssetID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="93" customHeight="1" s="46">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>weapon_sniper</t>
+        </is>
+      </c>
+      <c r="B10" s="94" t="inlineStr">
+        <is>
+          <t>弹弓狙击</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D10" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E10" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L333</t>
+        </is>
+      </c>
+      <c r="G10" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A36</t>
+        </is>
+      </c>
+      <c r="H10" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I10" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L333 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J10" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K10" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L10" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M10" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N10" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-SNIPER</t>
+        </is>
+      </c>
+      <c r="O10" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A10</t>
+        </is>
+      </c>
+      <c r="P10" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q10" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="93" customHeight="1" s="46">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>weapon_launcher</t>
+        </is>
+      </c>
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>反胃榴弹筒</t>
+        </is>
+      </c>
+      <c r="C11" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E11" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L360</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A31</t>
+        </is>
+      </c>
+      <c r="H11" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行15 / exploder</t>
+        </is>
+      </c>
+      <c r="I11" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L360 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J11" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K11" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L11" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M11" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N11" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-LAUNCHER</t>
+        </is>
+      </c>
+      <c r="O11" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A11</t>
+        </is>
+      </c>
+      <c r="P11" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q11" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1" s="46">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>weapon_charge</t>
+        </is>
+      </c>
+      <c r="B12" s="94" t="inlineStr">
+        <is>
+          <t>蓄力萝卜炮</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D12" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E12" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L387</t>
+        </is>
+      </c>
+      <c r="G12" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A30</t>
+        </is>
+      </c>
+      <c r="H12" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I12" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L387 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J12" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K12" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L12" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M12" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N12" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-CHARGE</t>
+        </is>
+      </c>
+      <c r="O12" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A12</t>
+        </is>
+      </c>
+      <c r="P12" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q12" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="59" customHeight="1" s="46">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>weapon_baseball_bat</t>
+        </is>
+      </c>
+      <c r="B13" s="94" t="inlineStr">
+        <is>
+          <t>废土棒球棍</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D13" s="94" t="inlineStr">
+        <is>
+          <t>melee_weapon</t>
+        </is>
+      </c>
+      <c r="E13" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L410</t>
+        </is>
+      </c>
+      <c r="G13" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A49</t>
+        </is>
+      </c>
+      <c r="H13" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行3 / melee_chaser</t>
+        </is>
+      </c>
+      <c r="I13" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L410 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
+        </is>
+      </c>
+      <c r="J13" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K13" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L13" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M13" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N13" s="94" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-BASEBALL-BAT</t>
+        </is>
+      </c>
+      <c r="O13" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A30</t>
+        </is>
+      </c>
+      <c r="P13" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q13" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1" s="46">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t>weapon_greatblade</t>
+        </is>
+      </c>
+      <c r="B14" s="94" t="inlineStr">
+        <is>
+          <t>巨型工业断刃</t>
+        </is>
+      </c>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D14" s="94" t="inlineStr">
+        <is>
+          <t>melee_weapon</t>
+        </is>
+      </c>
+      <c r="E14" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L430</t>
+        </is>
+      </c>
+      <c r="G14" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A47</t>
+        </is>
+      </c>
+      <c r="H14" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I14" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L430 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J14" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K14" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L14" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M14" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N14" s="94" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-GREATBLADE</t>
+        </is>
+      </c>
+      <c r="O14" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A28</t>
+        </is>
+      </c>
+      <c r="P14" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q14" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1" s="46">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>weapon_waraxe</t>
+        </is>
+      </c>
+      <c r="B15" s="94" t="inlineStr">
+        <is>
+          <t>攻城裂甲斧</t>
+        </is>
+      </c>
+      <c r="C15" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>melee_weapon</t>
+        </is>
+      </c>
+      <c r="E15" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L452</t>
+        </is>
+      </c>
+      <c r="G15" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A48</t>
+        </is>
+      </c>
+      <c r="H15" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I15" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L452 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J15" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K15" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L15" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M15" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N15" s="94" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-WARAXE</t>
+        </is>
+      </c>
+      <c r="O15" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A29</t>
+        </is>
+      </c>
+      <c r="P15" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q15" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1" s="46">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t>item_ammo_pack</t>
+        </is>
+      </c>
+      <c r="B16" s="94" t="inlineStr">
+        <is>
+          <t>通用弹药</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D16" s="94" t="inlineStr"/>
+      <c r="E16" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L739</t>
+        </is>
+      </c>
+      <c r="G16" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A18</t>
+        </is>
+      </c>
+      <c r="H16" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / melee_chaser
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / ranged_caster
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行16 / exploder</t>
+        </is>
+      </c>
+      <c r="I16" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L739 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J16" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K16" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_on_inventory_item_clicked</t>
+        </is>
+      </c>
+      <c r="L16" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M16" s="94" t="inlineStr">
+        <is>
+          <t>ammo；程序罐体</t>
+        </is>
+      </c>
+      <c r="N16" s="94" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="O16" s="94" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="P16" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q16" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1" s="46">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_standard</t>
+        </is>
+      </c>
+      <c r="B17" s="94" t="inlineStr">
+        <is>
+          <t>标准子弹模块</t>
+        </is>
+      </c>
+      <c r="C17" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E17" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L886</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A28</t>
+        </is>
+      </c>
+      <c r="H17" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
+        </is>
+      </c>
+      <c r="I17" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L886 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J17" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K17" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L17" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M17" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N17" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STANDARD
+VFX-BULLET-STANDARD-3D</t>
+        </is>
+      </c>
+      <c r="O17" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A27</t>
+        </is>
+      </c>
+      <c r="P17" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q17" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1" s="46">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_sticky</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>黏黏弹模块</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E18" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L909</t>
+        </is>
+      </c>
+      <c r="G18" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A29</t>
+        </is>
+      </c>
+      <c r="H18" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I18" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L909 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J18" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K18" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L18" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M18" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N18" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STICKY
+VFX-BULLET-STICKY-3D</t>
+        </is>
+      </c>
+      <c r="O18" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A14
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A28</t>
+        </is>
+      </c>
+      <c r="P18" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q18" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1" s="46">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_bounce</t>
+        </is>
+      </c>
+      <c r="B19" s="94" t="inlineStr">
+        <is>
+          <t>回旋镖弹模块</t>
+        </is>
+      </c>
+      <c r="C19" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E19" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L932</t>
+        </is>
+      </c>
+      <c r="G19" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A24</t>
+        </is>
+      </c>
+      <c r="H19" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I19" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L932 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J19" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K19" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L19" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M19" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N19" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BOUNCE
+VFX-BULLET-BOUNCE-3D</t>
+        </is>
+      </c>
+      <c r="O19" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A15
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A29</t>
+        </is>
+      </c>
+      <c r="P19" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q19" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1" s="46">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_piercing</t>
+        </is>
+      </c>
+      <c r="B20" s="94" t="inlineStr">
+        <is>
+          <t>穿甲弹模块</t>
+        </is>
+      </c>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D20" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E20" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L961</t>
+        </is>
+      </c>
+      <c r="G20" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A27</t>
+        </is>
+      </c>
+      <c r="H20" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I20" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L961 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J20" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K20" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L20" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M20" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N20" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-PIERCING
+VFX-BULLET-PIERCING-3D</t>
+        </is>
+      </c>
+      <c r="O20" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A16
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A30</t>
+        </is>
+      </c>
+      <c r="P20" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q20" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1" s="46">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_explosive</t>
+        </is>
+      </c>
+      <c r="B21" s="94" t="inlineStr">
+        <is>
+          <t>爆炸弹模块</t>
+        </is>
+      </c>
+      <c r="C21" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D21" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E21" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L982</t>
+        </is>
+      </c>
+      <c r="G21" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A25</t>
+        </is>
+      </c>
+      <c r="H21" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
+        </is>
+      </c>
+      <c r="I21" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L982 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J21" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K21" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L21" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M21" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N21" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-EXPLOSIVE
+VFX-BULLET-EXPLOSIVE-3D</t>
+        </is>
+      </c>
+      <c r="O21" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A17
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A31</t>
+        </is>
+      </c>
+      <c r="P21" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q21" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1" s="46">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_homing</t>
+        </is>
+      </c>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>蜂卵弹模块</t>
+        </is>
+      </c>
+      <c r="C22" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E22" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1003</t>
+        </is>
+      </c>
+      <c r="G22" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A26</t>
+        </is>
+      </c>
+      <c r="H22" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I22" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1003 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J22" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K22" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L22" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M22" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N22" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-HOMING
+VFX-BULLET-HOMING-3D</t>
+        </is>
+      </c>
+      <c r="O22" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A18
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A32</t>
+        </is>
+      </c>
+      <c r="P22" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q22" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1" s="46">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_blackhole</t>
+        </is>
+      </c>
+      <c r="B23" s="94" t="inlineStr">
+        <is>
+          <t>黑洞弹模块</t>
+        </is>
+      </c>
+      <c r="C23" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D23" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E23" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1024</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A23</t>
+        </is>
+      </c>
+      <c r="H23" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1024 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J23" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K23" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L23" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M23" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N23" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BLACKHOLE
+VFX-BULLET-BLACKHOLE-3D</t>
+        </is>
+      </c>
+      <c r="O23" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A19
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A33</t>
+        </is>
+      </c>
+      <c r="P23" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q23" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1" s="46">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>mod_bullet_balloon</t>
+        </is>
+      </c>
+      <c r="B24" s="94" t="inlineStr">
+        <is>
+          <t>气球弹模块</t>
+        </is>
+      </c>
+      <c r="C24" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E24" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1045</t>
+        </is>
+      </c>
+      <c r="G24" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A22</t>
+        </is>
+      </c>
+      <c r="H24" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I24" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1045 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+        </is>
+      </c>
+      <c r="J24" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K24" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L24" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M24" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N24" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BALLOON
+VFX-BULLET-BALLOON-3D</t>
+        </is>
+      </c>
+      <c r="O24" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A20
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A34</t>
+        </is>
+      </c>
+      <c r="P24" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q24" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="93" customHeight="1" s="46">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>attach_triple_muzzle</t>
+        </is>
+      </c>
+      <c r="B25" s="94" t="inlineStr">
+        <is>
+          <t>三叉枪口</t>
+        </is>
+      </c>
+      <c r="C25" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D25" s="94" t="inlineStr">
+        <is>
+          <t>muzzle</t>
+        </is>
+      </c>
+      <c r="E25" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1073</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A10</t>
+        </is>
+      </c>
+      <c r="H25" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1073 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J25" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K25" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L25" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M25" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N25" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
+        </is>
+      </c>
+      <c r="O25" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A21</t>
+        </is>
+      </c>
+      <c r="P25" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q25" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="93" customHeight="1" s="46">
+      <c r="A26" s="94" t="inlineStr">
+        <is>
+          <t>attach_rubber_stock</t>
+        </is>
+      </c>
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>橡皮枪托</t>
+        </is>
+      </c>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E26" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1098</t>
+        </is>
+      </c>
+      <c r="G26" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A8</t>
+        </is>
+      </c>
+      <c r="H26" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I26" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1098 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J26" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K26" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L26" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M26" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N26" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-RUBBER-STOCK</t>
+        </is>
+      </c>
+      <c r="O26" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A22</t>
+        </is>
+      </c>
+      <c r="P26" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q26" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="76" customHeight="1" s="46">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>attach_scope</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>放大镜瞄具</t>
+        </is>
+      </c>
+      <c r="C27" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="E27" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1129</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A9</t>
+        </is>
+      </c>
+      <c r="H27" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1129 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J27" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K27" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L27" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M27" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N27" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-SCOPE</t>
+        </is>
+      </c>
+      <c r="O27" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A23</t>
+        </is>
+      </c>
+      <c r="P27" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q27" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="76" customHeight="1" s="46">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>attach_big_mag</t>
+        </is>
+      </c>
+      <c r="B28" s="94" t="inlineStr">
+        <is>
+          <t>肉质弹匣</t>
+        </is>
+      </c>
+      <c r="C28" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D28" s="94" t="inlineStr">
+        <is>
+          <t>magazine</t>
+        </is>
+      </c>
+      <c r="E28" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F28" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1151</t>
+        </is>
+      </c>
+      <c r="G28" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A5</t>
+        </is>
+      </c>
+      <c r="H28" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I28" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1151 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J28" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K28" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L28" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M28" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N28" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-BIG-MAG</t>
+        </is>
+      </c>
+      <c r="O28" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A24</t>
+        </is>
+      </c>
+      <c r="P28" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q28" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="76" customHeight="1" s="46">
+      <c r="A29" s="94" t="inlineStr">
+        <is>
+          <t>attach_fan</t>
+        </is>
+      </c>
+      <c r="B29" s="94" t="inlineStr">
+        <is>
+          <t>小风扇</t>
+        </is>
+      </c>
+      <c r="C29" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D29" s="94" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="E29" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1173</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A7</t>
+        </is>
+      </c>
+      <c r="H29" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I29" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1173 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J29" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K29" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L29" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M29" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N29" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-FAN</t>
+        </is>
+      </c>
+      <c r="O29" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A25</t>
+        </is>
+      </c>
+      <c r="P29" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q29" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="76" customHeight="1" s="46">
+      <c r="A30" s="94" t="inlineStr">
+        <is>
+          <t>attach_copy_sticker</t>
+        </is>
+      </c>
+      <c r="B30" s="94" t="inlineStr">
+        <is>
+          <t>复制贴纸</t>
+        </is>
+      </c>
+      <c r="C30" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
+        <is>
+          <t>mutator</t>
+        </is>
+      </c>
+      <c r="E30" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F30" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1195</t>
+        </is>
+      </c>
+      <c r="G30" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A6</t>
+        </is>
+      </c>
+      <c r="H30" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I30" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1195 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J30" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K30" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L30" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M30" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N30" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-COPY-STICKER</t>
+        </is>
+      </c>
+      <c r="O30" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A26</t>
+        </is>
+      </c>
+      <c r="P30" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q30" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId171"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId172"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$41</definedName>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B13" s="57" t="inlineStr">
         <is>
-          <t>标准子弹</t>
+          <t>标准子弹模块</t>
         </is>
       </c>
       <c r="C13" s="57" t="inlineStr">
@@ -3169,22 +3169,22 @@
       <c r="G13" s="57" t="n"/>
       <c r="H13" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
         </is>
       </c>
       <c r="I13" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J13" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
         </is>
       </c>
       <c r="K13" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L13" s="70" t="inlineStr">
@@ -3199,16 +3199,24 @@
       </c>
       <c r="N13" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O13" s="57" t="n"/>
+          <t>0.3760×0.3760×0.9400m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 176三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O13" s="57" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_source_v001.blend; art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="P13" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q13" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/bullet_standard/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q13" s="57" t="inlineStr">
+        <is>
+          <t>mod_bullet_standard;标准子弹模块</t>
+        </is>
+      </c>
       <c r="R13" s="57">
         <f>LOWER(TRIM(C13)&amp;"|"&amp;TRIM(D13)&amp;"|"&amp;TRIM(E13)&amp;"|"&amp;TRIM(F13)&amp;"|"&amp;TRIM(H13)&amp;"|"&amp;TRIM(I13))</f>
         <v/>
@@ -3217,29 +3225,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T13" s="57" t="n"/>
+      <c r="T13" s="57" t="inlineStr">
+        <is>
+          <t>9c1f7ffa3a57dc6b2bfedbb10ccb1d023df98c7761ea42f9eb00aa729958bb5e</t>
+        </is>
+      </c>
       <c r="U13" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V13" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W13" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
       <c r="X13" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WPN_标准子弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y13" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=3368三角；ground=176三角；地面源SHA256=183bdba5012c84457782d224b2cc6e871af09e3d126187f665497d98a8ca89cd；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -4033,22 +4044,22 @@
       <c r="G21" s="57" t="n"/>
       <c r="H21" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
         </is>
       </c>
       <c r="I21" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J21" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
         </is>
       </c>
       <c r="K21" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L21" s="70" t="inlineStr">
@@ -4063,16 +4074,24 @@
       </c>
       <c r="N21" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O21" s="57" t="n"/>
+          <t>0.1404×0.1600×0.1460m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 198三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O21" s="57" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend; art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="P21" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q21" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/triple_muzzle/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q21" s="57" t="inlineStr">
+        <is>
+          <t>attach_triple_muzzle;三叉枪口</t>
+        </is>
+      </c>
       <c r="R21" s="57">
         <f>LOWER(TRIM(C21)&amp;"|"&amp;TRIM(D21)&amp;"|"&amp;TRIM(E21)&amp;"|"&amp;TRIM(F21)&amp;"|"&amp;TRIM(H21)&amp;"|"&amp;TRIM(I21))</f>
         <v/>
@@ -4081,29 +4100,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T21" s="57" t="n"/>
+      <c r="T21" s="57" t="inlineStr">
+        <is>
+          <t>53871c61c511ac2ac41685bcc65e765b591b5cbcd7880d3685cacf545cdd94c5</t>
+        </is>
+      </c>
       <c r="U21" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V21" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W21" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
       <c r="X21" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WPN_三叉枪口_中文资产管理</t>
         </is>
       </c>
       <c r="Y21" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=7820三角；ground=198三角；地面源SHA256=3fba4ba572c107b080cb05289d21f8d5f6ae778776f7587ffa998222bdf7c293；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -4141,22 +4163,22 @@
       <c r="G22" s="57" t="n"/>
       <c r="H22" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
         </is>
       </c>
       <c r="I22" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J22" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
         </is>
       </c>
       <c r="K22" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L22" s="70" t="inlineStr">
@@ -4171,16 +4193,24 @@
       </c>
       <c r="N22" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O22" s="57" t="n"/>
+          <t>0.1246×0.3200×0.2222m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 145三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O22" s="57" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend; art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="P22" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q22" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/rubber_stock/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q22" s="57" t="inlineStr">
+        <is>
+          <t>attach_rubber_stock;橡皮枪托</t>
+        </is>
+      </c>
       <c r="R22" s="57">
         <f>LOWER(TRIM(C22)&amp;"|"&amp;TRIM(D22)&amp;"|"&amp;TRIM(E22)&amp;"|"&amp;TRIM(F22)&amp;"|"&amp;TRIM(H22)&amp;"|"&amp;TRIM(I22))</f>
         <v/>
@@ -4189,29 +4219,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T22" s="57" t="n"/>
+      <c r="T22" s="57" t="inlineStr">
+        <is>
+          <t>f1cf82e20b7c1a481dfe979503bc3f98fd9566cac09ede315ba238ab9a6c90bb</t>
+        </is>
+      </c>
       <c r="U22" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V22" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W22" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
       <c r="X22" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WPN_橡皮枪托_中文资产管理</t>
         </is>
       </c>
       <c r="Y22" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=20732三角；ground=145三角；地面源SHA256=4e4a906492d9eb1f79bfd5e756991584422fd30664dd502a25cfe542436791d7；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4282,22 @@
       <c r="G23" s="57" t="n"/>
       <c r="H23" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
         </is>
       </c>
       <c r="I23" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J23" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
         </is>
       </c>
       <c r="K23" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L23" s="70" t="inlineStr">
@@ -4279,16 +4312,24 @@
       </c>
       <c r="N23" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O23" s="57" t="n"/>
+          <t>0.1346×0.2800×0.1806m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 198三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O23" s="57" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend; art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="P23" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q23" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/scope/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q23" s="57" t="inlineStr">
+        <is>
+          <t>attach_scope;放大镜瞄具</t>
+        </is>
+      </c>
       <c r="R23" s="57">
         <f>LOWER(TRIM(C23)&amp;"|"&amp;TRIM(D23)&amp;"|"&amp;TRIM(E23)&amp;"|"&amp;TRIM(F23)&amp;"|"&amp;TRIM(H23)&amp;"|"&amp;TRIM(I23))</f>
         <v/>
@@ -4297,29 +4338,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T23" s="57" t="n"/>
+      <c r="T23" s="57" t="inlineStr">
+        <is>
+          <t>6c4244348bb117f35a862187503ab5577be801b5f1dd00e72bcb17c095274b95</t>
+        </is>
+      </c>
       <c r="U23" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V23" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W23" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
       <c r="X23" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WPN_放大镜瞄具_中文资产管理</t>
         </is>
       </c>
       <c r="Y23" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=9044三角；ground=198三角；地面源SHA256=a6ebf1f74d67fb2ee77f1be0bc5442fe1d74d1058826c6cf4d0a43d3f9b9e138；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -4357,22 +4401,22 @@
       <c r="G24" s="57" t="n"/>
       <c r="H24" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
         </is>
       </c>
       <c r="I24" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J24" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
         </is>
       </c>
       <c r="K24" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L24" s="70" t="inlineStr">
@@ -4387,16 +4431,24 @@
       </c>
       <c r="N24" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O24" s="57" t="n"/>
+          <t>0.1101×0.0705×0.2400m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 192三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O24" s="57" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend; art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="P24" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q24" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/big_mag/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q24" s="57" t="inlineStr">
+        <is>
+          <t>attach_big_mag;肉质弹匣</t>
+        </is>
+      </c>
       <c r="R24" s="57">
         <f>LOWER(TRIM(C24)&amp;"|"&amp;TRIM(D24)&amp;"|"&amp;TRIM(E24)&amp;"|"&amp;TRIM(F24)&amp;"|"&amp;TRIM(H24)&amp;"|"&amp;TRIM(I24))</f>
         <v/>
@@ -4405,29 +4457,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T24" s="57" t="n"/>
+      <c r="T24" s="57" t="inlineStr">
+        <is>
+          <t>8513e3320fad3a4af8ee4562b5149b9a45f0e95d72df06accb96b0b7befe72f5</t>
+        </is>
+      </c>
       <c r="U24" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V24" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W24" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
       <c r="X24" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WPN_肉质弹匣_中文资产管理</t>
         </is>
       </c>
       <c r="Y24" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=5856三角；ground=192三角；地面源SHA256=a67664acb24910e970b61d43ed1cf2e3395a876a6896a67853cd5648a19cafff；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="45" min="1" max="1"/>
@@ -8719,6 +8774,80 @@
       <c r="G6" s="56" t="inlineStr">
         <is>
           <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="63" t="inlineStr">
+        <is>
+          <t>v0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>参考图8件道具：Blender原始源</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>道具与武器原始源</t>
+        </is>
+      </c>
+      <c r="E7" s="56" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-BIG-MAG,WPN-BUL-MOD-BULLET-STANDARD,WPN-ATT-ATTACH-RUBBER-STOCK,WPN-ATT-ATTACH-SCOPE,WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>实测尺寸/场景四材质/源已完成；未运行时接入</t>
+        </is>
+      </c>
+      <c r="G7" s="56" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.100</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>物品道具双模型源</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>preview / ground</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>现有高模保留；地面100–200三角面</t>
+        </is>
+      </c>
+      <c r="F8" s="45" t="inlineStr">
+        <is>
+          <t>源已完成；运行时用途选择未接入</t>
+        </is>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -8767,9 +8896,6 @@
           <t>武器账本 · 背包物品调用索引</t>
         </is>
       </c>
-      <c r="B1" s="94" t="n"/>
-      <c r="C1" s="94" t="n"/>
-      <c r="D1" s="94" t="n"/>
       <c r="E1" s="94" t="n"/>
       <c r="F1" s="94" t="n"/>
       <c r="G1" s="94" t="n"/>
@@ -8790,9 +8916,6 @@
           <t>成品武器、子弹模块、通用弹药、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
         </is>
       </c>
-      <c r="B2" s="94" t="n"/>
-      <c r="C2" s="94" t="n"/>
-      <c r="D2" s="94" t="n"/>
       <c r="E2" s="94" t="n"/>
       <c r="F2" s="94" t="n"/>
       <c r="G2" s="94" t="n"/>
@@ -10023,14 +10146,12 @@
       </c>
       <c r="N17" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-STANDARD
-VFX-BULLET-STANDARD-3D</t>
+          <t>WPN-BUL-MOD-BULLET-STANDARD</t>
         </is>
       </c>
       <c r="O17" s="94" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A27</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13</t>
         </is>
       </c>
       <c r="P17" s="94" t="inlineStr">
@@ -10040,7 +10161,7 @@
       </c>
       <c r="Q17" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10871,7 @@
       </c>
       <c r="Q25" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10958,7 @@
       </c>
       <c r="Q26" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -10924,7 +11045,7 @@
       </c>
       <c r="Q27" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11132,7 @@
       </c>
       <c r="Q28" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-武器'!$A$4:$P$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1158,8 +1159,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeaponInventoryItems" displayName="WeaponInventoryItems" ref="A4:Q30" headerRowCount="1">
-  <autoFilter ref="A4:Q30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeaponInventoryItems" displayName="WeaponInventoryItems" ref="A4:Q31" headerRowCount="1">
+  <autoFilter ref="A4:Q31"/>
   <tableColumns count="17">
     <tableColumn id="1" name="内容ID"/>
     <tableColumn id="2" name="名称"/>
@@ -3179,12 +3180,12 @@
       </c>
       <c r="J13" s="57" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>武器装配标准子弹模块；继续程序表现</t>
         </is>
       </c>
       <c r="K13" s="57" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>程序占位</t>
         </is>
       </c>
       <c r="L13" s="70" t="inlineStr">
@@ -3202,14 +3203,10 @@
           <t>0.3760×0.3760×0.9400m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 176三角面（100–200预算）</t>
         </is>
       </c>
-      <c r="O13" s="57" t="inlineStr">
-        <is>
-          <t>art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_source_v001.blend; art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_ground_source_v001.blend</t>
-        </is>
-      </c>
+      <c r="O13" s="57" t="n"/>
       <c r="P13" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/bullet_standard/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q13" s="57" t="inlineStr">
@@ -3225,11 +3222,7 @@
         <f>IF(COUNTIF($R$6:$R$41,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T13" s="57" t="inlineStr">
-        <is>
-          <t>9c1f7ffa3a57dc6b2bfedbb10ccb1d023df98c7761ea42f9eb00aa729958bb5e</t>
-        </is>
-      </c>
+      <c r="T13" s="57" t="n"/>
       <c r="U13" s="57" t="inlineStr">
         <is>
           <t>Codex</t>
@@ -3243,14 +3236,10 @@
           <t>用户提供参考图重建；项目公共色盘</t>
         </is>
       </c>
-      <c r="X13" s="72" t="inlineStr">
-        <is>
-          <t>WPN_标准子弹模块_中文资产管理</t>
-        </is>
-      </c>
+      <c r="X13" s="72" t="n"/>
       <c r="Y13" s="57" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=3368三角；ground=176三角；地面源SHA256=183bdba5012c84457782d224b2cc6e871af09e3d126187f665497d98a8ca89cd；高模哈希保持；未接入运行时。</t>
+          <t>用户更正：此前蓝金弹头源重新归属通用弹药ITM-CONSUMABLE-ITEM-AMMO-PACK；此资产尚无对应正式模型。</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4043,12 @@
       </c>
       <c r="J21" s="57" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K21" s="57" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L21" s="70" t="inlineStr">
@@ -4079,12 +4068,12 @@
       </c>
       <c r="O21" s="57" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend; art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/weapons/triple_muzzle/runtime/wpn_triple_muzzle_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P21" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/triple_muzzle/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q21" s="57" t="inlineStr">
@@ -4102,7 +4091,7 @@
       </c>
       <c r="T21" s="57" t="inlineStr">
         <is>
-          <t>53871c61c511ac2ac41685bcc65e765b591b5cbcd7880d3685cacf545cdd94c5</t>
+          <t>dc29f696a3a6ba10438dd5bdb8ea0c0dfde55ded2bbb30dd8a1c45355286cef5</t>
         </is>
       </c>
       <c r="U21" s="57" t="inlineStr">
@@ -4125,7 +4114,7 @@
       </c>
       <c r="Y21" s="57" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=7820三角；ground=198三角；地面源SHA256=3fba4ba572c107b080cb05289d21f8d5f6ae778776f7587ffa998222bdf7c293；高模哈希保持；未接入运行时。</t>
+          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/triple_muzzle/components/wpn_triple_muzzle_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend SHA256=3fba4ba572c107b080cb05289d21f8d5f6ae778776f7587ffa998222bdf7c293；preview源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend SHA256=53871c61c511ac2ac41685bcc65e765b591b5cbcd7880d3685cacf545cdd94c5；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4162,12 @@
       </c>
       <c r="J22" s="57" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K22" s="57" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L22" s="70" t="inlineStr">
@@ -4198,12 +4187,12 @@
       </c>
       <c r="O22" s="57" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend; art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/weapons/rubber_stock/runtime/wpn_rubber_stock_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P22" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/rubber_stock/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q22" s="57" t="inlineStr">
@@ -4221,7 +4210,7 @@
       </c>
       <c r="T22" s="57" t="inlineStr">
         <is>
-          <t>f1cf82e20b7c1a481dfe979503bc3f98fd9566cac09ede315ba238ab9a6c90bb</t>
+          <t>a4ccb5d3e2bf5bcf6bb921068be1de6e5c97db871024d0e8bdaa42bdb2dd19ce</t>
         </is>
       </c>
       <c r="U22" s="57" t="inlineStr">
@@ -4244,7 +4233,7 @@
       </c>
       <c r="Y22" s="57" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=20732三角；ground=145三角；地面源SHA256=4e4a906492d9eb1f79bfd5e756991584422fd30664dd502a25cfe542436791d7；高模哈希保持；未接入运行时。</t>
+          <t>ground=145三角；GLB=assets/art/items_weapons/weapons/rubber_stock/components/wpn_rubber_stock_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend SHA256=4e4a906492d9eb1f79bfd5e756991584422fd30664dd502a25cfe542436791d7；preview源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend SHA256=f1cf82e20b7c1a481dfe979503bc3f98fd9566cac09ede315ba238ab9a6c90bb；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4281,12 @@
       </c>
       <c r="J23" s="57" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K23" s="57" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L23" s="70" t="inlineStr">
@@ -4317,12 +4306,12 @@
       </c>
       <c r="O23" s="57" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend; art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/weapons/scope/runtime/wpn_scope_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P23" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/scope/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q23" s="57" t="inlineStr">
@@ -4340,7 +4329,7 @@
       </c>
       <c r="T23" s="57" t="inlineStr">
         <is>
-          <t>6c4244348bb117f35a862187503ab5577be801b5f1dd00e72bcb17c095274b95</t>
+          <t>d962c82f52ea48e01a84d91e781af87e55ee6936c8280c1b5a7242f4ea0beb1d</t>
         </is>
       </c>
       <c r="U23" s="57" t="inlineStr">
@@ -4363,7 +4352,7 @@
       </c>
       <c r="Y23" s="57" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=9044三角；ground=198三角；地面源SHA256=a6ebf1f74d67fb2ee77f1be0bc5442fe1d74d1058826c6cf4d0a43d3f9b9e138；高模哈希保持；未接入运行时。</t>
+          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/scope/components/wpn_scope_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend SHA256=a6ebf1f74d67fb2ee77f1be0bc5442fe1d74d1058826c6cf4d0a43d3f9b9e138；preview源=art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend SHA256=6c4244348bb117f35a862187503ab5577be801b5f1dd00e72bcb17c095274b95；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4400,12 @@
       </c>
       <c r="J24" s="57" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K24" s="57" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L24" s="70" t="inlineStr">
@@ -4436,12 +4425,12 @@
       </c>
       <c r="O24" s="57" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend; art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/weapons/big_mag/runtime/wpn_big_mag_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P24" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/weapons/big_mag/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q24" s="57" t="inlineStr">
@@ -4459,7 +4448,7 @@
       </c>
       <c r="T24" s="57" t="inlineStr">
         <is>
-          <t>8513e3320fad3a4af8ee4562b5149b9a45f0e95d72df06accb96b0b7befe72f5</t>
+          <t>5de5c693bc21fb7f09a618ccab95c4830ca88902da8844dc1be885928072a775</t>
         </is>
       </c>
       <c r="U24" s="57" t="inlineStr">
@@ -4482,7 +4471,7 @@
       </c>
       <c r="Y24" s="57" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=5856三角；ground=192三角；地面源SHA256=a67664acb24910e970b61d43ed1cf2e3395a876a6896a67853cd5648a19cafff；高模哈希保持；未接入运行时。</t>
+          <t>ground=192三角；GLB=assets/art/items_weapons/weapons/big_mag/components/wpn_big_mag_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend SHA256=a67664acb24910e970b61d43ed1cf2e3395a876a6896a67853cd5648a19cafff；preview源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend SHA256=8513e3320fad3a4af8ee4562b5149b9a45f0e95d72df06accb96b0b7befe72f5；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6699,7 @@
     <row r="427" ht="84.75" customHeight="1" s="46"/>
     <row r="429" ht="120" customHeight="1" s="46"/>
   </sheetData>
-  <autoFilter ref="A5:X41"/>
+  <autoFilter ref="A5:Y41"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -6757,7 +6746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="45" min="1" max="1"/>
@@ -6787,7 +6776,7 @@
     <row r="2" ht="33.75" customHeight="1" s="46">
       <c r="A2" s="76" t="inlineStr">
         <is>
-          <t>枪械、近战武器与武器装配根；本次扫描 22 个独立Prefab。</t>
+          <t>一行一个独立PackedScene；地面模型使用ground角色，状态以各行记录为准。</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8634,336 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-BIG-MAG</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="inlineStr">
+        <is>
+          <t>肉质弹匣（地面）</t>
+        </is>
+      </c>
+      <c r="C27" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/big_mag/runtime/wpn_big_mag_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D27" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/big_mag/components/wpn_big_mag_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E27" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F27" s="82" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G27" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H27" s="82" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I27" s="82" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J27" s="82" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K27" s="82" t="inlineStr">
+        <is>
+          <t>0.110071×0.070468×0.24m；192三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L27" s="82" t="inlineStr">
+        <is>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
+        </is>
+      </c>
+      <c r="M27" s="82" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N27" s="82" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O27" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P27" s="84" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="inlineStr">
+        <is>
+          <t>三叉枪口（地面）</t>
+        </is>
+      </c>
+      <c r="C28" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/triple_muzzle/runtime/wpn_triple_muzzle_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D28" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/triple_muzzle/components/wpn_triple_muzzle_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E28" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F28" s="82" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G28" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H28" s="82" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I28" s="82" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J28" s="82" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K28" s="82" t="inlineStr">
+        <is>
+          <t>0.140351×0.16×0.145965m；198三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L28" s="82" t="inlineStr">
+        <is>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
+        </is>
+      </c>
+      <c r="M28" s="82" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N28" s="82" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O28" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P28" s="84" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-RUBBER-STOCK</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>橡皮枪托（地面）</t>
+        </is>
+      </c>
+      <c r="C29" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/rubber_stock/runtime/wpn_rubber_stock_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D29" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/rubber_stock/components/wpn_rubber_stock_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E29" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F29" s="82" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G29" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H29" s="82" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I29" s="82" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J29" s="82" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K29" s="82" t="inlineStr">
+        <is>
+          <t>0.124603×0.32×0.222154m；145三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L29" s="82" t="inlineStr">
+        <is>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
+        </is>
+      </c>
+      <c r="M29" s="82" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N29" s="82" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O29" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P29" s="84" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-SCOPE</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
+        <is>
+          <t>放大镜瞄具（地面）</t>
+        </is>
+      </c>
+      <c r="C30" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/scope/runtime/wpn_scope_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D30" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/scope/components/wpn_scope_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E30" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F30" s="82" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G30" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H30" s="82" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I30" s="82" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J30" s="82" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K30" s="82" t="inlineStr">
+        <is>
+          <t>0.134558×0.28×0.180565m；198三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L30" s="82" t="inlineStr">
+        <is>
+          <t>挂点中心原点；Blender +Y 对应 Godot -Z 枪口，+Z向上</t>
+        </is>
+      </c>
+      <c r="M30" s="82" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N30" s="82" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O30" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P30" s="84" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:P31"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -8676,7 +8994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="45" min="1" max="1"/>
@@ -8814,7 +9132,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" s="46">
       <c r="A8" s="45" t="inlineStr">
         <is>
           <t>v0.1.100</t>
@@ -8848,6 +9166,191 @@
       <c r="G8" s="45" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="46">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.101</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>武器基础数值与范围伤害调整（内容侧）</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>远程枪身 / 配件 / 范围爆炸</t>
+        </is>
+      </c>
+      <c r="E9" s="45" t="inlineStr">
+        <is>
+          <t>豌豆手枪18→25、花洒机枪8→12、散射喷壶12→45、步枪22→60、弹弓狙击55→380、反胃榴弹筒38→250且射速0.8→1、放大镜瞄具伤害+5→+15、蓄力萝卜炮30→880；反胃榴弹筒与蓄力萝卜炮新增 explosion_damage_scale（中心范围伤害180/560）；蓄力萝卜炮新增 explosive 行为标签，获得命中范围爆炸。数值真身 src/base/BlueprintRegistry.gd 与 src/combat3d/WeaponModel3D.gd；内容数据库《武器》表已同步。</t>
+        </is>
+      </c>
+      <c r="F9" s="45" t="inlineStr">
+        <is>
+          <t>本账本《资产主表》不持玩法数值：资产条目、AssetID、路径与SHA-256全部不变。旧存档 WeaponInstance.assembly_snapshot 保留生成时 base_stats，旧枪不自动生效新数值。</t>
+        </is>
+      </c>
+      <c r="G9" s="45" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.102</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>地面简模正式路径与代码接线</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>8件物品ground角色</t>
+        </is>
+      </c>
+      <c r="E10" s="45" t="inlineStr">
+        <is>
+          <t>GLB/PackedScene/公共色盘导入；同一AssetID；预览待导入</t>
+        </is>
+      </c>
+      <c r="F10" s="45" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="G10" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="46">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.103</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>新增初始步枪（出厂枪）</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>武器·背包物品调用索引 / 内容表 / 开场剧本</t>
+        </is>
+      </c>
+      <c r="E11" s="45" t="inlineStr">
+        <is>
+          <t>新增枪身 bp_starter_rifle（初始步枪，以步枪为原型：damage 50 / fire_rate 50 / reload_time 1.8s / magazine 30 / spread 0.07，命运槽容量 4）。成品 weapon_starter_rifle 与本枪蓝图 bp_starter_rifle 同批注册；出场枪由 bp_sprinkler 改为 bp_starter_rifle（BlueprintRegistry.DEFAULT_STARTING_GUN_ID），开场剧本 nar_tower_opening_01_wake 的地面枪同步改为 weapon_starter_rifle。本账本《背包物品调用索引》按 scripts/sync_inventory_item_ledger.py --write 重生成，武器条目 26→27。内容数据库《武器》《掉落物品》《总览》同步补行与更正口径。</t>
+        </is>
+      </c>
+      <c r="F11" s="45" t="inlineStr">
+        <is>
+          <t>《资产主表》未改动：无新 AssetID、无新 GLB，枪械美术复用步枪的 broom_rifle 资产（口径同花洒机枪复用蜂窝机枪）。旧存档中的枪实例保留生成时快照，不自动变为新枪。花洒机枪（weapon_sprinkler）仍只有运行注册、内容表未登记行。</t>
+        </is>
+      </c>
+      <c r="G11" s="45" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="46">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.104</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>用户更正通用弹药用途</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>模型身份/图标/倾斜</t>
+        </is>
+      </c>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>通用弹药复用蓝金弹头；标准模块退回程序表现</t>
+        </is>
+      </c>
+      <c r="F12" s="45" t="inlineStr">
+        <is>
+          <t>已接线，待运行验收</t>
+        </is>
+      </c>
+      <c r="G12" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="46">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.105</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>枪械射程独立化（新增每枪 range 字段）</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>远程枪身 / 弹体生命周期</t>
+        </is>
+      </c>
+      <c r="E13" s="45" t="inlineStr">
+        <is>
+          <t>新增枪身 base_stats.range（米）＝弹体最远飞行距离，与 bullet_speed 解耦（弹速只决定飞行时间）。Projectile3D 新增 range_m / _traveled 与射程判定，并按实际飞行路径长度累计；爆炸类弹到射程原地自动引爆（榴弹 18m 自动爆炸），普通弹直接消失；命中路径与射程上限共用新抽出的 _is_explosive_payload()。WeaponModel3D 新增 range_m，三处 spawn 配置（主弹/副枪/复制波次）注入。逐枪定值：散射喷壶 7、豌豆手枪 15、步枪 20、初始步枪 20、反胃榴弹筒 18、蜂窝机枪/花洒机枪/蓄力萝卜炮 18、弹弓狙击 60。内容表《武器》核心数值列同步 range=。</t>
+        </is>
+      </c>
+      <c r="F13" s="45" t="inlineStr">
+        <is>
+          <t>本账本《资产主表》与《背包物品调用索引》未改动：无新 AssetID、无新资产，射程是玩法数值不进资产行。verify_starting_weapon_contract 新增射程数据与接线两层判据（含负向自测）。弹种之间不再有射程差异（穿甲弹原 32.2m 优势消失）；蜂窝/花洒/萝卜炮/狙击为工程取值待业主确认。</t>
+        </is>
+      </c>
+      <c r="G13" s="45" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
         </is>
       </c>
     </row>
@@ -8868,7 +9371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="46" min="1" max="1"/>
@@ -9471,15 +9974,15 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="93" customHeight="1" s="46">
+    <row r="10" ht="110" customHeight="1" s="46">
       <c r="A10" s="94" t="inlineStr">
         <is>
-          <t>weapon_sniper</t>
+          <t>weapon_starter_rifle</t>
         </is>
       </c>
       <c r="B10" s="94" t="inlineStr">
         <is>
-          <t>弹弓狙击</t>
+          <t>初始步枪</t>
         </is>
       </c>
       <c r="C10" s="94" t="inlineStr">
@@ -9504,7 +10007,7 @@
       </c>
       <c r="G10" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A36</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A50</t>
         </is>
       </c>
       <c r="H10" s="94" t="inlineStr">
@@ -9514,7 +10017,7 @@
       </c>
       <c r="I10" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L333 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L333 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J10" s="95" t="inlineStr">
@@ -9539,12 +10042,12 @@
       </c>
       <c r="N10" s="94" t="inlineStr">
         <is>
-          <t>WPN-GUN-BP-SNIPER</t>
-        </is>
-      </c>
-      <c r="O10" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A10</t>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="O10" s="94" t="inlineStr">
+        <is>
+          <t>未登记</t>
         </is>
       </c>
       <c r="P10" s="94" t="inlineStr">
@@ -9554,1510 +10057,1512 @@
       </c>
       <c r="Q10" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="93" customHeight="1" s="46">
       <c r="A11" s="94" t="inlineStr">
         <is>
+          <t>weapon_sniper</t>
+        </is>
+      </c>
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>弹弓狙击</t>
+        </is>
+      </c>
+      <c r="C11" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E11" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L365</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A36</t>
+        </is>
+      </c>
+      <c r="H11" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I11" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L365 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J11" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K11" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L11" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M11" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N11" s="94" t="inlineStr">
+        <is>
+          <t>WPN-GUN-BP-SNIPER</t>
+        </is>
+      </c>
+      <c r="O11" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A10</t>
+        </is>
+      </c>
+      <c r="P11" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q11" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="93" customHeight="1" s="46">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
           <t>weapon_launcher</t>
         </is>
       </c>
-      <c r="B11" s="94" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>反胃榴弹筒</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="D11" s="94" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>gun_body</t>
         </is>
       </c>
-      <c r="E11" s="94" t="inlineStr">
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F11" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L360</t>
-        </is>
-      </c>
-      <c r="G11" s="95" t="inlineStr">
+      <c r="F12" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L392</t>
+        </is>
+      </c>
+      <c r="G12" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A31</t>
         </is>
       </c>
-      <c r="H11" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行15 / exploder</t>
-        </is>
-      </c>
-      <c r="I11" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L360 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
-        </is>
-      </c>
-      <c r="J11" s="95" t="inlineStr">
+      <c r="H12" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行13 / exploder</t>
+        </is>
+      </c>
+      <c r="I12" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L392 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J12" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K11" s="95" t="inlineStr">
+      <c r="K12" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
         </is>
       </c>
-      <c r="L11" s="95" t="inlineStr">
+      <c r="L12" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M11" s="94" t="inlineStr">
+      <c r="M12" s="94" t="inlineStr">
         <is>
           <t>weapon；真实武器快照重建</t>
         </is>
       </c>
-      <c r="N11" s="94" t="inlineStr">
+      <c r="N12" s="94" t="inlineStr">
         <is>
           <t>WPN-GUN-BP-LAUNCHER</t>
         </is>
       </c>
-      <c r="O11" s="95" t="inlineStr">
+      <c r="O12" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A11</t>
         </is>
       </c>
-      <c r="P11" s="94" t="inlineStr">
+      <c r="P12" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q11" s="94" t="inlineStr">
+      <c r="Q12" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="76" customHeight="1" s="46">
-      <c r="A12" s="94" t="inlineStr">
+    <row r="13" ht="76" customHeight="1" s="46">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>weapon_charge</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>蓄力萝卜炮</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C13" s="94" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="D12" s="94" t="inlineStr">
+      <c r="D13" s="94" t="inlineStr">
         <is>
           <t>gun_body</t>
         </is>
       </c>
-      <c r="E12" s="94" t="inlineStr">
+      <c r="E13" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F12" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L387</t>
-        </is>
-      </c>
-      <c r="G12" s="95" t="inlineStr">
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L419</t>
+        </is>
+      </c>
+      <c r="G13" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A30</t>
         </is>
       </c>
-      <c r="H12" s="94" t="inlineStr">
+      <c r="H13" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I12" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L387 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
-        </is>
-      </c>
-      <c r="J12" s="95" t="inlineStr">
+      <c r="I13" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L419 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J13" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K12" s="95" t="inlineStr">
+      <c r="K13" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
         </is>
       </c>
-      <c r="L12" s="95" t="inlineStr">
+      <c r="L13" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M12" s="94" t="inlineStr">
+      <c r="M13" s="94" t="inlineStr">
         <is>
           <t>weapon；真实武器快照重建</t>
         </is>
       </c>
-      <c r="N12" s="94" t="inlineStr">
+      <c r="N13" s="94" t="inlineStr">
         <is>
           <t>WPN-GUN-BP-CHARGE</t>
         </is>
       </c>
-      <c r="O12" s="95" t="inlineStr">
+      <c r="O13" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A12</t>
         </is>
       </c>
-      <c r="P12" s="94" t="inlineStr">
+      <c r="P13" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q12" s="94" t="inlineStr">
+      <c r="Q13" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="59" customHeight="1" s="46">
-      <c r="A13" s="94" t="inlineStr">
+    <row r="14" ht="59" customHeight="1" s="46">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>weapon_baseball_bat</t>
         </is>
       </c>
-      <c r="B13" s="94" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>废土棒球棍</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
+      <c r="C14" s="94" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="D13" s="94" t="inlineStr">
+      <c r="D14" s="94" t="inlineStr">
         <is>
           <t>melee_weapon</t>
         </is>
       </c>
-      <c r="E13" s="94" t="inlineStr">
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F13" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L410</t>
-        </is>
-      </c>
-      <c r="G13" s="95" t="inlineStr">
+      <c r="F14" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L442</t>
+        </is>
+      </c>
+      <c r="G14" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A49</t>
         </is>
       </c>
-      <c r="H13" s="94" t="inlineStr">
+      <c r="H14" s="94" t="inlineStr">
         <is>
           <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行3 / melee_chaser</t>
         </is>
       </c>
-      <c r="I13" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L410 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
-        </is>
-      </c>
-      <c r="J13" s="95" t="inlineStr">
+      <c r="I14" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L442 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
+        </is>
+      </c>
+      <c r="J14" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K13" s="95" t="inlineStr">
+      <c r="K14" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
         </is>
       </c>
-      <c r="L13" s="95" t="inlineStr">
+      <c r="L14" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M13" s="94" t="inlineStr">
+      <c r="M14" s="94" t="inlineStr">
         <is>
           <t>weapon；真实武器快照重建</t>
         </is>
       </c>
-      <c r="N13" s="94" t="inlineStr">
+      <c r="N14" s="94" t="inlineStr">
         <is>
           <t>WPN-MELEE-BP-BASEBALL-BAT</t>
         </is>
       </c>
-      <c r="O13" s="95" t="inlineStr">
+      <c r="O14" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A30</t>
         </is>
       </c>
-      <c r="P13" s="94" t="inlineStr">
+      <c r="P14" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q13" s="94" t="inlineStr">
+      <c r="Q14" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="76" customHeight="1" s="46">
-      <c r="A14" s="94" t="inlineStr">
-        <is>
-          <t>weapon_greatblade</t>
-        </is>
-      </c>
-      <c r="B14" s="94" t="inlineStr">
-        <is>
-          <t>巨型工业断刃</t>
-        </is>
-      </c>
-      <c r="C14" s="94" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="D14" s="94" t="inlineStr">
-        <is>
-          <t>melee_weapon</t>
-        </is>
-      </c>
-      <c r="E14" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F14" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L430</t>
-        </is>
-      </c>
-      <c r="G14" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A47</t>
-        </is>
-      </c>
-      <c r="H14" s="94" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
-      <c r="I14" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L430 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J14" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K14" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
-        </is>
-      </c>
-      <c r="L14" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M14" s="94" t="inlineStr">
-        <is>
-          <t>weapon；真实武器快照重建</t>
-        </is>
-      </c>
-      <c r="N14" s="94" t="inlineStr">
-        <is>
-          <t>WPN-MELEE-BP-GREATBLADE</t>
-        </is>
-      </c>
-      <c r="O14" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A28</t>
-        </is>
-      </c>
-      <c r="P14" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="Q14" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1" s="46">
       <c r="A15" s="94" t="inlineStr">
         <is>
+          <t>weapon_greatblade</t>
+        </is>
+      </c>
+      <c r="B15" s="94" t="inlineStr">
+        <is>
+          <t>巨型工业断刃</t>
+        </is>
+      </c>
+      <c r="C15" s="94" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>melee_weapon</t>
+        </is>
+      </c>
+      <c r="E15" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L462</t>
+        </is>
+      </c>
+      <c r="G15" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A47</t>
+        </is>
+      </c>
+      <c r="H15" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I15" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L462 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J15" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K15" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
+        </is>
+      </c>
+      <c r="L15" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M15" s="94" t="inlineStr">
+        <is>
+          <t>weapon；真实武器快照重建</t>
+        </is>
+      </c>
+      <c r="N15" s="94" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-GREATBLADE</t>
+        </is>
+      </c>
+      <c r="O15" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A28</t>
+        </is>
+      </c>
+      <c r="P15" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q15" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1" s="46">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
           <t>weapon_waraxe</t>
         </is>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>攻城裂甲斧</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="D15" s="94" t="inlineStr">
+      <c r="D16" s="94" t="inlineStr">
         <is>
           <t>melee_weapon</t>
         </is>
       </c>
-      <c r="E15" s="94" t="inlineStr">
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F15" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L452</t>
-        </is>
-      </c>
-      <c r="G15" s="95" t="inlineStr">
+      <c r="F16" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L484</t>
+        </is>
+      </c>
+      <c r="G16" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A48</t>
         </is>
       </c>
-      <c r="H15" s="94" t="inlineStr">
+      <c r="H16" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I15" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L452 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
-        </is>
-      </c>
-      <c r="J15" s="95" t="inlineStr">
+      <c r="I16" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L484 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
+        </is>
+      </c>
+      <c r="J16" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K15" s="95" t="inlineStr">
+      <c r="K16" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_equip_weapon_from_inventory</t>
         </is>
       </c>
-      <c r="L15" s="95" t="inlineStr">
+      <c r="L16" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M15" s="94" t="inlineStr">
+      <c r="M16" s="94" t="inlineStr">
         <is>
           <t>weapon；真实武器快照重建</t>
         </is>
       </c>
-      <c r="N15" s="94" t="inlineStr">
+      <c r="N16" s="94" t="inlineStr">
         <is>
           <t>WPN-MELEE-BP-WARAXE</t>
         </is>
       </c>
-      <c r="O15" s="95" t="inlineStr">
+      <c r="O16" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A29</t>
         </is>
       </c>
-      <c r="P15" s="94" t="inlineStr">
+      <c r="P16" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q15" s="94" t="inlineStr">
+      <c r="Q16" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="110" customHeight="1" s="46">
-      <c r="A16" s="94" t="inlineStr">
+    <row r="17" ht="110" customHeight="1" s="46">
+      <c r="A17" s="94" t="inlineStr">
         <is>
           <t>item_ammo_pack</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>通用弹药</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="D16" s="94" t="inlineStr"/>
-      <c r="E16" s="94" t="inlineStr">
+      <c r="D17" s="94" t="inlineStr"/>
+      <c r="E17" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F16" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L739</t>
-        </is>
-      </c>
-      <c r="G16" s="95" t="inlineStr">
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L800</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A18</t>
         </is>
       </c>
-      <c r="H16" s="94" t="inlineStr">
+      <c r="H17" s="94" t="inlineStr">
         <is>
           <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / melee_chaser
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / ranged_caster
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行16 / exploder</t>
-        </is>
-      </c>
-      <c r="I16" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L739 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
-        </is>
-      </c>
-      <c r="J16" s="95" t="inlineStr">
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14 / exploder</t>
+        </is>
+      </c>
+      <c r="I17" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L800 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J17" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K16" s="95" t="inlineStr">
+      <c r="K17" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_on_inventory_item_clicked</t>
         </is>
       </c>
-      <c r="L16" s="95" t="inlineStr">
+      <c r="L17" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M16" s="94" t="inlineStr">
+      <c r="M17" s="94" t="inlineStr">
         <is>
           <t>ammo；程序罐体</t>
         </is>
       </c>
-      <c r="N16" s="94" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O16" s="94" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="P16" s="94" t="inlineStr">
+      <c r="N17" s="94" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-AMMO-PACK</t>
+        </is>
+      </c>
+      <c r="O17" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A34</t>
+        </is>
+      </c>
+      <c r="P17" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q16" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="76" customHeight="1" s="46">
-      <c r="A17" s="94" t="inlineStr">
-        <is>
-          <t>mod_bullet_standard</t>
-        </is>
-      </c>
-      <c r="B17" s="94" t="inlineStr">
-        <is>
-          <t>标准子弹模块</t>
-        </is>
-      </c>
-      <c r="C17" s="94" t="inlineStr">
-        <is>
-          <t>module</t>
-        </is>
-      </c>
-      <c r="D17" s="94" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="E17" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F17" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L886</t>
-        </is>
-      </c>
-      <c r="G17" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A28</t>
-        </is>
-      </c>
-      <c r="H17" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
-        </is>
-      </c>
-      <c r="I17" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L886 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J17" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K17" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
-        </is>
-      </c>
-      <c r="L17" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M17" s="94" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="N17" s="94" t="inlineStr">
-        <is>
-          <t>WPN-BUL-MOD-BULLET-STANDARD</t>
-        </is>
-      </c>
-      <c r="O17" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13</t>
-        </is>
-      </c>
-      <c r="P17" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
       <c r="Q17" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>蓝金色通用弹药模型已映射地面与图标；倾斜45度旋转</t>
         </is>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1" s="46">
       <c r="A18" s="94" t="inlineStr">
         <is>
+          <t>mod_bullet_standard</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>标准子弹模块</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="E18" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L947</t>
+        </is>
+      </c>
+      <c r="G18" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A28</t>
+        </is>
+      </c>
+      <c r="H18" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
+        </is>
+      </c>
+      <c r="I18" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L947 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J18" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K18" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+        </is>
+      </c>
+      <c r="L18" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M18" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="N18" s="94" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STANDARD
+VFX-BULLET-STANDARD-3D</t>
+        </is>
+      </c>
+      <c r="O18" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13
+assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A27</t>
+        </is>
+      </c>
+      <c r="P18" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q18" s="94" t="inlineStr">
+        <is>
+          <t>标准子弹模块继续程序表现；蓝金弹头模型按用户更正归属通用弹药</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1" s="46">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
           <t>mod_bullet_sticky</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B19" s="94" t="inlineStr">
         <is>
           <t>黏黏弹模块</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C19" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D18" s="94" t="inlineStr">
+      <c r="D19" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E18" s="94" t="inlineStr">
+      <c r="E19" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F18" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L909</t>
-        </is>
-      </c>
-      <c r="G18" s="95" t="inlineStr">
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L970</t>
+        </is>
+      </c>
+      <c r="G19" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A29</t>
         </is>
       </c>
-      <c r="H18" s="94" t="inlineStr">
+      <c r="H19" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I18" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L909 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J18" s="95" t="inlineStr">
+      <c r="I19" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L970 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J19" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K18" s="95" t="inlineStr">
+      <c r="K19" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L18" s="95" t="inlineStr">
+      <c r="L19" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M18" s="94" t="inlineStr">
+      <c r="M19" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N18" s="94" t="inlineStr">
+      <c r="N19" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-STICKY
 VFX-BULLET-STICKY-3D</t>
         </is>
       </c>
-      <c r="O18" s="94" t="inlineStr">
+      <c r="O19" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A14
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A28</t>
         </is>
       </c>
-      <c r="P18" s="94" t="inlineStr">
+      <c r="P19" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q18" s="94" t="inlineStr">
+      <c r="Q19" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1" s="46">
-      <c r="A19" s="94" t="inlineStr">
+    <row r="20" ht="76" customHeight="1" s="46">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_bounce</t>
         </is>
       </c>
-      <c r="B19" s="94" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>回旋镖弹模块</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
+      <c r="C20" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D19" s="94" t="inlineStr">
+      <c r="D20" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E19" s="94" t="inlineStr">
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F19" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L932</t>
-        </is>
-      </c>
-      <c r="G19" s="95" t="inlineStr">
+      <c r="F20" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L993</t>
+        </is>
+      </c>
+      <c r="G20" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A24</t>
         </is>
       </c>
-      <c r="H19" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
-        </is>
-      </c>
-      <c r="I19" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L932 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J19" s="95" t="inlineStr">
+      <c r="H20" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I20" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L993 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J20" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K19" s="95" t="inlineStr">
+      <c r="K20" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L19" s="95" t="inlineStr">
+      <c r="L20" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M19" s="94" t="inlineStr">
+      <c r="M20" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N19" s="94" t="inlineStr">
+      <c r="N20" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-BOUNCE
 VFX-BULLET-BOUNCE-3D</t>
         </is>
       </c>
-      <c r="O19" s="94" t="inlineStr">
+      <c r="O20" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A15
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A29</t>
         </is>
       </c>
-      <c r="P19" s="94" t="inlineStr">
+      <c r="P20" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q19" s="94" t="inlineStr">
+      <c r="Q20" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="76" customHeight="1" s="46">
-      <c r="A20" s="94" t="inlineStr">
+    <row r="21" ht="76" customHeight="1" s="46">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_piercing</t>
         </is>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>穿甲弹模块</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C21" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D20" s="94" t="inlineStr">
+      <c r="D21" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E20" s="94" t="inlineStr">
+      <c r="E21" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F20" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L961</t>
-        </is>
-      </c>
-      <c r="G20" s="95" t="inlineStr">
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1022</t>
+        </is>
+      </c>
+      <c r="G21" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A27</t>
         </is>
       </c>
-      <c r="H20" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
-        </is>
-      </c>
-      <c r="I20" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L961 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
-        </is>
-      </c>
-      <c r="J20" s="95" t="inlineStr">
+      <c r="H21" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行6 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I21" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1022 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J21" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K20" s="95" t="inlineStr">
+      <c r="K21" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L20" s="95" t="inlineStr">
+      <c r="L21" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M20" s="94" t="inlineStr">
+      <c r="M21" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N20" s="94" t="inlineStr">
+      <c r="N21" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-PIERCING
 VFX-BULLET-PIERCING-3D</t>
         </is>
       </c>
-      <c r="O20" s="94" t="inlineStr">
+      <c r="O21" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A16
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A30</t>
         </is>
       </c>
-      <c r="P20" s="94" t="inlineStr">
+      <c r="P21" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q20" s="94" t="inlineStr">
+      <c r="Q21" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1" s="46">
-      <c r="A21" s="94" t="inlineStr">
+    <row r="22" ht="76" customHeight="1" s="46">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_explosive</t>
         </is>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>爆炸弹模块</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
+      <c r="C22" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D21" s="94" t="inlineStr">
+      <c r="D22" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E21" s="94" t="inlineStr">
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F21" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L982</t>
-        </is>
-      </c>
-      <c r="G21" s="95" t="inlineStr">
+      <c r="F22" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1043</t>
+        </is>
+      </c>
+      <c r="G22" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A25</t>
         </is>
       </c>
-      <c r="H21" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
-        </is>
-      </c>
-      <c r="I21" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L982 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
-        </is>
-      </c>
-      <c r="J21" s="95" t="inlineStr">
+      <c r="H22" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / exploder</t>
+        </is>
+      </c>
+      <c r="I22" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1043 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J22" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K21" s="95" t="inlineStr">
+      <c r="K22" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L21" s="95" t="inlineStr">
+      <c r="L22" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M21" s="94" t="inlineStr">
+      <c r="M22" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N21" s="94" t="inlineStr">
+      <c r="N22" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-EXPLOSIVE
 VFX-BULLET-EXPLOSIVE-3D</t>
         </is>
       </c>
-      <c r="O21" s="94" t="inlineStr">
+      <c r="O22" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A17
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A31</t>
         </is>
       </c>
-      <c r="P21" s="94" t="inlineStr">
+      <c r="P22" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q21" s="94" t="inlineStr">
+      <c r="Q22" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1" s="46">
-      <c r="A22" s="94" t="inlineStr">
+    <row r="23" ht="76" customHeight="1" s="46">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_homing</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>蜂卵弹模块</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C23" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D22" s="94" t="inlineStr">
+      <c r="D23" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E22" s="94" t="inlineStr">
+      <c r="E23" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F22" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1003</t>
-        </is>
-      </c>
-      <c r="G22" s="95" t="inlineStr">
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1064</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A26</t>
         </is>
       </c>
-      <c r="H22" s="94" t="inlineStr">
+      <c r="H23" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I22" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1003 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
-        </is>
-      </c>
-      <c r="J22" s="95" t="inlineStr">
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1064 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J23" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K22" s="95" t="inlineStr">
+      <c r="K23" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L22" s="95" t="inlineStr">
+      <c r="L23" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M22" s="94" t="inlineStr">
+      <c r="M23" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N22" s="94" t="inlineStr">
+      <c r="N23" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-HOMING
 VFX-BULLET-HOMING-3D</t>
         </is>
       </c>
-      <c r="O22" s="94" t="inlineStr">
+      <c r="O23" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A18
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A32</t>
         </is>
       </c>
-      <c r="P22" s="94" t="inlineStr">
+      <c r="P23" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q22" s="94" t="inlineStr">
+      <c r="Q23" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="76" customHeight="1" s="46">
-      <c r="A23" s="94" t="inlineStr">
+    <row r="24" ht="76" customHeight="1" s="46">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_blackhole</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>黑洞弹模块</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
+      <c r="C24" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D23" s="94" t="inlineStr">
+      <c r="D24" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E23" s="94" t="inlineStr">
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F23" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1024</t>
-        </is>
-      </c>
-      <c r="G23" s="95" t="inlineStr">
+      <c r="F24" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1085</t>
+        </is>
+      </c>
+      <c r="G24" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A23</t>
         </is>
       </c>
-      <c r="H23" s="94" t="inlineStr">
+      <c r="H24" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I23" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1024 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
-        </is>
-      </c>
-      <c r="J23" s="95" t="inlineStr">
+      <c r="I24" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1085 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J24" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K23" s="95" t="inlineStr">
+      <c r="K24" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L23" s="95" t="inlineStr">
+      <c r="L24" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M23" s="94" t="inlineStr">
+      <c r="M24" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N23" s="94" t="inlineStr">
+      <c r="N24" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-BLACKHOLE
 VFX-BULLET-BLACKHOLE-3D</t>
         </is>
       </c>
-      <c r="O23" s="94" t="inlineStr">
+      <c r="O24" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A19
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A33</t>
         </is>
       </c>
-      <c r="P23" s="94" t="inlineStr">
+      <c r="P24" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q23" s="94" t="inlineStr">
+      <c r="Q24" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="76" customHeight="1" s="46">
-      <c r="A24" s="94" t="inlineStr">
+    <row r="25" ht="76" customHeight="1" s="46">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_balloon</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>气球弹模块</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C25" s="94" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D24" s="94" t="inlineStr">
+      <c r="D25" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="E24" s="94" t="inlineStr">
+      <c r="E25" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F24" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1045</t>
-        </is>
-      </c>
-      <c r="G24" s="95" t="inlineStr">
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1106</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A22</t>
         </is>
       </c>
-      <c r="H24" s="94" t="inlineStr">
+      <c r="H25" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I24" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1045 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
-        </is>
-      </c>
-      <c r="J24" s="95" t="inlineStr">
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1106 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+        </is>
+      </c>
+      <c r="J25" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K24" s="95" t="inlineStr">
+      <c r="K25" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
-      <c r="L24" s="95" t="inlineStr">
+      <c r="L25" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M24" s="94" t="inlineStr">
+      <c r="M25" s="94" t="inlineStr">
         <is>
           <t>bullet</t>
         </is>
       </c>
-      <c r="N24" s="94" t="inlineStr">
+      <c r="N25" s="94" t="inlineStr">
         <is>
           <t>WPN-BUL-MOD-BULLET-BALLOON
 VFX-BULLET-BALLOON-3D</t>
         </is>
       </c>
-      <c r="O24" s="94" t="inlineStr">
+      <c r="O25" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A20
 assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A34</t>
         </is>
       </c>
-      <c r="P24" s="94" t="inlineStr">
+      <c r="P25" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q24" s="94" t="inlineStr">
+      <c r="Q25" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="93" customHeight="1" s="46">
-      <c r="A25" s="94" t="inlineStr">
-        <is>
-          <t>attach_triple_muzzle</t>
-        </is>
-      </c>
-      <c r="B25" s="94" t="inlineStr">
-        <is>
-          <t>三叉枪口</t>
-        </is>
-      </c>
-      <c r="C25" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="D25" s="94" t="inlineStr">
-        <is>
-          <t>muzzle</t>
-        </is>
-      </c>
-      <c r="E25" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F25" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1073</t>
-        </is>
-      </c>
-      <c r="G25" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A10</t>
-        </is>
-      </c>
-      <c r="H25" s="94" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
-      <c r="I25" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1073 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J25" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K25" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
-        </is>
-      </c>
-      <c r="L25" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M25" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="N25" s="94" t="inlineStr">
-        <is>
-          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
-        </is>
-      </c>
-      <c r="O25" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A21</t>
-        </is>
-      </c>
-      <c r="P25" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="Q25" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="93" customHeight="1" s="46">
       <c r="A26" s="94" t="inlineStr">
         <is>
+          <t>attach_triple_muzzle</t>
+        </is>
+      </c>
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>三叉枪口</t>
+        </is>
+      </c>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
+        <is>
+          <t>muzzle</t>
+        </is>
+      </c>
+      <c r="E26" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1134</t>
+        </is>
+      </c>
+      <c r="G26" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A10</t>
+        </is>
+      </c>
+      <c r="H26" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I26" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1134 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J26" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K26" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L26" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M26" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N26" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
+        </is>
+      </c>
+      <c r="O26" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A21</t>
+        </is>
+      </c>
+      <c r="P26" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q26" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="93" customHeight="1" s="46">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
           <t>attach_rubber_stock</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>橡皮枪托</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C27" s="94" t="inlineStr">
         <is>
           <t>attachment</t>
         </is>
       </c>
-      <c r="D26" s="94" t="inlineStr">
+      <c r="D27" s="94" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="E26" s="94" t="inlineStr">
+      <c r="E27" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F26" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1098</t>
-        </is>
-      </c>
-      <c r="G26" s="95" t="inlineStr">
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1159</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A8</t>
         </is>
       </c>
-      <c r="H26" s="94" t="inlineStr">
+      <c r="H27" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I26" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1098 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J26" s="95" t="inlineStr">
+      <c r="I27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1159 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J27" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K26" s="95" t="inlineStr">
+      <c r="K27" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
         </is>
       </c>
-      <c r="L26" s="95" t="inlineStr">
+      <c r="L27" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M26" s="94" t="inlineStr">
+      <c r="M27" s="94" t="inlineStr">
         <is>
           <t>attachment</t>
         </is>
       </c>
-      <c r="N26" s="94" t="inlineStr">
+      <c r="N27" s="94" t="inlineStr">
         <is>
           <t>WPN-ATT-ATTACH-RUBBER-STOCK</t>
         </is>
       </c>
-      <c r="O26" s="95" t="inlineStr">
+      <c r="O27" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A22</t>
         </is>
       </c>
-      <c r="P26" s="94" t="inlineStr">
+      <c r="P27" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q26" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="76" customHeight="1" s="46">
-      <c r="A27" s="94" t="inlineStr">
-        <is>
-          <t>attach_scope</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>放大镜瞄具</t>
-        </is>
-      </c>
-      <c r="C27" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="E27" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1129</t>
-        </is>
-      </c>
-      <c r="G27" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A9</t>
-        </is>
-      </c>
-      <c r="H27" s="94" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster</t>
-        </is>
-      </c>
-      <c r="I27" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1129 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
-        </is>
-      </c>
-      <c r="J27" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K27" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
-        </is>
-      </c>
-      <c r="L27" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M27" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="N27" s="94" t="inlineStr">
-        <is>
-          <t>WPN-ATT-ATTACH-SCOPE</t>
-        </is>
-      </c>
-      <c r="O27" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A23</t>
-        </is>
-      </c>
-      <c r="P27" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
       <c r="Q27" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="76" customHeight="1" s="46">
       <c r="A28" s="94" t="inlineStr">
         <is>
-          <t>attach_big_mag</t>
+          <t>attach_scope</t>
         </is>
       </c>
       <c r="B28" s="94" t="inlineStr">
         <is>
-          <t>肉质弹匣</t>
+          <t>放大镜瞄具</t>
         </is>
       </c>
       <c r="C28" s="94" t="inlineStr">
@@ -11067,7 +11572,7 @@
       </c>
       <c r="D28" s="94" t="inlineStr">
         <is>
-          <t>magazine</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="E28" s="94" t="inlineStr">
@@ -11077,22 +11582,22 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1151</t>
+          <t>src/base/ItemRegistry.gd#L1190</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A5</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A9</t>
         </is>
       </c>
       <c r="H28" s="94" t="inlineStr">
         <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
         </is>
       </c>
       <c r="I28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1151 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1190 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J28" s="95" t="inlineStr">
@@ -11117,12 +11622,12 @@
       </c>
       <c r="N28" s="94" t="inlineStr">
         <is>
-          <t>WPN-ATT-ATTACH-BIG-MAG</t>
+          <t>WPN-ATT-ATTACH-SCOPE</t>
         </is>
       </c>
       <c r="O28" s="95" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A24</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A23</t>
         </is>
       </c>
       <c r="P28" s="94" t="inlineStr">
@@ -11132,19 +11637,19 @@
       </c>
       <c r="Q28" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="29" ht="76" customHeight="1" s="46">
       <c r="A29" s="94" t="inlineStr">
         <is>
-          <t>attach_fan</t>
+          <t>attach_big_mag</t>
         </is>
       </c>
       <c r="B29" s="94" t="inlineStr">
         <is>
-          <t>小风扇</t>
+          <t>肉质弹匣</t>
         </is>
       </c>
       <c r="C29" s="94" t="inlineStr">
@@ -11154,7 +11659,7 @@
       </c>
       <c r="D29" s="94" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>magazine</t>
         </is>
       </c>
       <c r="E29" s="94" t="inlineStr">
@@ -11164,12 +11669,12 @@
       </c>
       <c r="F29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1173</t>
+          <t>src/base/ItemRegistry.gd#L1212</t>
         </is>
       </c>
       <c r="G29" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A7</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A5</t>
         </is>
       </c>
       <c r="H29" s="94" t="inlineStr">
@@ -11179,7 +11684,7 @@
       </c>
       <c r="I29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1173 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1212 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J29" s="95" t="inlineStr">
@@ -11204,12 +11709,12 @@
       </c>
       <c r="N29" s="94" t="inlineStr">
         <is>
-          <t>WPN-ATT-ATTACH-FAN</t>
+          <t>WPN-ATT-ATTACH-BIG-MAG</t>
         </is>
       </c>
       <c r="O29" s="95" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A25</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A24</t>
         </is>
       </c>
       <c r="P29" s="94" t="inlineStr">
@@ -11226,85 +11731,172 @@
     <row r="30" ht="76" customHeight="1" s="46">
       <c r="A30" s="94" t="inlineStr">
         <is>
+          <t>attach_fan</t>
+        </is>
+      </c>
+      <c r="B30" s="94" t="inlineStr">
+        <is>
+          <t>小风扇</t>
+        </is>
+      </c>
+      <c r="C30" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="E30" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F30" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1234</t>
+        </is>
+      </c>
+      <c r="G30" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A7</t>
+        </is>
+      </c>
+      <c r="H30" s="94" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I30" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1234 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J30" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K30" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L30" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M30" s="94" t="inlineStr">
+        <is>
+          <t>attachment</t>
+        </is>
+      </c>
+      <c r="N30" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-FAN</t>
+        </is>
+      </c>
+      <c r="O30" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A25</t>
+        </is>
+      </c>
+      <c r="P30" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q30" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="76" customHeight="1" s="46">
+      <c r="A31" s="94" t="inlineStr">
+        <is>
           <t>attach_copy_sticker</t>
         </is>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B31" s="94" t="inlineStr">
         <is>
           <t>复制贴纸</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C31" s="94" t="inlineStr">
         <is>
           <t>attachment</t>
         </is>
       </c>
-      <c r="D30" s="94" t="inlineStr">
+      <c r="D31" s="94" t="inlineStr">
         <is>
           <t>mutator</t>
         </is>
       </c>
-      <c r="E30" s="94" t="inlineStr">
+      <c r="E31" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F30" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1195</t>
-        </is>
-      </c>
-      <c r="G30" s="95" t="inlineStr">
+      <c r="F31" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1256</t>
+        </is>
+      </c>
+      <c r="G31" s="95" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A6</t>
         </is>
       </c>
-      <c r="H30" s="94" t="inlineStr">
+      <c r="H31" s="94" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I30" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1195 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
-        </is>
-      </c>
-      <c r="J30" s="95" t="inlineStr">
+      <c r="I31" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1256 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+        </is>
+      </c>
+      <c r="J31" s="95" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K30" s="95" t="inlineStr">
+      <c r="K31" s="95" t="inlineStr">
         <is>
           <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
         </is>
       </c>
-      <c r="L30" s="95" t="inlineStr">
+      <c r="L31" s="95" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M30" s="94" t="inlineStr">
+      <c r="M31" s="94" t="inlineStr">
         <is>
           <t>attachment</t>
         </is>
       </c>
-      <c r="N30" s="94" t="inlineStr">
+      <c r="N31" s="94" t="inlineStr">
         <is>
           <t>WPN-ATT-ATTACH-COPY-STICKER</t>
         </is>
       </c>
-      <c r="O30" s="95" t="inlineStr">
+      <c r="O31" s="95" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A26</t>
         </is>
       </c>
-      <c r="P30" s="94" t="inlineStr">
+      <c r="P31" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q30" s="94" t="inlineStr">
+      <c r="Q31" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
@@ -11355,48 +11947,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId84"/>
@@ -11451,46 +12043,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId172"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId178"/>
   </tableParts>
 </worksheet>
 </file>
--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-武器'!$A$4:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-武器'!$A$4:$P$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -24,8 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -609,7 +610,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -891,6 +892,9 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1159,8 +1163,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeaponInventoryItems" displayName="WeaponInventoryItems" ref="A4:Q31" headerRowCount="1">
-  <autoFilter ref="A4:Q31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeaponInventoryItems" displayName="WeaponInventoryItems" ref="A4:Q30" headerRowCount="1">
+  <autoFilter ref="A4:Q30"/>
   <tableColumns count="17">
     <tableColumn id="1" name="内容ID"/>
     <tableColumn id="2" name="名称"/>
@@ -3170,7 +3174,7 @@
       <c r="G13" s="57" t="n"/>
       <c r="H13" s="57" t="inlineStr">
         <is>
-          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I13" s="70" t="inlineStr">
@@ -3180,12 +3184,12 @@
       </c>
       <c r="J13" s="57" t="inlineStr">
         <is>
-          <t>武器装配标准子弹模块；继续程序表现</t>
+          <t>地面/图标；preview独立源；mod_bullet_standard</t>
         </is>
       </c>
       <c r="K13" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L13" s="70" t="inlineStr">
@@ -3200,18 +3204,22 @@
       </c>
       <c r="N13" s="57" t="inlineStr">
         <is>
-          <t>0.3760×0.3760×0.9400m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 176三角面（100–200预算）</t>
-        </is>
-      </c>
-      <c r="O13" s="57" t="n"/>
+          <t>Godot XYZ=[0.544772744178772, 0.940000057220459, 0.5501136779785156]m；ground 140三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O13" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P13" s="70" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q13" s="57" t="inlineStr">
         <is>
-          <t>mod_bullet_standard;标准子弹模块</t>
+          <t>标准子弹模块;mod_bullet_standard</t>
         </is>
       </c>
       <c r="R13" s="57">
@@ -3222,7 +3230,11 @@
         <f>IF(COUNTIF($R$6:$R$41,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T13" s="57" t="n"/>
+      <c r="T13" s="57" t="inlineStr">
+        <is>
+          <t>05f1372f6aa8ee1963642597f11a41fed9e19c94e2aab2ccb7e2ce26a5d67a97</t>
+        </is>
+      </c>
       <c r="U13" s="57" t="inlineStr">
         <is>
           <t>Codex</t>
@@ -3233,13 +3245,17 @@
       </c>
       <c r="W13" s="57" t="inlineStr">
         <is>
-          <t>用户提供参考图重建；项目公共色盘</t>
-        </is>
-      </c>
-      <c r="X13" s="72" t="n"/>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X13" s="72" t="inlineStr">
+        <is>
+          <t>标准子弹模块_中文资产管理</t>
+        </is>
+      </c>
       <c r="Y13" s="57" t="inlineStr">
         <is>
-          <t>用户更正：此前蓝金弹头源重新归属通用弹药ITM-CONSUMABLE-ITEM-AMMO-PACK；此资产尚无对应正式模型。</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3267,7 @@
       </c>
       <c r="B14" s="57" t="inlineStr">
         <is>
-          <t>黏黏弹</t>
+          <t>黏黏弹模块</t>
         </is>
       </c>
       <c r="C14" s="57" t="inlineStr">
@@ -3277,22 +3293,22 @@
       <c r="G14" s="57" t="n"/>
       <c r="H14" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I14" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J14" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_sticky</t>
         </is>
       </c>
       <c r="K14" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L14" s="70" t="inlineStr">
@@ -3307,16 +3323,24 @@
       </c>
       <c r="N14" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O14" s="57" t="n"/>
+          <t>Godot XYZ=[0.7113512754440308, 0.9399999380111694, 0.7113512754440308]m；ground 194三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O14" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P14" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q14" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q14" s="57" t="inlineStr">
+        <is>
+          <t>黏黏弹模块;mod_bullet_sticky</t>
+        </is>
+      </c>
       <c r="R14" s="57">
         <f>LOWER(TRIM(C14)&amp;"|"&amp;TRIM(D14)&amp;"|"&amp;TRIM(E14)&amp;"|"&amp;TRIM(F14)&amp;"|"&amp;TRIM(H14)&amp;"|"&amp;TRIM(I14))</f>
         <v/>
@@ -3325,29 +3349,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T14" s="57" t="n"/>
+      <c r="T14" s="57" t="inlineStr">
+        <is>
+          <t>8804c79a0e38ef5644b6e5e13d159e2d850d2a692da5435cc2cafb8b30705590</t>
+        </is>
+      </c>
       <c r="U14" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V14" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W14" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X14" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>黏黏弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y14" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3386,7 @@
       </c>
       <c r="B15" s="57" t="inlineStr">
         <is>
-          <t>回旋镖弹</t>
+          <t>回旋镖弹模块</t>
         </is>
       </c>
       <c r="C15" s="57" t="inlineStr">
@@ -3385,22 +3412,22 @@
       <c r="G15" s="57" t="n"/>
       <c r="H15" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I15" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J15" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_bounce</t>
         </is>
       </c>
       <c r="K15" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L15" s="70" t="inlineStr">
@@ -3415,16 +3442,24 @@
       </c>
       <c r="N15" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O15" s="57" t="n"/>
+          <t>Godot XYZ=[0.8982222080230713, 0.9399999976158142, 0.5222222208976746]m；ground 124三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O15" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P15" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q15" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q15" s="57" t="inlineStr">
+        <is>
+          <t>回旋镖弹模块;mod_bullet_bounce</t>
+        </is>
+      </c>
       <c r="R15" s="57">
         <f>LOWER(TRIM(C15)&amp;"|"&amp;TRIM(D15)&amp;"|"&amp;TRIM(E15)&amp;"|"&amp;TRIM(F15)&amp;"|"&amp;TRIM(H15)&amp;"|"&amp;TRIM(I15))</f>
         <v/>
@@ -3433,29 +3468,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T15" s="57" t="n"/>
+      <c r="T15" s="57" t="inlineStr">
+        <is>
+          <t>4c9b4298a79d572beaac51ab6132b09c3ceb9b641f0f0fa36623bfb2cd44ba5c</t>
+        </is>
+      </c>
       <c r="U15" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V15" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W15" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X15" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>回旋镖弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y15" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3505,7 @@
       </c>
       <c r="B16" s="57" t="inlineStr">
         <is>
-          <t>穿甲弹</t>
+          <t>穿甲弹模块</t>
         </is>
       </c>
       <c r="C16" s="57" t="inlineStr">
@@ -3493,22 +3531,22 @@
       <c r="G16" s="57" t="n"/>
       <c r="H16" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I16" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J16" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_piercing</t>
         </is>
       </c>
       <c r="K16" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L16" s="70" t="inlineStr">
@@ -3523,16 +3561,24 @@
       </c>
       <c r="N16" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O16" s="57" t="n"/>
+          <t>Godot XYZ=[0.5293203592300415, 0.9399999976158142, 0.4563106894493103]m；ground 144三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O16" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P16" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q16" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q16" s="57" t="inlineStr">
+        <is>
+          <t>穿甲弹模块;mod_bullet_piercing</t>
+        </is>
+      </c>
       <c r="R16" s="57">
         <f>LOWER(TRIM(C16)&amp;"|"&amp;TRIM(D16)&amp;"|"&amp;TRIM(E16)&amp;"|"&amp;TRIM(F16)&amp;"|"&amp;TRIM(H16)&amp;"|"&amp;TRIM(I16))</f>
         <v/>
@@ -3541,29 +3587,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T16" s="57" t="n"/>
+      <c r="T16" s="57" t="inlineStr">
+        <is>
+          <t>442eb9c2265e1a2b1e14000cbe093c6643d7b9d5028481d2617ef4e17ff1622c</t>
+        </is>
+      </c>
       <c r="U16" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V16" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W16" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X16" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>穿甲弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y16" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3624,7 @@
       </c>
       <c r="B17" s="57" t="inlineStr">
         <is>
-          <t>爆炸弹</t>
+          <t>爆炸弹模块</t>
         </is>
       </c>
       <c r="C17" s="57" t="inlineStr">
@@ -3601,22 +3650,22 @@
       <c r="G17" s="57" t="n"/>
       <c r="H17" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I17" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J17" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_explosive</t>
         </is>
       </c>
       <c r="K17" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L17" s="70" t="inlineStr">
@@ -3631,16 +3680,24 @@
       </c>
       <c r="N17" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O17" s="57" t="n"/>
+          <t>Godot XYZ=[0.6087619662284851, 0.940000057220459, 0.622190535068512]m；ground 180三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O17" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P17" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q17" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q17" s="57" t="inlineStr">
+        <is>
+          <t>爆炸弹模块;mod_bullet_explosive</t>
+        </is>
+      </c>
       <c r="R17" s="57">
         <f>LOWER(TRIM(C17)&amp;"|"&amp;TRIM(D17)&amp;"|"&amp;TRIM(E17)&amp;"|"&amp;TRIM(F17)&amp;"|"&amp;TRIM(H17)&amp;"|"&amp;TRIM(I17))</f>
         <v/>
@@ -3649,29 +3706,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T17" s="57" t="n"/>
+      <c r="T17" s="57" t="inlineStr">
+        <is>
+          <t>1d05f672d11fd878b108e941cde5530a4a13705402bc493dd84068e444ccf2b9</t>
+        </is>
+      </c>
       <c r="U17" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V17" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W17" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X17" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>爆炸弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y17" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3743,7 @@
       </c>
       <c r="B18" s="57" t="inlineStr">
         <is>
-          <t>蜂卵弹</t>
+          <t>蜂卵弹模块</t>
         </is>
       </c>
       <c r="C18" s="57" t="inlineStr">
@@ -3709,22 +3769,22 @@
       <c r="G18" s="57" t="n"/>
       <c r="H18" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I18" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J18" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_homing</t>
         </is>
       </c>
       <c r="K18" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L18" s="70" t="inlineStr">
@@ -3739,16 +3799,24 @@
       </c>
       <c r="N18" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O18" s="57" t="n"/>
+          <t>Godot XYZ=[0.7946391701698303, 0.9399999976158142, 0.5930721759796143]m；ground 194三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O18" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P18" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q18" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q18" s="57" t="inlineStr">
+        <is>
+          <t>蜂卵弹模块;mod_bullet_homing</t>
+        </is>
+      </c>
       <c r="R18" s="57">
         <f>LOWER(TRIM(C18)&amp;"|"&amp;TRIM(D18)&amp;"|"&amp;TRIM(E18)&amp;"|"&amp;TRIM(F18)&amp;"|"&amp;TRIM(H18)&amp;"|"&amp;TRIM(I18))</f>
         <v/>
@@ -3757,29 +3825,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T18" s="57" t="n"/>
+      <c r="T18" s="57" t="inlineStr">
+        <is>
+          <t>e84776963544adb2baa7da0b45f65d85f31925b3801ba230c89c3b4eebf29303</t>
+        </is>
+      </c>
       <c r="U18" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V18" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W18" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X18" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>蜂卵弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y18" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3862,7 @@
       </c>
       <c r="B19" s="57" t="inlineStr">
         <is>
-          <t>黑洞弹</t>
+          <t>黑洞弹模块</t>
         </is>
       </c>
       <c r="C19" s="57" t="inlineStr">
@@ -3817,22 +3888,22 @@
       <c r="G19" s="57" t="n"/>
       <c r="H19" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I19" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J19" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_blackhole</t>
         </is>
       </c>
       <c r="K19" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L19" s="70" t="inlineStr">
@@ -3847,16 +3918,24 @@
       </c>
       <c r="N19" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O19" s="57" t="n"/>
+          <t>Godot XYZ=[0.7773077487945557, 0.9399999976158142, 0.5242307782173157]m；ground 194三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O19" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P19" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q19" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q19" s="57" t="inlineStr">
+        <is>
+          <t>黑洞弹模块;mod_bullet_blackhole</t>
+        </is>
+      </c>
       <c r="R19" s="57">
         <f>LOWER(TRIM(C19)&amp;"|"&amp;TRIM(D19)&amp;"|"&amp;TRIM(E19)&amp;"|"&amp;TRIM(F19)&amp;"|"&amp;TRIM(H19)&amp;"|"&amp;TRIM(I19))</f>
         <v/>
@@ -3865,29 +3944,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T19" s="57" t="n"/>
+      <c r="T19" s="57" t="inlineStr">
+        <is>
+          <t>142fa92b45d252d6738fda877f724672eebc6d9053281b75bea15aebcd1c2b07</t>
+        </is>
+      </c>
       <c r="U19" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V19" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W19" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X19" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>黑洞弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y19" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3981,7 @@
       </c>
       <c r="B20" s="57" t="inlineStr">
         <is>
-          <t>气球弹</t>
+          <t>气球弹模块</t>
         </is>
       </c>
       <c r="C20" s="57" t="inlineStr">
@@ -3925,22 +4007,22 @@
       <c r="G20" s="57" t="n"/>
       <c r="H20" s="57" t="inlineStr">
         <is>
-          <t>顶视/方向无关</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I20" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J20" s="57" t="inlineStr">
         <is>
-          <t>弹体/VFX/UI 图标</t>
+          <t>地面/图标；preview独立源；mod_bullet_balloon</t>
         </is>
       </c>
       <c r="K20" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L20" s="70" t="inlineStr">
@@ -3955,16 +4037,24 @@
       </c>
       <c r="N20" s="57" t="inlineStr">
         <is>
-          <t>建议 12×12 px</t>
-        </is>
-      </c>
-      <c r="O20" s="57" t="n"/>
+          <t>Godot XYZ=[0.6207547187805176, 0.9399999976158142, 0.6207547187805176]m；ground 168三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O20" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P20" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q20" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q20" s="57" t="inlineStr">
+        <is>
+          <t>气球弹模块;mod_bullet_balloon</t>
+        </is>
+      </c>
       <c r="R20" s="57">
         <f>LOWER(TRIM(C20)&amp;"|"&amp;TRIM(D20)&amp;"|"&amp;TRIM(E20)&amp;"|"&amp;TRIM(F20)&amp;"|"&amp;TRIM(H20)&amp;"|"&amp;TRIM(I20))</f>
         <v/>
@@ -3973,29 +4063,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T20" s="57" t="n"/>
+      <c r="T20" s="57" t="inlineStr">
+        <is>
+          <t>e9a0d40db8d7783b720e26b554bd67e1b24d29c1a5200d3ce38b0bcdd98267d4</t>
+        </is>
+      </c>
       <c r="U20" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V20" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W20" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X20" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>气球弹模块_中文资产管理</t>
         </is>
       </c>
       <c r="Y20" s="57" t="inlineStr">
         <is>
-          <t>优先复用颜色和弹道特效，不为每把枪重复制作
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4586,7 @@
       </c>
       <c r="D25" s="70" t="inlineStr">
         <is>
-          <t>attachment</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E25" s="70" t="inlineStr">
@@ -4509,27 +4602,27 @@
       <c r="G25" s="57" t="n"/>
       <c r="H25" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I25" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J25" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>地面/图标；preview独立源；attach_fan</t>
         </is>
       </c>
       <c r="K25" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L25" s="70" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M25" s="70" t="inlineStr">
@@ -4539,16 +4632,24 @@
       </c>
       <c r="N25" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O25" s="57" t="n"/>
+          <t>Godot XYZ=[0.4676923155784607, 0.6399999856948853, 0.20615386962890625]m；ground 144三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O25" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P25" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q25" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q25" s="57" t="inlineStr">
+        <is>
+          <t>小风扇;attach_fan</t>
+        </is>
+      </c>
       <c r="R25" s="57">
         <f>LOWER(TRIM(C25)&amp;"|"&amp;TRIM(D25)&amp;"|"&amp;TRIM(E25)&amp;"|"&amp;TRIM(F25)&amp;"|"&amp;TRIM(H25)&amp;"|"&amp;TRIM(I25))</f>
         <v/>
@@ -4557,29 +4658,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T25" s="57" t="n"/>
+      <c r="T25" s="57" t="inlineStr">
+        <is>
+          <t>53bc8cda8d205eb3e02eaf1544c008a39bba81ba327b2c49cbc913fd9640454b</t>
+        </is>
+      </c>
       <c r="U25" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V25" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W25" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X25" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>小风扇_中文资产管理</t>
         </is>
       </c>
       <c r="Y25" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_source_v001.blend；地面源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4705,7 @@
       </c>
       <c r="D26" s="70" t="inlineStr">
         <is>
-          <t>attachment</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E26" s="70" t="inlineStr">
@@ -4617,27 +4721,27 @@
       <c r="G26" s="57" t="n"/>
       <c r="H26" s="57" t="inlineStr">
         <is>
-          <t>侧面朝右</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I26" s="70" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J26" s="57" t="inlineStr">
         <is>
-          <t>装配树/枪身/UI 图标</t>
+          <t>地面/图标；preview独立源；attach_copy_sticker</t>
         </is>
       </c>
       <c r="K26" s="57" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L26" s="70" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M26" s="70" t="inlineStr">
@@ -4647,16 +4751,24 @@
       </c>
       <c r="N26" s="57" t="inlineStr">
         <is>
-          <t>建议 12–24 px</t>
-        </is>
-      </c>
-      <c r="O26" s="57" t="n"/>
+          <t>Godot XYZ=[0.7014707326889038, 0.6399999260902405, 0.25417670607566833]m；ground 150三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O26" s="57" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P26" s="70" t="inlineStr">
         <is>
-          <t>src/base/BlueprintRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q26" s="57" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q26" s="57" t="inlineStr">
+        <is>
+          <t>复制贴纸;attach_copy_sticker</t>
+        </is>
+      </c>
       <c r="R26" s="57">
         <f>LOWER(TRIM(C26)&amp;"|"&amp;TRIM(D26)&amp;"|"&amp;TRIM(E26)&amp;"|"&amp;TRIM(F26)&amp;"|"&amp;TRIM(H26)&amp;"|"&amp;TRIM(I26))</f>
         <v/>
@@ -4665,29 +4777,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T26" s="57" t="n"/>
+      <c r="T26" s="57" t="inlineStr">
+        <is>
+          <t>f81d20391e0f0a608a426177d73fd91f0373137b12a7b4a04b7460992b21f93a</t>
+        </is>
+      </c>
       <c r="U26" s="57" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V26" s="71" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W26" s="57" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X26" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>复制贴纸_中文资产管理</t>
         </is>
       </c>
       <c r="Y26" s="57" t="inlineStr">
         <is>
-          <t>以挂点部件制作，不烘焙进整枪
-2026-08-30 AST-01规范化（原大类：枪械）</t>
+          <t>高精度源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_source_v001.blend；地面源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4934,7 @@
       </c>
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>巨型工业断刃程序原型</t>
+          <t>巨型工业断刃</t>
         </is>
       </c>
       <c r="C28" s="49" t="inlineStr">
@@ -4845,27 +4960,27 @@
       <c r="G28" s="73" t="n"/>
       <c r="H28" s="49" t="inlineStr">
         <is>
-          <t>俯视3D</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I28" s="73" t="inlineStr">
         <is>
-          <t>default / three_step_combo</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J28" s="49" t="inlineStr">
         <is>
-          <t>手持/背负/地面/背包图标/表现页</t>
+          <t>地面/图标；preview独立源；weapon_greatblade</t>
         </is>
       </c>
       <c r="K28" s="49" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L28" s="73" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M28" s="73" t="inlineStr">
@@ -4875,22 +4990,22 @@
       </c>
       <c r="N28" s="49" t="inlineStr">
         <is>
-          <t>程序Mesh；0.82×0.30×2.42m；无碰撞</t>
+          <t>Godot XYZ=[1.1473641395568848, 0.407951682806015, 2.9194042682647705]m；ground 168三角；公共色盘；原点existing_grip</t>
         </is>
       </c>
       <c r="O28" s="73" t="inlineStr">
         <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_greatblade_root_top3d_v001.tscn</t>
+          <t>assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P28" s="73" t="inlineStr">
         <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q28" s="49" t="inlineStr">
         <is>
-          <t>近战;大型武器;工业断刃;三段连击;greatblade;melee</t>
+          <t>巨型工业断刃;weapon_greatblade</t>
         </is>
       </c>
       <c r="R28" s="73">
@@ -4901,28 +5016,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T28" s="73" t="n"/>
+      <c r="T28" s="73" t="inlineStr">
+        <is>
+          <t>850065e0aec45baf4979bd3146e068fe7ee1d1f6f5cb24d4cc79f5ceae857093</t>
+        </is>
+      </c>
       <c r="U28" s="73" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>
       </c>
       <c r="V28" s="74" t="n">
-        <v>46244</v>
+        <v>46309</v>
       </c>
       <c r="W28" s="49" t="inlineStr">
         <is>
-          <t>原创程序原型</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X28" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>巨型工业断刃_中文资产管理</t>
         </is>
       </c>
       <c r="Y28" s="49" t="inlineStr">
         <is>
-          <t>总长2.42m；双手重型持握；四态动作子状态机；三段池化弧光/命中爆点与专属挥砍/冲击音频已接入；最终美术替换保留握柄原点/local -Z与稳定ID。</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
         </is>
       </c>
     </row>
@@ -4934,7 +5053,7 @@
       </c>
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t>攻城裂甲斧程序原型</t>
+          <t>攻城裂甲斧</t>
         </is>
       </c>
       <c r="C29" s="49" t="inlineStr">
@@ -4960,27 +5079,27 @@
       <c r="G29" s="73" t="n"/>
       <c r="H29" s="49" t="inlineStr">
         <is>
-          <t>俯视3D</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I29" s="73" t="inlineStr">
         <is>
-          <t>default / three_step_combo</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J29" s="49" t="inlineStr">
         <is>
-          <t>手持/背负/地面/背包图标/表现页</t>
+          <t>地面/图标；preview独立源；weapon_waraxe</t>
         </is>
       </c>
       <c r="K29" s="49" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L29" s="73" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M29" s="73" t="inlineStr">
@@ -4990,22 +5109,22 @@
       </c>
       <c r="N29" s="49" t="inlineStr">
         <is>
-          <t>程序Mesh；1.18×0.34×2.62m；无碰撞</t>
+          <t>Godot XYZ=[1.6731491088867188, 0.45187240839004517, 2.8700003623962402]m；ground 152三角；公共色盘；原点existing_grip</t>
         </is>
       </c>
       <c r="O29" s="73" t="inlineStr">
         <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_waraxe_root_top3d_v001.tscn</t>
+          <t>assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P29" s="73" t="inlineStr">
         <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q29" s="49" t="inlineStr">
         <is>
-          <t>近战;大型武器;攻城斧;三段连击;waraxe;melee</t>
+          <t>攻城裂甲斧;weapon_waraxe</t>
         </is>
       </c>
       <c r="R29" s="73">
@@ -5016,28 +5135,32 @@
         <f>IF(COUNTIF($R$6:$R$41,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T29" s="73" t="n"/>
+      <c r="T29" s="73" t="inlineStr">
+        <is>
+          <t>baa91469acf229a4a604fba6d8d4f0c98e17191503ddcd671196792d3d7535bc</t>
+        </is>
+      </c>
       <c r="U29" s="73" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>
       </c>
       <c r="V29" s="74" t="n">
-        <v>46244</v>
+        <v>46309</v>
       </c>
       <c r="W29" s="49" t="inlineStr">
         <is>
-          <t>原创程序原型</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X29" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>攻城裂甲斧_中文资产管理</t>
         </is>
       </c>
       <c r="Y29" s="49" t="inlineStr">
         <is>
-          <t>总长2.62m；高伤高击退；四态动作子状态机；第三段最大弧光并降低音高/提高冲击响度；最终美术替换保留握柄原点/local -Z与稳定ID。</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5172,7 @@
       </c>
       <c r="B30" s="49" t="inlineStr">
         <is>
-          <t>废土棒球棍程序原型</t>
+          <t>废土棒球棍</t>
         </is>
       </c>
       <c r="C30" s="49" t="inlineStr">
@@ -5075,27 +5198,27 @@
       <c r="G30" s="73" t="n"/>
       <c r="H30" s="49" t="inlineStr">
         <is>
-          <t>俯视3D</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I30" s="73" t="inlineStr">
         <is>
-          <t>default / three_step_combo</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J30" s="49" t="inlineStr">
         <is>
-          <t>手持/背负/地面/背包图标/表现页/基地贩卖机</t>
+          <t>地面/图标；preview独立源；weapon_baseball_bat</t>
         </is>
       </c>
       <c r="K30" s="49" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L30" s="73" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M30" s="73" t="inlineStr">
@@ -5105,22 +5228,22 @@
       </c>
       <c r="N30" s="49" t="inlineStr">
         <is>
-          <t>程序Mesh；0.28×0.28×1.48m；无碰撞</t>
+          <t>Godot XYZ=[0.46580973267555237, 0.46580973267555237, 1.7349998950958252]m；ground 194三角；公共色盘；原点existing_grip</t>
         </is>
       </c>
       <c r="O30" s="73" t="inlineStr">
         <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_baseball_bat_root_top3d_v001.tscn</t>
+          <t>assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P30" s="73" t="inlineStr">
         <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd; tests/verification/verify_weapon_attachment_inventory_flow.gd</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q30" s="49" t="inlineStr">
         <is>
-          <t>近战;初级武器;棒球棍;三段连击;baseball_bat;melee;基地贩卖机</t>
+          <t>废土棒球棍;weapon_baseball_bat</t>
         </is>
       </c>
       <c r="R30" s="73">
@@ -5133,7 +5256,7 @@
       </c>
       <c r="T30" s="73" t="inlineStr">
         <is>
-          <t>700ecf26ca26d653967db40dbe48f8572387ae63b43a1428aa54721c25ca7b0a</t>
+          <t>de0fc3fad9fb694a52ad3304dde8c9e10275c7626e4d675caa584df1524637e8</t>
         </is>
       </c>
       <c r="U30" s="73" t="inlineStr">
@@ -5141,22 +5264,22 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V30" s="73" t="n">
-        <v>46244</v>
+      <c r="V30" s="97" t="n">
+        <v>46309</v>
       </c>
       <c r="W30" s="49" t="inlineStr">
         <is>
-          <t>原创程序原型</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X30" s="72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>废土棒球棍_中文资产管理</t>
         </is>
       </c>
       <c r="Y30" s="49" t="inlineStr">
         <is>
-          <t>基地45魂初级近战；三段快速挥击、第三段强化击退；复用近战四态、弧光/命中VFX和版本化音频。最终美术替换须保留握柄原点/local -Z与稳定ID。</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="45" min="1" max="1"/>
@@ -6870,24 +6993,32 @@
       </c>
       <c r="B5" s="82" t="inlineStr">
         <is>
-          <t>废土棒球棍程序原型</t>
+          <t>废土棒球棍 / ground</t>
         </is>
       </c>
       <c r="C5" s="83" t="inlineStr">
         <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_baseball_bat_root_top3d_v001.tscn</t>
-        </is>
-      </c>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="83" t="n"/>
+          <t>assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_baseball_bat/components/wpn_melee_baseball_bat_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E5" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_ground_source_v001.blend</t>
+        </is>
+      </c>
       <c r="F5" s="82" t="inlineStr">
         <is>
-          <t>武器3D表现Prefab；由武器系统装配</t>
+          <t>纯视觉；游戏规则由原系统持有</t>
         </is>
       </c>
       <c r="G5" s="83" t="inlineStr">
         <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
         </is>
       </c>
       <c r="H5" s="82" t="inlineStr">
@@ -6897,190 +7028,206 @@
       </c>
       <c r="I5" s="82" t="inlineStr">
         <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J5" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K5" s="82" t="inlineStr">
+        <is>
+          <t>[0.46580973267555237, 0.46580973267555237, 1.7349998950958252]；194三角</t>
+        </is>
+      </c>
+      <c r="L5" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M5" s="82" t="inlineStr">
+        <is>
+          <t>weapon_baseball_bat</t>
+        </is>
+      </c>
+      <c r="N5" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O5" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P5" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1" s="46">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-GREATBLADE</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
+        <is>
+          <t>巨型工业断刃 / ground</t>
+        </is>
+      </c>
+      <c r="C6" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D6" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_greatblade/components/wpn_melee_greatblade_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E6" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F6" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G6" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H6" s="82" t="inlineStr">
+        <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J5" s="82" t="inlineStr">
+      <c r="I6" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J6" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K6" s="82" t="inlineStr">
+        <is>
+          <t>[1.1473641395568848, 0.407951682806015, 2.9194042682647705]；168三角</t>
+        </is>
+      </c>
+      <c r="L6" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M6" s="82" t="inlineStr">
+        <is>
+          <t>weapon_greatblade</t>
+        </is>
+      </c>
+      <c r="N6" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O6" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P6" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1" s="46">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-WARAXE</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
+        <is>
+          <t>攻城裂甲斧 / ground</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D7" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_waraxe/components/wpn_melee_waraxe_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E7" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F7" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G7" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H7" s="82" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K5" s="82" t="inlineStr">
-        <is>
-          <t>程序Mesh；0.28×0.28×1.48m；无碰撞</t>
-        </is>
-      </c>
-      <c r="L5" s="82" t="inlineStr">
-        <is>
-          <t>未声明</t>
-        </is>
-      </c>
-      <c r="M5" s="82" t="inlineStr">
-        <is>
-          <t>手持/背负/地面/背包图标/表现页/基地贩卖机</t>
-        </is>
-      </c>
-      <c r="N5" s="82" t="inlineStr">
-        <is>
-          <t>程序占位</t>
-        </is>
-      </c>
-      <c r="O5" s="83" t="inlineStr">
+      <c r="I7" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J7" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K7" s="82" t="inlineStr">
+        <is>
+          <t>[1.6731491088867188, 0.45187240839004517, 2.8700003623962402]；152三角</t>
+        </is>
+      </c>
+      <c r="L7" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M7" s="82" t="inlineStr">
+        <is>
+          <t>weapon_waraxe</t>
+        </is>
+      </c>
+      <c r="N7" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O7" s="83" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="P5" s="84" t="inlineStr">
-        <is>
-          <t>根节点=BaseballBatRootTop3D(Node3D)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1" s="46">
-      <c r="A6" s="85" t="inlineStr">
-        <is>
-          <t>WPN-MELEE-BP-GREATBLADE</t>
-        </is>
-      </c>
-      <c r="B6" s="86" t="inlineStr">
-        <is>
-          <t>巨型工业断刃程序原型</t>
-        </is>
-      </c>
-      <c r="C6" s="87" t="inlineStr">
-        <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_greatblade_root_top3d_v001.tscn</t>
-        </is>
-      </c>
-      <c r="D6" s="87" t="n"/>
-      <c r="E6" s="87" t="n"/>
-      <c r="F6" s="86" t="inlineStr">
-        <is>
-          <t>武器3D表现Prefab；由武器系统装配</t>
-        </is>
-      </c>
-      <c r="G6" s="87" t="inlineStr">
-        <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd</t>
-        </is>
-      </c>
-      <c r="H6" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="I6" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J6" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K6" s="86" t="inlineStr">
-        <is>
-          <t>程序Mesh；0.82×0.30×2.42m；无碰撞</t>
-        </is>
-      </c>
-      <c r="L6" s="86" t="inlineStr">
-        <is>
-          <t>未声明</t>
-        </is>
-      </c>
-      <c r="M6" s="86" t="inlineStr">
-        <is>
-          <t>手持/背负/地面/背包图标/表现页</t>
-        </is>
-      </c>
-      <c r="N6" s="86" t="inlineStr">
-        <is>
-          <t>程序占位</t>
-        </is>
-      </c>
-      <c r="O6" s="87" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="P6" s="88" t="inlineStr">
-        <is>
-          <t>根节点=GreatbladeVisual3D(Node3D)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="66" customHeight="1" s="46">
-      <c r="A7" s="85" t="inlineStr">
-        <is>
-          <t>WPN-MELEE-BP-WARAXE</t>
-        </is>
-      </c>
-      <c r="B7" s="86" t="inlineStr">
-        <is>
-          <t>攻城裂甲斧程序原型</t>
-        </is>
-      </c>
-      <c r="C7" s="87" t="inlineStr">
-        <is>
-          <t>assets/art/weapons/melee_3d/wpn_melee_waraxe_root_top3d_v001.tscn</t>
-        </is>
-      </c>
-      <c r="D7" s="87" t="n"/>
-      <c r="E7" s="87" t="n"/>
-      <c r="F7" s="86" t="inlineStr">
-        <is>
-          <t>武器3D表现Prefab；由武器系统装配</t>
-        </is>
-      </c>
-      <c r="G7" s="87" t="inlineStr">
-        <is>
-          <t>src/combat3d/MeleeWeaponVisual3D.gd</t>
-        </is>
-      </c>
-      <c r="H7" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="I7" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J7" s="86" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K7" s="86" t="inlineStr">
-        <is>
-          <t>程序Mesh；1.18×0.34×2.62m；无碰撞</t>
-        </is>
-      </c>
-      <c r="L7" s="86" t="inlineStr">
-        <is>
-          <t>未声明</t>
-        </is>
-      </c>
-      <c r="M7" s="86" t="inlineStr">
-        <is>
-          <t>手持/背负/地面/背包图标/表现页</t>
-        </is>
-      </c>
-      <c r="N7" s="86" t="inlineStr">
-        <is>
-          <t>程序占位</t>
-        </is>
-      </c>
-      <c r="O7" s="87" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="P7" s="88" t="inlineStr">
-        <is>
-          <t>根节点=WaraxeVisual3D(Node3D)</t>
+      <c r="P7" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
         </is>
       </c>
     </row>
@@ -8962,8 +9109,1894 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STANDARD</t>
+        </is>
+      </c>
+      <c r="B31" s="82" t="inlineStr">
+        <is>
+          <t>标准子弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C31" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D31" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_standard/components/wpn_bullet_module_standard_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E31" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F31" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G31" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H31" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I31" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J31" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K31" s="82" t="inlineStr">
+        <is>
+          <t>[0.544772744178772, 0.940000057220459, 0.5501136779785156]；1132三角</t>
+        </is>
+      </c>
+      <c r="L31" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M31" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_standard</t>
+        </is>
+      </c>
+      <c r="N31" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O31" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P31" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STANDARD</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="inlineStr">
+        <is>
+          <t>标准子弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C32" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D32" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_standard/components/wpn_bullet_module_standard_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E32" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F32" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G32" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H32" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I32" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J32" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K32" s="82" t="inlineStr">
+        <is>
+          <t>[0.544772744178772, 0.940000057220459, 0.5501136779785156]；140三角</t>
+        </is>
+      </c>
+      <c r="L32" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M32" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_standard</t>
+        </is>
+      </c>
+      <c r="N32" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O32" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P32" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STICKY</t>
+        </is>
+      </c>
+      <c r="B33" s="82" t="inlineStr">
+        <is>
+          <t>黏黏弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C33" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D33" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_sticky/components/wpn_bullet_module_sticky_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E33" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F33" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G33" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H33" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I33" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J33" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K33" s="82" t="inlineStr">
+        <is>
+          <t>[0.7113512754440308, 0.9399999380111694, 0.7113512754440308]；2280三角</t>
+        </is>
+      </c>
+      <c r="L33" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M33" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_sticky</t>
+        </is>
+      </c>
+      <c r="N33" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O33" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P33" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-STICKY</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="inlineStr">
+        <is>
+          <t>黏黏弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C34" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D34" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_sticky/components/wpn_bullet_module_sticky_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E34" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F34" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G34" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H34" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I34" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J34" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K34" s="82" t="inlineStr">
+        <is>
+          <t>[0.7113512754440308, 0.9399999380111694, 0.7113512754440308]；194三角</t>
+        </is>
+      </c>
+      <c r="L34" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M34" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_sticky</t>
+        </is>
+      </c>
+      <c r="N34" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O34" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P34" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BOUNCE</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="inlineStr">
+        <is>
+          <t>回旋镖弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C35" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D35" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_bounce/components/wpn_bullet_module_bounce_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E35" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F35" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G35" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H35" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I35" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J35" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K35" s="82" t="inlineStr">
+        <is>
+          <t>[0.8982222080230713, 0.9399999976158142, 0.5222222208976746]；1272三角</t>
+        </is>
+      </c>
+      <c r="L35" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M35" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_bounce</t>
+        </is>
+      </c>
+      <c r="N35" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O35" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P35" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BOUNCE</t>
+        </is>
+      </c>
+      <c r="B36" s="82" t="inlineStr">
+        <is>
+          <t>回旋镖弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C36" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D36" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_bounce/components/wpn_bullet_module_bounce_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E36" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F36" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G36" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H36" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I36" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J36" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K36" s="82" t="inlineStr">
+        <is>
+          <t>[0.8982222080230713, 0.9399999976158142, 0.5222222208976746]；124三角</t>
+        </is>
+      </c>
+      <c r="L36" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M36" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_bounce</t>
+        </is>
+      </c>
+      <c r="N36" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O36" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P36" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-PIERCING</t>
+        </is>
+      </c>
+      <c r="B37" s="82" t="inlineStr">
+        <is>
+          <t>穿甲弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C37" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D37" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_piercing/components/wpn_bullet_module_piercing_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E37" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F37" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G37" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H37" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I37" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J37" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K37" s="82" t="inlineStr">
+        <is>
+          <t>[0.5293203592300415, 0.9399999976158142, 0.4563106894493103]；1224三角</t>
+        </is>
+      </c>
+      <c r="L37" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M37" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_piercing</t>
+        </is>
+      </c>
+      <c r="N37" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O37" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P37" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-PIERCING</t>
+        </is>
+      </c>
+      <c r="B38" s="82" t="inlineStr">
+        <is>
+          <t>穿甲弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C38" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D38" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_piercing/components/wpn_bullet_module_piercing_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E38" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F38" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G38" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H38" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I38" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J38" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K38" s="82" t="inlineStr">
+        <is>
+          <t>[0.5293203592300415, 0.9399999976158142, 0.4563106894493103]；144三角</t>
+        </is>
+      </c>
+      <c r="L38" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M38" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_piercing</t>
+        </is>
+      </c>
+      <c r="N38" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O38" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P38" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-EXPLOSIVE</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="inlineStr">
+        <is>
+          <t>爆炸弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D39" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_explosive/components/wpn_bullet_module_explosive_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E39" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F39" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G39" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H39" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I39" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J39" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K39" s="82" t="inlineStr">
+        <is>
+          <t>[0.6087619662284851, 0.940000057220459, 0.622190535068512]；1604三角</t>
+        </is>
+      </c>
+      <c r="L39" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M39" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_explosive</t>
+        </is>
+      </c>
+      <c r="N39" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O39" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P39" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-EXPLOSIVE</t>
+        </is>
+      </c>
+      <c r="B40" s="82" t="inlineStr">
+        <is>
+          <t>爆炸弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C40" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D40" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_explosive/components/wpn_bullet_module_explosive_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E40" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F40" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G40" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H40" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I40" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J40" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K40" s="82" t="inlineStr">
+        <is>
+          <t>[0.6087619662284851, 0.940000057220459, 0.622190535068512]；180三角</t>
+        </is>
+      </c>
+      <c r="L40" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M40" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_explosive</t>
+        </is>
+      </c>
+      <c r="N40" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O40" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P40" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-HOMING</t>
+        </is>
+      </c>
+      <c r="B41" s="82" t="inlineStr">
+        <is>
+          <t>蜂卵弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C41" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D41" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_homing/components/wpn_bullet_module_homing_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E41" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F41" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G41" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H41" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I41" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J41" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K41" s="82" t="inlineStr">
+        <is>
+          <t>[0.7946391701698303, 0.9399999976158142, 0.5930721759796143]；1992三角</t>
+        </is>
+      </c>
+      <c r="L41" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M41" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_homing</t>
+        </is>
+      </c>
+      <c r="N41" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O41" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P41" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-HOMING</t>
+        </is>
+      </c>
+      <c r="B42" s="82" t="inlineStr">
+        <is>
+          <t>蜂卵弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C42" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D42" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_homing/components/wpn_bullet_module_homing_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E42" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F42" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G42" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H42" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I42" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J42" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K42" s="82" t="inlineStr">
+        <is>
+          <t>[0.7946391701698303, 0.9399999976158142, 0.5930721759796143]；194三角</t>
+        </is>
+      </c>
+      <c r="L42" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M42" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_homing</t>
+        </is>
+      </c>
+      <c r="N42" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O42" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P42" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BLACKHOLE</t>
+        </is>
+      </c>
+      <c r="B43" s="82" t="inlineStr">
+        <is>
+          <t>黑洞弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C43" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D43" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_blackhole/components/wpn_bullet_module_blackhole_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E43" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F43" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G43" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H43" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I43" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J43" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K43" s="82" t="inlineStr">
+        <is>
+          <t>[0.7773077487945557, 0.9399999976158142, 0.5242307782173157]；1424三角</t>
+        </is>
+      </c>
+      <c r="L43" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M43" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_blackhole</t>
+        </is>
+      </c>
+      <c r="N43" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O43" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P43" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BLACKHOLE</t>
+        </is>
+      </c>
+      <c r="B44" s="82" t="inlineStr">
+        <is>
+          <t>黑洞弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C44" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D44" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_blackhole/components/wpn_bullet_module_blackhole_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E44" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F44" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G44" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H44" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I44" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J44" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K44" s="82" t="inlineStr">
+        <is>
+          <t>[0.7773077487945557, 0.9399999976158142, 0.5242307782173157]；194三角</t>
+        </is>
+      </c>
+      <c r="L44" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M44" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_blackhole</t>
+        </is>
+      </c>
+      <c r="N44" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O44" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P44" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BALLOON</t>
+        </is>
+      </c>
+      <c r="B45" s="82" t="inlineStr">
+        <is>
+          <t>气球弹模块 / preview</t>
+        </is>
+      </c>
+      <c r="C45" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D45" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_balloon/components/wpn_bullet_module_balloon_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E45" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F45" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G45" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H45" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I45" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J45" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K45" s="82" t="inlineStr">
+        <is>
+          <t>[0.6207547187805176, 0.9399999976158142, 0.6207547187805176]；1324三角</t>
+        </is>
+      </c>
+      <c r="L45" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M45" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_balloon</t>
+        </is>
+      </c>
+      <c r="N45" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O45" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P45" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="81" t="inlineStr">
+        <is>
+          <t>WPN-BUL-MOD-BULLET-BALLOON</t>
+        </is>
+      </c>
+      <c r="B46" s="82" t="inlineStr">
+        <is>
+          <t>气球弹模块 / ground</t>
+        </is>
+      </c>
+      <c r="C46" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D46" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_module_balloon/components/wpn_bullet_module_balloon_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E46" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F46" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G46" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H46" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I46" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J46" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K46" s="82" t="inlineStr">
+        <is>
+          <t>[0.6207547187805176, 0.9399999976158142, 0.6207547187805176]；168三角</t>
+        </is>
+      </c>
+      <c r="L46" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M46" s="82" t="inlineStr">
+        <is>
+          <t>mod_bullet_balloon</t>
+        </is>
+      </c>
+      <c r="N46" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O46" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P46" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-FAN</t>
+        </is>
+      </c>
+      <c r="B47" s="82" t="inlineStr">
+        <is>
+          <t>小风扇 / preview</t>
+        </is>
+      </c>
+      <c r="C47" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D47" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/attachment_fan/components/wpn_attachment_fan_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E47" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F47" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G47" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H47" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I47" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J47" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K47" s="82" t="inlineStr">
+        <is>
+          <t>[0.4676923155784607, 0.6399999856948853, 0.20615386962890625]；1512三角</t>
+        </is>
+      </c>
+      <c r="L47" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M47" s="82" t="inlineStr">
+        <is>
+          <t>attach_fan</t>
+        </is>
+      </c>
+      <c r="N47" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O47" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P47" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-FAN</t>
+        </is>
+      </c>
+      <c r="B48" s="82" t="inlineStr">
+        <is>
+          <t>小风扇 / ground</t>
+        </is>
+      </c>
+      <c r="C48" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D48" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/attachment_fan/components/wpn_attachment_fan_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E48" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F48" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G48" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H48" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I48" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J48" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K48" s="82" t="inlineStr">
+        <is>
+          <t>[0.4676923155784607, 0.6399999856948853, 0.20615386962890625]；144三角</t>
+        </is>
+      </c>
+      <c r="L48" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M48" s="82" t="inlineStr">
+        <is>
+          <t>attach_fan</t>
+        </is>
+      </c>
+      <c r="N48" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O48" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P48" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-COPY-STICKER</t>
+        </is>
+      </c>
+      <c r="B49" s="82" t="inlineStr">
+        <is>
+          <t>复制贴纸 / preview</t>
+        </is>
+      </c>
+      <c r="C49" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D49" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/copy_sticker/components/wpn_copy_sticker_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E49" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F49" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G49" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H49" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I49" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J49" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K49" s="82" t="inlineStr">
+        <is>
+          <t>[0.7014707326889038, 0.6399999260902405, 0.25417670607566833]；1316三角</t>
+        </is>
+      </c>
+      <c r="L49" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M49" s="82" t="inlineStr">
+        <is>
+          <t>attach_copy_sticker</t>
+        </is>
+      </c>
+      <c r="N49" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O49" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P49" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="81" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-COPY-STICKER</t>
+        </is>
+      </c>
+      <c r="B50" s="82" t="inlineStr">
+        <is>
+          <t>复制贴纸 / ground</t>
+        </is>
+      </c>
+      <c r="C50" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D50" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/copy_sticker/components/wpn_copy_sticker_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E50" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F50" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G50" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H50" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I50" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J50" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K50" s="82" t="inlineStr">
+        <is>
+          <t>[0.7014707326889038, 0.6399999260902405, 0.25417670607566833]；150三角</t>
+        </is>
+      </c>
+      <c r="L50" s="82" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M50" s="82" t="inlineStr">
+        <is>
+          <t>attach_copy_sticker</t>
+        </is>
+      </c>
+      <c r="N50" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O50" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P50" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="81" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-BASEBALL-BAT</t>
+        </is>
+      </c>
+      <c r="B51" s="82" t="inlineStr">
+        <is>
+          <t>废土棒球棍 / preview</t>
+        </is>
+      </c>
+      <c r="C51" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D51" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_baseball_bat/components/wpn_melee_baseball_bat_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E51" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F51" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G51" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H51" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I51" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J51" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K51" s="82" t="inlineStr">
+        <is>
+          <t>[0.46580973267555237, 0.46580973267555237, 1.7349998950958252]；1604三角</t>
+        </is>
+      </c>
+      <c r="L51" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M51" s="82" t="inlineStr">
+        <is>
+          <t>weapon_baseball_bat</t>
+        </is>
+      </c>
+      <c r="N51" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O51" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P51" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="81" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-GREATBLADE</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="inlineStr">
+        <is>
+          <t>巨型工业断刃 / preview</t>
+        </is>
+      </c>
+      <c r="C52" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D52" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_greatblade/components/wpn_melee_greatblade_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E52" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F52" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G52" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H52" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I52" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J52" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K52" s="82" t="inlineStr">
+        <is>
+          <t>[1.1473641395568848, 0.407951682806015, 2.9194042682647705]；1708三角</t>
+        </is>
+      </c>
+      <c r="L52" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M52" s="82" t="inlineStr">
+        <is>
+          <t>weapon_greatblade</t>
+        </is>
+      </c>
+      <c r="N52" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O52" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P52" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="81" t="inlineStr">
+        <is>
+          <t>WPN-MELEE-BP-WARAXE</t>
+        </is>
+      </c>
+      <c r="B53" s="82" t="inlineStr">
+        <is>
+          <t>攻城裂甲斧 / preview</t>
+        </is>
+      </c>
+      <c r="C53" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D53" s="83" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/melee_waraxe/components/wpn_melee_waraxe_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E53" s="83" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F53" s="82" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G53" s="83" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H53" s="82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I53" s="82" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J53" s="82" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K53" s="82" t="inlineStr">
+        <is>
+          <t>[1.6731491088867188, 0.45187240839004517, 2.8700003623962402]；1300三角</t>
+        </is>
+      </c>
+      <c r="L53" s="82" t="inlineStr">
+        <is>
+          <t>existing_grip；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M53" s="82" t="inlineStr">
+        <is>
+          <t>weapon_waraxe</t>
+        </is>
+      </c>
+      <c r="N53" s="82" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O53" s="83" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P53" s="84" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P31"/>
+  <autoFilter ref="A4:P53"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -8994,7 +11027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="45" min="1" max="1"/>
@@ -9351,6 +11384,43 @@
       <c r="G13" s="45" t="inlineStr">
         <is>
           <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.106</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>剩余程序化物品20模型/28内容ID</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>双模型/GLB/PackedScene/调用链</t>
+        </is>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>100–200三角；蓝图共用；真实渲染及映射通过</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="G14" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -9371,7 +11441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="46" min="1" max="1"/>
@@ -9399,6 +11469,9 @@
           <t>武器账本 · 背包物品调用索引</t>
         </is>
       </c>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="94" t="n"/>
+      <c r="D1" s="94" t="n"/>
       <c r="E1" s="94" t="n"/>
       <c r="F1" s="94" t="n"/>
       <c r="G1" s="94" t="n"/>
@@ -9416,9 +11489,12 @@
     <row r="2" ht="44" customHeight="1" s="46">
       <c r="A2" s="94" t="inlineStr">
         <is>
-          <t>成品武器、子弹模块、通用弹药、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
-        </is>
-      </c>
+          <t>成品武器、子弹模块、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
+        </is>
+      </c>
+      <c r="B2" s="94" t="n"/>
+      <c r="C2" s="94" t="n"/>
+      <c r="D2" s="94" t="n"/>
       <c r="E2" s="94" t="n"/>
       <c r="F2" s="94" t="n"/>
       <c r="G2" s="94" t="n"/>
@@ -9602,7 +11678,7 @@
       </c>
       <c r="M5" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/hair_dryer/wpn_hair_dryer_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N5" s="94" t="inlineStr">
@@ -9689,7 +11765,7 @@
       </c>
       <c r="M6" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/double_barrel_cannon/wpn_double_barrel_cannon_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N6" s="94" t="inlineStr">
@@ -9776,7 +11852,7 @@
       </c>
       <c r="M7" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/broom_rifle/wpn_broom_rifle_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N7" s="94" t="inlineStr">
@@ -9863,7 +11939,7 @@
       </c>
       <c r="M8" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N8" s="94" t="inlineStr">
@@ -9950,7 +12026,7 @@
       </c>
       <c r="M9" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/water_tank_blaster/wpn_water_tank_blaster_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N9" s="94" t="inlineStr">
@@ -10037,7 +12113,7 @@
       </c>
       <c r="M10" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/broom_rifle/wpn_broom_rifle_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N10" s="94" t="inlineStr">
@@ -10124,7 +12200,7 @@
       </c>
       <c r="M11" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/candy_sniper/wpn_candy_sniper_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N11" s="94" t="inlineStr">
@@ -10211,7 +12287,7 @@
       </c>
       <c r="M12" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/toaster_launcher/wpn_toaster_launcher_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N12" s="94" t="inlineStr">
@@ -10298,7 +12374,7 @@
       </c>
       <c r="M13" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/weapons/weapon_3d/runtime/gumball_cannon/wpn_gumball_cannon_root_top3d_v001.tscn</t>
         </is>
       </c>
       <c r="N13" s="94" t="inlineStr">
@@ -10322,7 +12398,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="59" customHeight="1" s="46">
+    <row r="14" ht="76" customHeight="1" s="46">
       <c r="A14" s="94" t="inlineStr">
         <is>
           <t>weapon_baseball_bat</t>
@@ -10385,7 +12461,7 @@
       </c>
       <c r="M14" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N14" s="94" t="inlineStr">
@@ -10472,7 +12548,7 @@
       </c>
       <c r="M15" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N15" s="94" t="inlineStr">
@@ -10559,7 +12635,7 @@
       </c>
       <c r="M16" s="94" t="inlineStr">
         <is>
-          <t>weapon；真实武器快照重建</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N16" s="94" t="inlineStr">
@@ -10583,23 +12659,27 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="110" customHeight="1" s="46">
+    <row r="17" ht="76" customHeight="1" s="46">
       <c r="A17" s="94" t="inlineStr">
         <is>
-          <t>item_ammo_pack</t>
+          <t>mod_bullet_standard</t>
         </is>
       </c>
       <c r="B17" s="94" t="inlineStr">
         <is>
-          <t>通用弹药</t>
+          <t>标准子弹模块</t>
         </is>
       </c>
       <c r="C17" s="94" t="inlineStr">
         <is>
-          <t>consumable</t>
-        </is>
-      </c>
-      <c r="D17" s="94" t="inlineStr"/>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
       <c r="E17" s="94" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
@@ -10607,24 +12687,22 @@
       </c>
       <c r="F17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L800</t>
+          <t>src/base/ItemRegistry.gd#L947</t>
         </is>
       </c>
       <c r="G17" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A18</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A28</t>
         </is>
       </c>
       <c r="H17" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / melee_chaser
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
         </is>
       </c>
       <c r="I17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L800 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L947 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J17" s="95" t="inlineStr">
@@ -10634,7 +12712,7 @@
       </c>
       <c r="K17" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_on_inventory_item_clicked</t>
+          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
         </is>
       </c>
       <c r="L17" s="95" t="inlineStr">
@@ -10644,17 +12722,17 @@
       </c>
       <c r="M17" s="94" t="inlineStr">
         <is>
-          <t>ammo；程序罐体</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N17" s="94" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-AMMO-PACK</t>
-        </is>
-      </c>
-      <c r="O17" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A34</t>
+          <t>WPN-BUL-MOD-BULLET-STANDARD</t>
+        </is>
+      </c>
+      <c r="O17" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13</t>
         </is>
       </c>
       <c r="P17" s="94" t="inlineStr">
@@ -10664,19 +12742,19 @@
       </c>
       <c r="Q17" s="94" t="inlineStr">
         <is>
-          <t>蓝金色通用弹药模型已映射地面与图标；倾斜45度旋转</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1" s="46">
       <c r="A18" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_standard</t>
+          <t>mod_bullet_sticky</t>
         </is>
       </c>
       <c r="B18" s="94" t="inlineStr">
         <is>
-          <t>标准子弹模块</t>
+          <t>黏黏弹模块</t>
         </is>
       </c>
       <c r="C18" s="94" t="inlineStr">
@@ -10696,22 +12774,22 @@
       </c>
       <c r="F18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L947</t>
+          <t>src/base/ItemRegistry.gd#L970</t>
         </is>
       </c>
       <c r="G18" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A28</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A29</t>
         </is>
       </c>
       <c r="H18" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L947 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L970 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J18" s="95" t="inlineStr">
@@ -10731,19 +12809,17 @@
       </c>
       <c r="M18" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N18" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-STANDARD
-VFX-BULLET-STANDARD-3D</t>
-        </is>
-      </c>
-      <c r="O18" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A13
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A27</t>
+          <t>WPN-BUL-MOD-BULLET-STICKY</t>
+        </is>
+      </c>
+      <c r="O18" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A14</t>
         </is>
       </c>
       <c r="P18" s="94" t="inlineStr">
@@ -10753,19 +12829,19 @@
       </c>
       <c r="Q18" s="94" t="inlineStr">
         <is>
-          <t>标准子弹模块继续程序表现；蓝金弹头模型按用户更正归属通用弹药</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76" customHeight="1" s="46">
       <c r="A19" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_sticky</t>
+          <t>mod_bullet_bounce</t>
         </is>
       </c>
       <c r="B19" s="94" t="inlineStr">
         <is>
-          <t>黏黏弹模块</t>
+          <t>回旋镖弹模块</t>
         </is>
       </c>
       <c r="C19" s="94" t="inlineStr">
@@ -10785,22 +12861,22 @@
       </c>
       <c r="F19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L970</t>
+          <t>src/base/ItemRegistry.gd#L993</t>
         </is>
       </c>
       <c r="G19" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A29</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A24</t>
         </is>
       </c>
       <c r="H19" s="94" t="inlineStr">
         <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
         </is>
       </c>
       <c r="I19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L970 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L993 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J19" s="95" t="inlineStr">
@@ -10820,19 +12896,17 @@
       </c>
       <c r="M19" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N19" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-STICKY
-VFX-BULLET-STICKY-3D</t>
-        </is>
-      </c>
-      <c r="O19" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A14
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A28</t>
+          <t>WPN-BUL-MOD-BULLET-BOUNCE</t>
+        </is>
+      </c>
+      <c r="O19" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A15</t>
         </is>
       </c>
       <c r="P19" s="94" t="inlineStr">
@@ -10842,19 +12916,19 @@
       </c>
       <c r="Q19" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1" s="46">
       <c r="A20" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_bounce</t>
+          <t>mod_bullet_piercing</t>
         </is>
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>回旋镖弹模块</t>
+          <t>穿甲弹模块</t>
         </is>
       </c>
       <c r="C20" s="94" t="inlineStr">
@@ -10874,22 +12948,22 @@
       </c>
       <c r="F20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L993</t>
+          <t>src/base/ItemRegistry.gd#L1022</t>
         </is>
       </c>
       <c r="G20" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A24</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A27</t>
         </is>
       </c>
       <c r="H20" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行6 / ranged_caster</t>
         </is>
       </c>
       <c r="I20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L993 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1022 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J20" s="95" t="inlineStr">
@@ -10909,19 +12983,17 @@
       </c>
       <c r="M20" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N20" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-BOUNCE
-VFX-BULLET-BOUNCE-3D</t>
-        </is>
-      </c>
-      <c r="O20" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A15
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A29</t>
+          <t>WPN-BUL-MOD-BULLET-PIERCING</t>
+        </is>
+      </c>
+      <c r="O20" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A16</t>
         </is>
       </c>
       <c r="P20" s="94" t="inlineStr">
@@ -10938,12 +13010,12 @@
     <row r="21" ht="76" customHeight="1" s="46">
       <c r="A21" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_piercing</t>
+          <t>mod_bullet_explosive</t>
         </is>
       </c>
       <c r="B21" s="94" t="inlineStr">
         <is>
-          <t>穿甲弹模块</t>
+          <t>爆炸弹模块</t>
         </is>
       </c>
       <c r="C21" s="94" t="inlineStr">
@@ -10963,22 +13035,22 @@
       </c>
       <c r="F21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1022</t>
+          <t>src/base/ItemRegistry.gd#L1043</t>
         </is>
       </c>
       <c r="G21" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A27</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A25</t>
         </is>
       </c>
       <c r="H21" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行6 / ranged_caster</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / exploder</t>
         </is>
       </c>
       <c r="I21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1022 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1043 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J21" s="95" t="inlineStr">
@@ -10998,19 +13070,17 @@
       </c>
       <c r="M21" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N21" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-PIERCING
-VFX-BULLET-PIERCING-3D</t>
-        </is>
-      </c>
-      <c r="O21" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A16
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A30</t>
+          <t>WPN-BUL-MOD-BULLET-EXPLOSIVE</t>
+        </is>
+      </c>
+      <c r="O21" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A17</t>
         </is>
       </c>
       <c r="P21" s="94" t="inlineStr">
@@ -11027,12 +13097,12 @@
     <row r="22" ht="76" customHeight="1" s="46">
       <c r="A22" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_explosive</t>
+          <t>mod_bullet_homing</t>
         </is>
       </c>
       <c r="B22" s="94" t="inlineStr">
         <is>
-          <t>爆炸弹模块</t>
+          <t>蜂卵弹模块</t>
         </is>
       </c>
       <c r="C22" s="94" t="inlineStr">
@@ -11052,22 +13122,22 @@
       </c>
       <c r="F22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1043</t>
+          <t>src/base/ItemRegistry.gd#L1064</t>
         </is>
       </c>
       <c r="G22" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A25</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A26</t>
         </is>
       </c>
       <c r="H22" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / exploder</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1043 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1064 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J22" s="95" t="inlineStr">
@@ -11087,19 +13157,17 @@
       </c>
       <c r="M22" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N22" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-EXPLOSIVE
-VFX-BULLET-EXPLOSIVE-3D</t>
-        </is>
-      </c>
-      <c r="O22" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A17
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A31</t>
+          <t>WPN-BUL-MOD-BULLET-HOMING</t>
+        </is>
+      </c>
+      <c r="O22" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A18</t>
         </is>
       </c>
       <c r="P22" s="94" t="inlineStr">
@@ -11109,19 +13177,19 @@
       </c>
       <c r="Q22" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1" s="46">
       <c r="A23" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_homing</t>
+          <t>mod_bullet_blackhole</t>
         </is>
       </c>
       <c r="B23" s="94" t="inlineStr">
         <is>
-          <t>蜂卵弹模块</t>
+          <t>黑洞弹模块</t>
         </is>
       </c>
       <c r="C23" s="94" t="inlineStr">
@@ -11141,12 +13209,12 @@
       </c>
       <c r="F23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1064</t>
+          <t>src/base/ItemRegistry.gd#L1085</t>
         </is>
       </c>
       <c r="G23" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A26</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A23</t>
         </is>
       </c>
       <c r="H23" s="94" t="inlineStr">
@@ -11156,7 +13224,7 @@
       </c>
       <c r="I23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1064 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1085 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J23" s="95" t="inlineStr">
@@ -11176,19 +13244,17 @@
       </c>
       <c r="M23" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N23" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-HOMING
-VFX-BULLET-HOMING-3D</t>
-        </is>
-      </c>
-      <c r="O23" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A18
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A32</t>
+          <t>WPN-BUL-MOD-BULLET-BLACKHOLE</t>
+        </is>
+      </c>
+      <c r="O23" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A19</t>
         </is>
       </c>
       <c r="P23" s="94" t="inlineStr">
@@ -11205,12 +13271,12 @@
     <row r="24" ht="76" customHeight="1" s="46">
       <c r="A24" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_blackhole</t>
+          <t>mod_bullet_balloon</t>
         </is>
       </c>
       <c r="B24" s="94" t="inlineStr">
         <is>
-          <t>黑洞弹模块</t>
+          <t>气球弹模块</t>
         </is>
       </c>
       <c r="C24" s="94" t="inlineStr">
@@ -11230,12 +13296,12 @@
       </c>
       <c r="F24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1085</t>
+          <t>src/base/ItemRegistry.gd#L1106</t>
         </is>
       </c>
       <c r="G24" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A23</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A22</t>
         </is>
       </c>
       <c r="H24" s="94" t="inlineStr">
@@ -11245,7 +13311,7 @@
       </c>
       <c r="I24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1085 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1106 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J24" s="95" t="inlineStr">
@@ -11265,19 +13331,17 @@
       </c>
       <c r="M24" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N24" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-BLACKHOLE
-VFX-BULLET-BLACKHOLE-3D</t>
-        </is>
-      </c>
-      <c r="O24" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A19
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A33</t>
+          <t>WPN-BUL-MOD-BULLET-BALLOON</t>
+        </is>
+      </c>
+      <c r="O24" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A20</t>
         </is>
       </c>
       <c r="P24" s="94" t="inlineStr">
@@ -11291,25 +13355,25 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="76" customHeight="1" s="46">
+    <row r="25" ht="93" customHeight="1" s="46">
       <c r="A25" s="94" t="inlineStr">
         <is>
-          <t>mod_bullet_balloon</t>
+          <t>attach_triple_muzzle</t>
         </is>
       </c>
       <c r="B25" s="94" t="inlineStr">
         <is>
-          <t>气球弹模块</t>
+          <t>三叉枪口</t>
         </is>
       </c>
       <c r="C25" s="94" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>attachment</t>
         </is>
       </c>
       <c r="D25" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>muzzle</t>
         </is>
       </c>
       <c r="E25" s="94" t="inlineStr">
@@ -11319,12 +13383,12 @@
       </c>
       <c r="F25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1106</t>
+          <t>src/base/ItemRegistry.gd#L1134</t>
         </is>
       </c>
       <c r="G25" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A22</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A10</t>
         </is>
       </c>
       <c r="H25" s="94" t="inlineStr">
@@ -11334,7 +13398,7 @@
       </c>
       <c r="I25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1106 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L1134 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J25" s="95" t="inlineStr">
@@ -11344,7 +13408,7 @@
       </c>
       <c r="K25" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
         </is>
       </c>
       <c r="L25" s="95" t="inlineStr">
@@ -11354,19 +13418,17 @@
       </c>
       <c r="M25" s="94" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/triple_muzzle/runtime/wpn_triple_muzzle_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N25" s="94" t="inlineStr">
         <is>
-          <t>WPN-BUL-MOD-BULLET-BALLOON
-VFX-BULLET-BALLOON-3D</t>
-        </is>
-      </c>
-      <c r="O25" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A20
-assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx#资产主表!A34</t>
+          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
+        </is>
+      </c>
+      <c r="O25" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A21</t>
         </is>
       </c>
       <c r="P25" s="94" t="inlineStr">
@@ -11383,12 +13445,12 @@
     <row r="26" ht="93" customHeight="1" s="46">
       <c r="A26" s="94" t="inlineStr">
         <is>
-          <t>attach_triple_muzzle</t>
+          <t>attach_rubber_stock</t>
         </is>
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>三叉枪口</t>
+          <t>橡皮枪托</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
@@ -11398,7 +13460,7 @@
       </c>
       <c r="D26" s="94" t="inlineStr">
         <is>
-          <t>muzzle</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="E26" s="94" t="inlineStr">
@@ -11408,12 +13470,12 @@
       </c>
       <c r="F26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1134</t>
+          <t>src/base/ItemRegistry.gd#L1159</t>
         </is>
       </c>
       <c r="G26" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A10</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A8</t>
         </is>
       </c>
       <c r="H26" s="94" t="inlineStr">
@@ -11423,7 +13485,7 @@
       </c>
       <c r="I26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1134 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1159 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J26" s="95" t="inlineStr">
@@ -11443,126 +13505,126 @@
       </c>
       <c r="M26" s="94" t="inlineStr">
         <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/rubber_stock/runtime/wpn_rubber_stock_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N26" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-RUBBER-STOCK</t>
+        </is>
+      </c>
+      <c r="O26" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A22</t>
+        </is>
+      </c>
+      <c r="P26" s="94" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="Q26" s="94" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="76" customHeight="1" s="46">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>attach_scope</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>放大镜瞄具</t>
+        </is>
+      </c>
+      <c r="C27" s="94" t="inlineStr">
+        <is>
           <t>attachment</t>
         </is>
       </c>
-      <c r="N26" s="94" t="inlineStr">
-        <is>
-          <t>WPN-ATT-ATTACH-TRIPLE-MUZZLE</t>
-        </is>
-      </c>
-      <c r="O26" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A21</t>
-        </is>
-      </c>
-      <c r="P26" s="94" t="inlineStr">
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="E27" s="94" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1190</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A9</t>
+        </is>
+      </c>
+      <c r="H27" s="94" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
+        </is>
+      </c>
+      <c r="I27" s="95" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L1190 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J27" s="95" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K27" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
+        </is>
+      </c>
+      <c r="L27" s="95" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M27" s="94" t="inlineStr">
+        <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/scope/runtime/wpn_scope_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N27" s="94" t="inlineStr">
+        <is>
+          <t>WPN-ATT-ATTACH-SCOPE</t>
+        </is>
+      </c>
+      <c r="O27" s="95" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A23</t>
+        </is>
+      </c>
+      <c r="P27" s="94" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
         </is>
       </c>
-      <c r="Q26" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="93" customHeight="1" s="46">
-      <c r="A27" s="94" t="inlineStr">
-        <is>
-          <t>attach_rubber_stock</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>橡皮枪托</t>
-        </is>
-      </c>
-      <c r="C27" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="E27" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1159</t>
-        </is>
-      </c>
-      <c r="G27" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A8</t>
-        </is>
-      </c>
-      <c r="H27" s="94" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
-      <c r="I27" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1159 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J27" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K27" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
-        </is>
-      </c>
-      <c r="L27" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M27" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="N27" s="94" t="inlineStr">
-        <is>
-          <t>WPN-ATT-ATTACH-RUBBER-STOCK</t>
-        </is>
-      </c>
-      <c r="O27" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A22</t>
-        </is>
-      </c>
-      <c r="P27" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
       <c r="Q27" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="28" ht="76" customHeight="1" s="46">
       <c r="A28" s="94" t="inlineStr">
         <is>
-          <t>attach_scope</t>
+          <t>attach_big_mag</t>
         </is>
       </c>
       <c r="B28" s="94" t="inlineStr">
         <is>
-          <t>放大镜瞄具</t>
+          <t>肉质弹匣</t>
         </is>
       </c>
       <c r="C28" s="94" t="inlineStr">
@@ -11572,7 +13634,7 @@
       </c>
       <c r="D28" s="94" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>magazine</t>
         </is>
       </c>
       <c r="E28" s="94" t="inlineStr">
@@ -11582,22 +13644,22 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1190</t>
+          <t>src/base/ItemRegistry.gd#L1212</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A9</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A5</t>
         </is>
       </c>
       <c r="H28" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1190 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1212 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J28" s="95" t="inlineStr">
@@ -11617,17 +13679,17 @@
       </c>
       <c r="M28" s="94" t="inlineStr">
         <is>
-          <t>attachment</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/big_mag/runtime/wpn_big_mag_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N28" s="94" t="inlineStr">
         <is>
-          <t>WPN-ATT-ATTACH-SCOPE</t>
+          <t>WPN-ATT-ATTACH-BIG-MAG</t>
         </is>
       </c>
       <c r="O28" s="95" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A23</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A24</t>
         </is>
       </c>
       <c r="P28" s="94" t="inlineStr">
@@ -11637,19 +13699,19 @@
       </c>
       <c r="Q28" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="76" customHeight="1" s="46">
       <c r="A29" s="94" t="inlineStr">
         <is>
-          <t>attach_big_mag</t>
+          <t>attach_fan</t>
         </is>
       </c>
       <c r="B29" s="94" t="inlineStr">
         <is>
-          <t>肉质弹匣</t>
+          <t>小风扇</t>
         </is>
       </c>
       <c r="C29" s="94" t="inlineStr">
@@ -11659,7 +13721,7 @@
       </c>
       <c r="D29" s="94" t="inlineStr">
         <is>
-          <t>magazine</t>
+          <t>external</t>
         </is>
       </c>
       <c r="E29" s="94" t="inlineStr">
@@ -11669,12 +13731,12 @@
       </c>
       <c r="F29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1212</t>
+          <t>src/base/ItemRegistry.gd#L1234</t>
         </is>
       </c>
       <c r="G29" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A5</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A7</t>
         </is>
       </c>
       <c r="H29" s="94" t="inlineStr">
@@ -11684,7 +13746,7 @@
       </c>
       <c r="I29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1212 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1234 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J29" s="95" t="inlineStr">
@@ -11704,17 +13766,17 @@
       </c>
       <c r="M29" s="94" t="inlineStr">
         <is>
-          <t>attachment</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N29" s="94" t="inlineStr">
         <is>
-          <t>WPN-ATT-ATTACH-BIG-MAG</t>
+          <t>WPN-ATT-ATTACH-FAN</t>
         </is>
       </c>
       <c r="O29" s="95" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A24</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A25</t>
         </is>
       </c>
       <c r="P29" s="94" t="inlineStr">
@@ -11731,12 +13793,12 @@
     <row r="30" ht="76" customHeight="1" s="46">
       <c r="A30" s="94" t="inlineStr">
         <is>
-          <t>attach_fan</t>
+          <t>attach_copy_sticker</t>
         </is>
       </c>
       <c r="B30" s="94" t="inlineStr">
         <is>
-          <t>小风扇</t>
+          <t>复制贴纸</t>
         </is>
       </c>
       <c r="C30" s="94" t="inlineStr">
@@ -11746,7 +13808,7 @@
       </c>
       <c r="D30" s="94" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>mutator</t>
         </is>
       </c>
       <c r="E30" s="94" t="inlineStr">
@@ -11756,12 +13818,12 @@
       </c>
       <c r="F30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1234</t>
+          <t>src/base/ItemRegistry.gd#L1256</t>
         </is>
       </c>
       <c r="G30" s="95" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A7</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A6</t>
         </is>
       </c>
       <c r="H30" s="94" t="inlineStr">
@@ -11771,7 +13833,7 @@
       </c>
       <c r="I30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1234 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1256 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J30" s="95" t="inlineStr">
@@ -11791,17 +13853,17 @@
       </c>
       <c r="M30" s="94" t="inlineStr">
         <is>
-          <t>attachment</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N30" s="94" t="inlineStr">
         <is>
-          <t>WPN-ATT-ATTACH-FAN</t>
+          <t>WPN-ATT-ATTACH-COPY-STICKER</t>
         </is>
       </c>
       <c r="O30" s="95" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A25</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A26</t>
         </is>
       </c>
       <c r="P30" s="94" t="inlineStr">
@@ -11810,93 +13872,6 @@
         </is>
       </c>
       <c r="Q30" s="94" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="76" customHeight="1" s="46">
-      <c r="A31" s="94" t="inlineStr">
-        <is>
-          <t>attach_copy_sticker</t>
-        </is>
-      </c>
-      <c r="B31" s="94" t="inlineStr">
-        <is>
-          <t>复制贴纸</t>
-        </is>
-      </c>
-      <c r="C31" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="D31" s="94" t="inlineStr">
-        <is>
-          <t>mutator</t>
-        </is>
-      </c>
-      <c r="E31" s="94" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F31" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1256</t>
-        </is>
-      </c>
-      <c r="G31" s="95" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A6</t>
-        </is>
-      </c>
-      <c r="H31" s="94" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
-      <c r="I31" s="95" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L1256 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
-        </is>
-      </c>
-      <c r="J31" s="95" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K31" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_install_attachment_from_inventory</t>
-        </is>
-      </c>
-      <c r="L31" s="95" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M31" s="94" t="inlineStr">
-        <is>
-          <t>attachment</t>
-        </is>
-      </c>
-      <c r="N31" s="94" t="inlineStr">
-        <is>
-          <t>WPN-ATT-ATTACH-COPY-STICKER</t>
-        </is>
-      </c>
-      <c r="O31" s="95" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#资产主表!A26</t>
-        </is>
-      </c>
-      <c r="P31" s="94" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS / WEAPON-OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="Q31" s="94" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
@@ -11995,100 +13970,102 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId179"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId178"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId180"/>
   </tableParts>
 </worksheet>
 </file>
--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -3240,8 +3240,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V13" s="71" t="n">
-        <v>46309</v>
+      <c r="V13" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W13" s="57" t="inlineStr">
         <is>
@@ -3255,7 +3257,9 @@
       </c>
       <c r="Y13" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_standard/source/wpn_bullet_module_standard_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3359,8 +3363,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V14" s="71" t="n">
-        <v>46309</v>
+      <c r="V14" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W14" s="57" t="inlineStr">
         <is>
@@ -3374,7 +3380,9 @@
       </c>
       <c r="Y14" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_sticky/source/wpn_bullet_module_sticky_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3478,8 +3486,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V15" s="71" t="n">
-        <v>46309</v>
+      <c r="V15" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W15" s="57" t="inlineStr">
         <is>
@@ -3493,7 +3503,9 @@
       </c>
       <c r="Y15" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_bounce/source/wpn_bullet_module_bounce_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3597,8 +3609,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V16" s="71" t="n">
-        <v>46309</v>
+      <c r="V16" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W16" s="57" t="inlineStr">
         <is>
@@ -3612,7 +3626,9 @@
       </c>
       <c r="Y16" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_piercing/source/wpn_bullet_module_piercing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3716,8 +3732,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V17" s="71" t="n">
-        <v>46309</v>
+      <c r="V17" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W17" s="57" t="inlineStr">
         <is>
@@ -3731,7 +3749,9 @@
       </c>
       <c r="Y17" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_explosive/source/wpn_bullet_module_explosive_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3835,8 +3855,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V18" s="71" t="n">
-        <v>46309</v>
+      <c r="V18" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W18" s="57" t="inlineStr">
         <is>
@@ -3850,7 +3872,9 @@
       </c>
       <c r="Y18" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_homing/source/wpn_bullet_module_homing_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -3954,8 +3978,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V19" s="71" t="n">
-        <v>46309</v>
+      <c r="V19" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W19" s="57" t="inlineStr">
         <is>
@@ -3969,7 +3995,9 @@
       </c>
       <c r="Y19" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_blackhole/source/wpn_bullet_module_blackhole_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4073,8 +4101,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V20" s="71" t="n">
-        <v>46309</v>
+      <c r="V20" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W20" s="57" t="inlineStr">
         <is>
@@ -4088,7 +4118,9 @@
       </c>
       <c r="Y20" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_source_v001.blend；地面源=art_source/items_weapons/weapons/bullet_module_balloon/source/wpn_bullet_module_balloon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4192,8 +4224,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V21" s="71" t="n">
-        <v>46309</v>
+      <c r="V21" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W21" s="57" t="inlineStr">
         <is>
@@ -4207,7 +4241,9 @@
       </c>
       <c r="Y21" s="57" t="inlineStr">
         <is>
-          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/triple_muzzle/components/wpn_triple_muzzle_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend SHA256=3fba4ba572c107b080cb05289d21f8d5f6ae778776f7587ffa998222bdf7c293；preview源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend SHA256=53871c61c511ac2ac41685bcc65e765b591b5cbcd7880d3685cacf545cdd94c5；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
+          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/triple_muzzle/components/wpn_triple_muzzle_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_ground_source_v001.blend SHA256=73485f827928da5f98c7971b726a8d8eb4c75a2d21fa94ae8eeaacfab405e852；preview源=art_source/items_weapons/weapons/triple_muzzle/source/wpn_triple_muzzle_source_v001.blend SHA256=880e8cc432c602a28f85985594a4835d5e08f0ae1ab12b478f4814fa344e5816；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4311,8 +4347,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V22" s="71" t="n">
-        <v>46309</v>
+      <c r="V22" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W22" s="57" t="inlineStr">
         <is>
@@ -4326,7 +4364,9 @@
       </c>
       <c r="Y22" s="57" t="inlineStr">
         <is>
-          <t>ground=145三角；GLB=assets/art/items_weapons/weapons/rubber_stock/components/wpn_rubber_stock_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend SHA256=4e4a906492d9eb1f79bfd5e756991584422fd30664dd502a25cfe542436791d7；preview源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend SHA256=f1cf82e20b7c1a481dfe979503bc3f98fd9566cac09ede315ba238ab9a6c90bb；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
+          <t>ground=145三角；GLB=assets/art/items_weapons/weapons/rubber_stock/components/wpn_rubber_stock_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_ground_source_v001.blend SHA256=85bc63326868d201f9a592aca38826406dbcb160c1962d008dedaeab5103bfcc；preview源=art_source/items_weapons/weapons/rubber_stock/source/wpn_rubber_stock_source_v001.blend SHA256=9b678c44eb85edef527ce2cc504fc7e11ad396a0242147c6d31470b19b874eaf；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4430,8 +4470,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V23" s="71" t="n">
-        <v>46309</v>
+      <c r="V23" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W23" s="57" t="inlineStr">
         <is>
@@ -4445,7 +4487,9 @@
       </c>
       <c r="Y23" s="57" t="inlineStr">
         <is>
-          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/scope/components/wpn_scope_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend SHA256=a6ebf1f74d67fb2ee77f1be0bc5442fe1d74d1058826c6cf4d0a43d3f9b9e138；preview源=art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend SHA256=6c4244348bb117f35a862187503ab5577be801b5f1dd00e72bcb17c095274b95；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
+          <t>ground=198三角；GLB=assets/art/items_weapons/weapons/scope/components/wpn_scope_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/scope/source/wpn_scope_ground_source_v001.blend SHA256=61aa67a95319747a9e55aeaa3b8615050a1c873d3e57eca3cf99d0c5fe0ff468；preview源=art_source/items_weapons/weapons/scope/source/wpn_scope_source_v001.blend SHA256=f9f437a06931bc40eb3540b98a0cc36592204d6a424bdf1f27e5289fc91c2319；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4549,8 +4593,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V24" s="71" t="n">
-        <v>46309</v>
+      <c r="V24" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W24" s="57" t="inlineStr">
         <is>
@@ -4564,7 +4610,9 @@
       </c>
       <c r="Y24" s="57" t="inlineStr">
         <is>
-          <t>ground=192三角；GLB=assets/art/items_weapons/weapons/big_mag/components/wpn_big_mag_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend SHA256=a67664acb24910e970b61d43ed1cf2e3395a876a6896a67853cd5648a19cafff；preview源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend SHA256=8513e3320fad3a4af8ee4562b5149b9a45f0e95d72df06accb96b0b7befe72f5；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
+          <t>ground=192三角；GLB=assets/art/items_weapons/weapons/big_mag/components/wpn_big_mag_ground_visual_top3d.glb；ground源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_ground_source_v001.blend SHA256=920a6d65a25b72fca3cbffd95f58ab94f84f2b40113b6b746c911369baca3971；preview源=art_source/items_weapons/weapons/big_mag/source/wpn_big_mag_source_v001.blend SHA256=c69fcea3a4bbb66326d6426818267854141d152ee6479cd7fa5fe845e714b6a3；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4668,8 +4716,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V25" s="71" t="n">
-        <v>46309</v>
+      <c r="V25" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W25" s="57" t="inlineStr">
         <is>
@@ -4683,7 +4733,9 @@
       </c>
       <c r="Y25" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_source_v001.blend；地面源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_source_v001.blend；地面源=art_source/items_weapons/weapons/attachment_fan/source/wpn_attachment_fan_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -4787,8 +4839,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V26" s="71" t="n">
-        <v>46309</v>
+      <c r="V26" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W26" s="57" t="inlineStr">
         <is>
@@ -4802,7 +4856,9 @@
       </c>
       <c r="Y26" s="57" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_source_v001.blend；地面源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_source_v001.blend；地面源=art_source/items_weapons/weapons/copy_sticker/source/wpn_copy_sticker_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5026,8 +5082,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V28" s="74" t="n">
-        <v>46309</v>
+      <c r="V28" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W28" s="49" t="inlineStr">
         <is>
@@ -5041,7 +5099,9 @@
       </c>
       <c r="Y28" s="49" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5145,8 +5205,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V29" s="74" t="n">
-        <v>46309</v>
+      <c r="V29" s="74" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W29" s="49" t="inlineStr">
         <is>
@@ -5160,7 +5222,9 @@
       </c>
       <c r="Y29" s="49" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5264,8 +5328,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V30" s="97" t="n">
-        <v>46309</v>
+      <c r="V30" s="97" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W30" s="49" t="inlineStr">
         <is>
@@ -5279,7 +5345,9 @@
       </c>
       <c r="Y30" s="49" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法</t>
+          <t>高精度源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -6903,6 +6971,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="46">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -7063,7 +7132,7 @@
       </c>
       <c r="P5" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7214,7 @@
       </c>
       <c r="P6" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7296,7 @@
       </c>
       <c r="P7" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8928,7 @@
       </c>
       <c r="P27" s="84" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8941,7 +9010,7 @@
       </c>
       <c r="P28" s="84" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9092,7 @@
       </c>
       <c r="P29" s="84" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9174,7 @@
       </c>
       <c r="P30" s="84" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9256,7 @@
       </c>
       <c r="P31" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9338,7 @@
       </c>
       <c r="P32" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9420,7 @@
       </c>
       <c r="P33" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9502,7 @@
       </c>
       <c r="P34" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9584,7 @@
       </c>
       <c r="P35" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9666,7 @@
       </c>
       <c r="P36" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9748,7 @@
       </c>
       <c r="P37" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9830,7 @@
       </c>
       <c r="P38" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9912,7 @@
       </c>
       <c r="P39" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9994,7 @@
       </c>
       <c r="P40" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10076,7 @@
       </c>
       <c r="P41" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10158,7 @@
       </c>
       <c r="P42" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10240,7 @@
       </c>
       <c r="P43" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10322,7 @@
       </c>
       <c r="P44" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10404,7 @@
       </c>
       <c r="P45" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10486,7 @@
       </c>
       <c r="P46" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10568,7 @@
       </c>
       <c r="P47" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10650,7 @@
       </c>
       <c r="P48" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10732,7 @@
       </c>
       <c r="P49" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10814,7 @@
       </c>
       <c r="P50" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10896,7 @@
       </c>
       <c r="P51" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10978,7 @@
       </c>
       <c r="P52" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -10991,7 +11060,7 @@
       </c>
       <c r="P53" s="84" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="45" min="1" max="1"/>
@@ -11419,6 +11488,80 @@
         </is>
       </c>
       <c r="G14" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.107</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>物品专用色板与母版材质绑定</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>HSV S/V×1.40；31资产；51GLB；64Blender</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="inlineStr">
+        <is>
+          <t>运行底色/发光/图标通过，几何UV不变</t>
+        </is>
+      </c>
+      <c r="F15" s="45" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G15" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>v0.1.108</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>物品独立四材质与图标补光</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>HSV S/V×1.61；31资产；51GLB；64Blender；四个独立材质</t>
+        </is>
+      </c>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>同灯光开关补光对比通过，世界材质无污染</t>
+        </is>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>
@@ -11469,9 +11612,6 @@
           <t>武器账本 · 背包物品调用索引</t>
         </is>
       </c>
-      <c r="B1" s="94" t="n"/>
-      <c r="C1" s="94" t="n"/>
-      <c r="D1" s="94" t="n"/>
       <c r="E1" s="94" t="n"/>
       <c r="F1" s="94" t="n"/>
       <c r="G1" s="94" t="n"/>
@@ -11492,9 +11632,6 @@
           <t>成品武器、子弹模块、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
         </is>
       </c>
-      <c r="B2" s="94" t="n"/>
-      <c r="C2" s="94" t="n"/>
-      <c r="D2" s="94" t="n"/>
       <c r="E2" s="94" t="n"/>
       <c r="F2" s="94" t="n"/>
       <c r="G2" s="94" t="n"/>
@@ -11643,7 +11780,7 @@
       </c>
       <c r="F5" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L205</t>
+          <t>src/base/ItemRegistry.gd#L290</t>
         </is>
       </c>
       <c r="G5" s="95" t="inlineStr">
@@ -11658,7 +11795,7 @@
       </c>
       <c r="I5" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L205 / loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L290 / loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J5" s="95" t="inlineStr">
@@ -11730,7 +11867,7 @@
       </c>
       <c r="F6" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L224</t>
+          <t>src/base/ItemRegistry.gd#L309</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -11745,7 +11882,7 @@
       </c>
       <c r="I6" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L224 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L309 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J6" s="95" t="inlineStr">
@@ -11817,7 +11954,7 @@
       </c>
       <c r="F7" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L244</t>
+          <t>src/base/ItemRegistry.gd#L329</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
@@ -11832,7 +11969,7 @@
       </c>
       <c r="I7" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L244 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L329 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J7" s="95" t="inlineStr">
@@ -11904,7 +12041,7 @@
       </c>
       <c r="F8" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L273</t>
+          <t>src/base/ItemRegistry.gd#L358</t>
         </is>
       </c>
       <c r="G8" s="95" t="inlineStr">
@@ -11919,7 +12056,7 @@
       </c>
       <c r="I8" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L273 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L358 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J8" s="95" t="inlineStr">
@@ -11991,7 +12128,7 @@
       </c>
       <c r="F9" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L302</t>
+          <t>src/base/ItemRegistry.gd#L387</t>
         </is>
       </c>
       <c r="G9" s="94" t="inlineStr">
@@ -12006,7 +12143,7 @@
       </c>
       <c r="I9" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L302 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L387 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J9" s="95" t="inlineStr">
@@ -12078,7 +12215,7 @@
       </c>
       <c r="F10" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L333</t>
+          <t>src/base/ItemRegistry.gd#L418</t>
         </is>
       </c>
       <c r="G10" s="95" t="inlineStr">
@@ -12093,7 +12230,7 @@
       </c>
       <c r="I10" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L333 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L418 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J10" s="95" t="inlineStr">
@@ -12165,7 +12302,7 @@
       </c>
       <c r="F11" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L365</t>
+          <t>src/base/ItemRegistry.gd#L450</t>
         </is>
       </c>
       <c r="G11" s="95" t="inlineStr">
@@ -12180,7 +12317,7 @@
       </c>
       <c r="I11" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L365 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L450 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J11" s="95" t="inlineStr">
@@ -12252,7 +12389,7 @@
       </c>
       <c r="F12" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L392</t>
+          <t>src/base/ItemRegistry.gd#L477</t>
         </is>
       </c>
       <c r="G12" s="95" t="inlineStr">
@@ -12267,7 +12404,7 @@
       </c>
       <c r="I12" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L392 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L477 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
         </is>
       </c>
       <c r="J12" s="95" t="inlineStr">
@@ -12339,7 +12476,7 @@
       </c>
       <c r="F13" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L419</t>
+          <t>src/base/ItemRegistry.gd#L504</t>
         </is>
       </c>
       <c r="G13" s="95" t="inlineStr">
@@ -12354,7 +12491,7 @@
       </c>
       <c r="I13" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L419 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L504 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
         </is>
       </c>
       <c r="J13" s="95" t="inlineStr">
@@ -12398,7 +12535,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1" s="46">
+    <row r="14" ht="127" customHeight="1" s="46">
       <c r="A14" s="94" t="inlineStr">
         <is>
           <t>weapon_baseball_bat</t>
@@ -12426,7 +12563,7 @@
       </c>
       <c r="F14" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L442</t>
+          <t>src/base/ItemRegistry.gd#L527</t>
         </is>
       </c>
       <c r="G14" s="95" t="inlineStr">
@@ -12441,7 +12578,7 @@
       </c>
       <c r="I14" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L442 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L527 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
         </is>
       </c>
       <c r="J14" s="95" t="inlineStr">
@@ -12461,7 +12598,7 @@
       </c>
       <c r="M14" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_baseball_bat/runtime/wpn_melee_baseball_bat_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N14" s="94" t="inlineStr">
@@ -12485,7 +12622,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1" s="46">
+    <row r="15" ht="110" customHeight="1" s="46">
       <c r="A15" s="94" t="inlineStr">
         <is>
           <t>weapon_greatblade</t>
@@ -12513,7 +12650,7 @@
       </c>
       <c r="F15" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L462</t>
+          <t>src/base/ItemRegistry.gd#L547</t>
         </is>
       </c>
       <c r="G15" s="95" t="inlineStr">
@@ -12528,7 +12665,7 @@
       </c>
       <c r="I15" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L462 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L547 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J15" s="95" t="inlineStr">
@@ -12548,7 +12685,7 @@
       </c>
       <c r="M15" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_greatblade/runtime/wpn_melee_greatblade_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N15" s="94" t="inlineStr">
@@ -12572,7 +12709,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="76" customHeight="1" s="46">
+    <row r="16" ht="110" customHeight="1" s="46">
       <c r="A16" s="94" t="inlineStr">
         <is>
           <t>weapon_waraxe</t>
@@ -12600,7 +12737,7 @@
       </c>
       <c r="F16" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L484</t>
+          <t>src/base/ItemRegistry.gd#L569</t>
         </is>
       </c>
       <c r="G16" s="95" t="inlineStr">
@@ -12615,7 +12752,7 @@
       </c>
       <c r="I16" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L484 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L569 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J16" s="95" t="inlineStr">
@@ -12635,7 +12772,7 @@
       </c>
       <c r="M16" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/melee_waraxe/runtime/wpn_melee_waraxe_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N16" s="94" t="inlineStr">
@@ -12659,7 +12796,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1" s="46">
+    <row r="17" ht="127" customHeight="1" s="46">
       <c r="A17" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_standard</t>
@@ -12687,7 +12824,7 @@
       </c>
       <c r="F17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L947</t>
+          <t>src/base/ItemRegistry.gd#L1032</t>
         </is>
       </c>
       <c r="G17" s="95" t="inlineStr">
@@ -12702,7 +12839,7 @@
       </c>
       <c r="I17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L947 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1032 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J17" s="95" t="inlineStr">
@@ -12722,7 +12859,7 @@
       </c>
       <c r="M17" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_standard/runtime/wpn_bullet_module_standard_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N17" s="94" t="inlineStr">
@@ -12746,7 +12883,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="76" customHeight="1" s="46">
+    <row r="18" ht="127" customHeight="1" s="46">
       <c r="A18" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_sticky</t>
@@ -12774,7 +12911,7 @@
       </c>
       <c r="F18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L970</t>
+          <t>src/base/ItemRegistry.gd#L1055</t>
         </is>
       </c>
       <c r="G18" s="95" t="inlineStr">
@@ -12789,7 +12926,7 @@
       </c>
       <c r="I18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L970 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1055 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J18" s="95" t="inlineStr">
@@ -12809,7 +12946,7 @@
       </c>
       <c r="M18" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_sticky/runtime/wpn_bullet_module_sticky_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N18" s="94" t="inlineStr">
@@ -12833,7 +12970,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1" s="46">
+    <row r="19" ht="127" customHeight="1" s="46">
       <c r="A19" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_bounce</t>
@@ -12861,7 +12998,7 @@
       </c>
       <c r="F19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L993</t>
+          <t>src/base/ItemRegistry.gd#L1078</t>
         </is>
       </c>
       <c r="G19" s="95" t="inlineStr">
@@ -12876,7 +13013,7 @@
       </c>
       <c r="I19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L993 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1078 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J19" s="95" t="inlineStr">
@@ -12896,7 +13033,7 @@
       </c>
       <c r="M19" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_bounce/runtime/wpn_bullet_module_bounce_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N19" s="94" t="inlineStr">
@@ -12920,7 +13057,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="76" customHeight="1" s="46">
+    <row r="20" ht="127" customHeight="1" s="46">
       <c r="A20" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_piercing</t>
@@ -12948,7 +13085,7 @@
       </c>
       <c r="F20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1022</t>
+          <t>src/base/ItemRegistry.gd#L1107</t>
         </is>
       </c>
       <c r="G20" s="95" t="inlineStr">
@@ -12963,7 +13100,7 @@
       </c>
       <c r="I20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1022 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1107 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J20" s="95" t="inlineStr">
@@ -12983,7 +13120,7 @@
       </c>
       <c r="M20" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_piercing/runtime/wpn_bullet_module_piercing_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N20" s="94" t="inlineStr">
@@ -13007,7 +13144,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1" s="46">
+    <row r="21" ht="127" customHeight="1" s="46">
       <c r="A21" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_explosive</t>
@@ -13035,7 +13172,7 @@
       </c>
       <c r="F21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1043</t>
+          <t>src/base/ItemRegistry.gd#L1128</t>
         </is>
       </c>
       <c r="G21" s="95" t="inlineStr">
@@ -13050,7 +13187,7 @@
       </c>
       <c r="I21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1043 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1128 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J21" s="95" t="inlineStr">
@@ -13070,7 +13207,7 @@
       </c>
       <c r="M21" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_explosive/runtime/wpn_bullet_module_explosive_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N21" s="94" t="inlineStr">
@@ -13094,7 +13231,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1" s="46">
+    <row r="22" ht="127" customHeight="1" s="46">
       <c r="A22" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_homing</t>
@@ -13122,7 +13259,7 @@
       </c>
       <c r="F22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1064</t>
+          <t>src/base/ItemRegistry.gd#L1149</t>
         </is>
       </c>
       <c r="G22" s="95" t="inlineStr">
@@ -13137,7 +13274,7 @@
       </c>
       <c r="I22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1064 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1149 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J22" s="95" t="inlineStr">
@@ -13157,7 +13294,7 @@
       </c>
       <c r="M22" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_homing/runtime/wpn_bullet_module_homing_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N22" s="94" t="inlineStr">
@@ -13181,7 +13318,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="76" customHeight="1" s="46">
+    <row r="23" ht="127" customHeight="1" s="46">
       <c r="A23" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_blackhole</t>
@@ -13209,7 +13346,7 @@
       </c>
       <c r="F23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1085</t>
+          <t>src/base/ItemRegistry.gd#L1170</t>
         </is>
       </c>
       <c r="G23" s="95" t="inlineStr">
@@ -13224,7 +13361,7 @@
       </c>
       <c r="I23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1085 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1170 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J23" s="95" t="inlineStr">
@@ -13244,7 +13381,7 @@
       </c>
       <c r="M23" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_blackhole/runtime/wpn_bullet_module_blackhole_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N23" s="94" t="inlineStr">
@@ -13268,7 +13405,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="76" customHeight="1" s="46">
+    <row r="24" ht="127" customHeight="1" s="46">
       <c r="A24" s="94" t="inlineStr">
         <is>
           <t>mod_bullet_balloon</t>
@@ -13296,7 +13433,7 @@
       </c>
       <c r="F24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1106</t>
+          <t>src/base/ItemRegistry.gd#L1191</t>
         </is>
       </c>
       <c r="G24" s="95" t="inlineStr">
@@ -13311,7 +13448,7 @@
       </c>
       <c r="I24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1106 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L1191 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J24" s="95" t="inlineStr">
@@ -13331,7 +13468,7 @@
       </c>
       <c r="M24" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_module_balloon/runtime/wpn_bullet_module_balloon_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N24" s="94" t="inlineStr">
@@ -13355,7 +13492,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="93" customHeight="1" s="46">
+    <row r="25" ht="110" customHeight="1" s="46">
       <c r="A25" s="94" t="inlineStr">
         <is>
           <t>attach_triple_muzzle</t>
@@ -13383,7 +13520,7 @@
       </c>
       <c r="F25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1134</t>
+          <t>src/base/ItemRegistry.gd#L1219</t>
         </is>
       </c>
       <c r="G25" s="95" t="inlineStr">
@@ -13398,7 +13535,7 @@
       </c>
       <c r="I25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1134 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1219 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J25" s="95" t="inlineStr">
@@ -13418,7 +13555,7 @@
       </c>
       <c r="M25" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/triple_muzzle/runtime/wpn_triple_muzzle_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/triple_muzzle/runtime/wpn_triple_muzzle_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N25" s="94" t="inlineStr">
@@ -13442,7 +13579,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="93" customHeight="1" s="46">
+    <row r="26" ht="110" customHeight="1" s="46">
       <c r="A26" s="94" t="inlineStr">
         <is>
           <t>attach_rubber_stock</t>
@@ -13470,7 +13607,7 @@
       </c>
       <c r="F26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1159</t>
+          <t>src/base/ItemRegistry.gd#L1244</t>
         </is>
       </c>
       <c r="G26" s="95" t="inlineStr">
@@ -13485,7 +13622,7 @@
       </c>
       <c r="I26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1159 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1244 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J26" s="95" t="inlineStr">
@@ -13505,7 +13642,7 @@
       </c>
       <c r="M26" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/rubber_stock/runtime/wpn_rubber_stock_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/rubber_stock/runtime/wpn_rubber_stock_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N26" s="94" t="inlineStr">
@@ -13529,7 +13666,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="76" customHeight="1" s="46">
+    <row r="27" ht="110" customHeight="1" s="46">
       <c r="A27" s="94" t="inlineStr">
         <is>
           <t>attach_scope</t>
@@ -13557,7 +13694,7 @@
       </c>
       <c r="F27" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1190</t>
+          <t>src/base/ItemRegistry.gd#L1275</t>
         </is>
       </c>
       <c r="G27" s="95" t="inlineStr">
@@ -13572,7 +13709,7 @@
       </c>
       <c r="I27" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1190 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1275 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J27" s="95" t="inlineStr">
@@ -13592,7 +13729,7 @@
       </c>
       <c r="M27" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/scope/runtime/wpn_scope_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/scope/runtime/wpn_scope_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N27" s="94" t="inlineStr">
@@ -13616,7 +13753,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="76" customHeight="1" s="46">
+    <row r="28" ht="110" customHeight="1" s="46">
       <c r="A28" s="94" t="inlineStr">
         <is>
           <t>attach_big_mag</t>
@@ -13644,7 +13781,7 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1212</t>
+          <t>src/base/ItemRegistry.gd#L1297</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
@@ -13659,7 +13796,7 @@
       </c>
       <c r="I28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1212 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1297 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J28" s="95" t="inlineStr">
@@ -13679,7 +13816,7 @@
       </c>
       <c r="M28" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/big_mag/runtime/wpn_big_mag_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/big_mag/runtime/wpn_big_mag_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N28" s="94" t="inlineStr">
@@ -13703,7 +13840,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="76" customHeight="1" s="46">
+    <row r="29" ht="110" customHeight="1" s="46">
       <c r="A29" s="94" t="inlineStr">
         <is>
           <t>attach_fan</t>
@@ -13731,7 +13868,7 @@
       </c>
       <c r="F29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1234</t>
+          <t>src/base/ItemRegistry.gd#L1319</t>
         </is>
       </c>
       <c r="G29" s="95" t="inlineStr">
@@ -13746,7 +13883,7 @@
       </c>
       <c r="I29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1234 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1319 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J29" s="95" t="inlineStr">
@@ -13766,7 +13903,7 @@
       </c>
       <c r="M29" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/attachment_fan/runtime/wpn_attachment_fan_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N29" s="94" t="inlineStr">
@@ -13790,7 +13927,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="76" customHeight="1" s="46">
+    <row r="30" ht="110" customHeight="1" s="46">
       <c r="A30" s="94" t="inlineStr">
         <is>
           <t>attach_copy_sticker</t>
@@ -13818,7 +13955,7 @@
       </c>
       <c r="F30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1256</t>
+          <t>src/base/ItemRegistry.gd#L1341</t>
         </is>
       </c>
       <c r="G30" s="95" t="inlineStr">
@@ -13833,7 +13970,7 @@
       </c>
       <c r="I30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1256 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1341 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J30" s="95" t="inlineStr">
@@ -13853,7 +13990,7 @@
       </c>
       <c r="M30" s="94" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/copy_sticker/runtime/wpn_copy_sticker_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N30" s="94" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$41</definedName>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="T6" s="70" t="inlineStr">
         <is>
-          <t>ec5be48b60ec8724759108b9d8f0530473e324e0df25f392622474909f52f05e</t>
+          <t>2470638382999aaed09f3e141f345b3aac5173b00215a6e320d3a3e65c00271f</t>
         </is>
       </c>
       <c r="U6" s="70" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="T7" s="70" t="inlineStr">
         <is>
-          <t>67aa2883793ca21ce27b41732c48b1f4b250182c505dfab8267fcd45eb74831b</t>
+          <t>3e7dbd12824eb293a6f8e4331c3932591c172a659c47418caccf83a46e0556bb</t>
         </is>
       </c>
       <c r="U7" s="70" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="T8" s="70" t="inlineStr">
         <is>
-          <t>ce12927b14a1cb3be4f8403dfca41347f21a038faab502b3779245ef9f211cd8</t>
+          <t>d58d0c336be59b57b77c4f2cec6f529fcb62ecb454cb3f509049136988925255</t>
         </is>
       </c>
       <c r="U8" s="70" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="T9" s="70" t="inlineStr">
         <is>
-          <t>037a040062930e47d813d7b1ffd5f6cff96b826750d4a9b2e38f42a78b5f5f98</t>
+          <t>eaadde61c36370e93adbd649521bd0982e3dd95d514ec2358761853ccb9ff120</t>
         </is>
       </c>
       <c r="U9" s="70" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="T10" s="70" t="inlineStr">
         <is>
-          <t>a9c319e031c0f30b7404a435de8b5aaf2f5d5e470bd591e7dfbcf2e6ed8f2753</t>
+          <t>0420a3cfa88542bb07b4491ab80e3c51ea196bdaa52af0f3345858133765e25c</t>
         </is>
       </c>
       <c r="U10" s="70" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="T11" s="70" t="inlineStr">
         <is>
-          <t>97d05fc29d0ed170225489c8d7282c0065757d557c9bfaa31bd31761f8f67a41</t>
+          <t>12032855cedf0329be1addcf480b71b5d0ef59ea52c150171bc3d9ad12d2e638</t>
         </is>
       </c>
       <c r="U11" s="70" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="T12" s="70" t="inlineStr">
         <is>
-          <t>1c494d0811ef503c74e8dc61277b307e35db210241b46083a6da7b2121b54cee</t>
+          <t>0a2b6d1f567042f536a25f9e6ba692c294402595000bec1a41db938904a92119</t>
         </is>
       </c>
       <c r="U12" s="70" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="T27" s="73" t="inlineStr">
         <is>
-          <t>e13801540404433f6fc5f00faa0f523b804d18ec7fa30c0f6c15fab48f1ec4c9</t>
+          <t>ca471a3f8f041a7061f31ab7279ff9a976a0d9d182d0d0fd3c8e1437fe704bf4</t>
         </is>
       </c>
       <c r="U27" s="73" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="T31" s="70" t="inlineStr">
         <is>
-          <t>5af8a086bf2988755cc0e385bb5b6d527e9dbde0d11123c809741d306b38e45f</t>
+          <t>05d5f8631ae0e809f42dc4c103dae5eba8613929a0ce019b8ee17f0a508fb6e7</t>
         </is>
       </c>
       <c r="U31" s="70" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="T32" s="70" t="inlineStr">
         <is>
-          <t>7611a99cf53a4a0fd80404be89c450351994bafd161824a0b92d05a729ec05f3</t>
+          <t>1f91e9e4d2a54e82d5ebfc0b5099a7e65c91eb32e86e8c1c8f52afa2df52c264</t>
         </is>
       </c>
       <c r="U32" s="70" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="T33" s="70" t="inlineStr">
         <is>
-          <t>04a9659dcef16faed7af37c04dbe4f2bd7322b87992d9f269f503d87ea2f9cca</t>
+          <t>3e833ff63ebff0575600f0da74b12bdea155598fa239834294968f411495c426</t>
         </is>
       </c>
       <c r="U33" s="70" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="T34" s="70" t="inlineStr">
         <is>
-          <t>f73360d92e0188808efdd39aa652067dec9a7fd5fd1fef243879b6e28b61c465</t>
+          <t>d1fd5653d2d9e5b834f6d4e7327159e49c2810fff46a38a93da80a7d72a6848c</t>
         </is>
       </c>
       <c r="U34" s="70" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="T35" s="70" t="inlineStr">
         <is>
-          <t>ad9e3e21a430c104cc44345297a05b7a4ea61a02bb1d605ef79c4b8d1c49de35</t>
+          <t>a30e709f22c4e33f99398b002307af2d27c2f4dd3aca10bf192921c063223aa4</t>
         </is>
       </c>
       <c r="U35" s="70" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="T36" s="70" t="inlineStr">
         <is>
-          <t>01c3204ae0d66aa0e0bf28bf2643c327a7550ff1c024f36114f45fb9010de7a8</t>
+          <t>dbcc9441cc5f5c2df19d1b745850072880ca1abf39030ed90353999828eec57a</t>
         </is>
       </c>
       <c r="U36" s="70" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="T37" s="70" t="inlineStr">
         <is>
-          <t>bc0fa22a6e7c32ed741079af21a73152e3404b7f4fd236cdb38e2a3ab0e477fa</t>
+          <t>b8c6a97267f825937f58851aad49588de64c1d3e713526a26f275306413b702f</t>
         </is>
       </c>
       <c r="U37" s="70" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="T38" s="70" t="inlineStr">
         <is>
-          <t>01d4ecf005d76562942e584db25fa586a9bfb9fa2533ea7290fbfdd65bc1f749</t>
+          <t>c0e1abe37949f4aee0619e04f40104b4bcf0c59f4269ddc64f4f10df4733416b</t>
         </is>
       </c>
       <c r="U38" s="70" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="T39" s="70" t="inlineStr">
         <is>
-          <t>07ec25c941bb19732944bafdaae85db88ea93b4a870606b3202669bee8313932</t>
+          <t>e4afd543d2e1be93ac923edc02ba570611ca0ee73fe3a0764ff0f7677ead1968</t>
         </is>
       </c>
       <c r="U39" s="70" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="T40" s="70" t="inlineStr">
         <is>
-          <t>6c277b10c52f4dde4790e91c760a6f981fa38af9b19bf67fdf584785659a618e</t>
+          <t>d4acc27b57bae6f0d1688365d8bbba123fa6e174b9f2acce02173853513659f7</t>
         </is>
       </c>
       <c r="U40" s="70" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="T41" s="70" t="inlineStr">
         <is>
-          <t>5b740e26cc2b5e2b4cbdd1334b371224cba40165048a6747fad4e5962e53c8c7</t>
+          <t>3ef7b483eb98314077ee9a014c6b6de00dddf66509f8d35ab78aec539958fe18</t>
         </is>
       </c>
       <c r="U41" s="70" t="inlineStr">
@@ -6971,7 +6971,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="46">
       <c r="A4" s="77" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$41</definedName>
@@ -5082,10 +5082,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V28" s="74" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="V28" s="74" t="n">
+        <v>46311</v>
       </c>
       <c r="W28" s="49" t="inlineStr">
         <is>
@@ -5101,7 +5099,7 @@
         <is>
           <t>高精度源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_greatblade/source/wpn_melee_greatblade_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
 【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
-【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。；2026-10-16角色动作v041：点按左右交替三连；按住0.35秒旋风，0.55秒一圈/0.25秒伤害；松开结束；横扫/旋风特效；模型版本不变；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
         </is>
       </c>
     </row>
@@ -5205,10 +5203,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V29" s="74" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="V29" s="74" t="n">
+        <v>46312</v>
       </c>
       <c r="W29" s="49" t="inlineStr">
         <is>
@@ -5224,7 +5220,7 @@
         <is>
           <t>高精度源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_waraxe/source/wpn_melee_waraxe_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
 【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
-【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。；2026-10-16角色动作v041：慢速头顶下劈；按住1秒蓄满，松开强击退；普通2帧/蓄力4帧停顿；蓄力环/竖劈/冲击；模型版本不变；docs/v0.1/development/2026-10-16_melee_styles_v041.md；2026-10-17角色动作v042修正握持绕柄-90°，银刃沿下劈领先；武器模型未改；docs/v0.1/development/2026-10-17_axe_edge_v042.md</t>
         </is>
       </c>
     </row>
@@ -5328,10 +5324,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V30" s="97" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="V30" s="97" t="n">
+        <v>46311</v>
       </c>
       <c r="W30" s="49" t="inlineStr">
         <is>
@@ -5347,7 +5341,7 @@
         <is>
           <t>高精度源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_source_v001.blend；地面源=art_source/items_weapons/weapons/melee_baseball_bat/source/wpn_melee_baseball_bat_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；近战保持握点、伤害归原玩法
 【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
-【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。；2026-10-16角色动作v041：普通三连挥棒；1帧停顿；现有风痕；模型版本不变；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="45" min="1" max="1"/>
@@ -11122,6 +11116,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -11561,6 +11556,80 @@
         </is>
       </c>
       <c r="G16" s="45" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1" s="46">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>v0.1.109</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>三类近战玩法与角色动作差异</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>近战差异 v041</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="inlineStr">
+        <is>
+          <t>模型复用；角色源、命中反馈及VFX按各武器独立接线。</t>
+        </is>
+      </c>
+      <c r="F17" s="56" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="G17" s="56" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" s="46">
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>v0.1.110</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>战斧持握刃向校正</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t>角色握持角度</t>
+        </is>
+      </c>
+      <c r="E18" s="56" t="inlineStr">
+        <is>
+          <t>角色源14动作修正，武器源模型保持。</t>
+        </is>
+      </c>
+      <c r="F18" s="56" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-17_axe_edge_v042.md</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-武器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="背包物品调用索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$41</definedName>
@@ -11116,7 +11116,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="46">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -11680,6 +11679,9 @@
           <t>武器账本 · 背包物品调用索引</t>
         </is>
       </c>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="94" t="n"/>
+      <c r="D1" s="94" t="n"/>
       <c r="E1" s="94" t="n"/>
       <c r="F1" s="94" t="n"/>
       <c r="G1" s="94" t="n"/>
@@ -11700,6 +11702,9 @@
           <t>成品武器、子弹模块、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
         </is>
       </c>
+      <c r="B2" s="94" t="n"/>
+      <c r="C2" s="94" t="n"/>
+      <c r="D2" s="94" t="n"/>
       <c r="E2" s="94" t="n"/>
       <c r="F2" s="94" t="n"/>
       <c r="G2" s="94" t="n"/>
@@ -11858,12 +11863,12 @@
       </c>
       <c r="H5" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行2 / melee_chaser</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I5" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L290 / loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L290 / scavenge_floor_1, scavenge_floor_2, strong_weapon_floor_1, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J5" s="95" t="inlineStr">
@@ -11903,11 +11908,11 @@
       </c>
       <c r="Q5" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="59" customHeight="1" s="46">
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="93" customHeight="1" s="46">
       <c r="A6" s="94" t="inlineStr">
         <is>
           <t>weapon_shotgun</t>
@@ -11935,7 +11940,7 @@
       </c>
       <c r="F6" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L309</t>
+          <t>src/base/ItemRegistry.gd#L311</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -11950,7 +11955,7 @@
       </c>
       <c r="I6" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L309 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L311 / spawn_starter, scavenge_floor_1, scavenge_floor_2, strong_weapon_floor_1, strong_weapon_floor_2, boss_weapon_floor_1, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J6" s="95" t="inlineStr">
@@ -12022,7 +12027,7 @@
       </c>
       <c r="F7" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L329</t>
+          <t>src/base/ItemRegistry.gd#L333</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
@@ -12037,7 +12042,7 @@
       </c>
       <c r="I7" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L329 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L333 / boss_weapon_floor_1, boss_weapon_floor_2, strong_weapon_floor_1, strong_weapon_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J7" s="95" t="inlineStr">
@@ -12081,7 +12086,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="110" customHeight="1" s="46">
+    <row r="8" ht="127" customHeight="1" s="46">
       <c r="A8" s="94" t="inlineStr">
         <is>
           <t>weapon_machinegun</t>
@@ -12109,7 +12114,7 @@
       </c>
       <c r="F8" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L358</t>
+          <t>src/base/ItemRegistry.gd#L360</t>
         </is>
       </c>
       <c r="G8" s="95" t="inlineStr">
@@ -12124,7 +12129,7 @@
       </c>
       <c r="I8" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L358 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L360 / boss_weapon_floor_1, boss_weapon_floor_2, strong_weapon_floor_1, strong_weapon_floor_2, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J8" s="95" t="inlineStr">
@@ -12168,7 +12173,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="110" customHeight="1" s="46">
+    <row r="9" ht="127" customHeight="1" s="46">
       <c r="A9" s="94" t="inlineStr">
         <is>
           <t>weapon_sprinkler</t>
@@ -12196,7 +12201,7 @@
       </c>
       <c r="F9" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L387</t>
+          <t>src/base/ItemRegistry.gd#L389</t>
         </is>
       </c>
       <c r="G9" s="94" t="inlineStr">
@@ -12211,7 +12216,7 @@
       </c>
       <c r="I9" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L387 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L389 / strong_weapon_floor_1, strong_weapon_floor_2, boss_weapon_floor_2, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J9" s="95" t="inlineStr">
@@ -12255,7 +12260,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1" s="46">
+    <row r="10" ht="127" customHeight="1" s="46">
       <c r="A10" s="94" t="inlineStr">
         <is>
           <t>weapon_starter_rifle</t>
@@ -12283,7 +12288,7 @@
       </c>
       <c r="F10" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L418</t>
+          <t>src/base/ItemRegistry.gd#L419</t>
         </is>
       </c>
       <c r="G10" s="95" t="inlineStr">
@@ -12298,7 +12303,7 @@
       </c>
       <c r="I10" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L418 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L419 / strong_weapon_floor_1, strong_weapon_floor_2, boss_weapon_floor_2, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J10" s="95" t="inlineStr">
@@ -12385,7 +12390,7 @@
       </c>
       <c r="I11" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L450 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L450 / boss_weapon_floor_1, boss_weapon_floor_2, strong_weapon_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J11" s="95" t="inlineStr">
@@ -12457,7 +12462,7 @@
       </c>
       <c r="F12" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L477</t>
+          <t>src/base/ItemRegistry.gd#L475</t>
         </is>
       </c>
       <c r="G12" s="95" t="inlineStr">
@@ -12467,12 +12472,12 @@
       </c>
       <c r="H12" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行13 / exploder</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I12" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L477 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L475 / boss_weapon_floor_1, boss_weapon_floor_2, strong_weapon_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, elite_floor_2</t>
         </is>
       </c>
       <c r="J12" s="95" t="inlineStr">
@@ -12512,7 +12517,7 @@
       </c>
       <c r="Q12" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12549,7 @@
       </c>
       <c r="F13" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L504</t>
+          <t>src/base/ItemRegistry.gd#L500</t>
         </is>
       </c>
       <c r="G13" s="95" t="inlineStr">
@@ -12559,7 +12564,7 @@
       </c>
       <c r="I13" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L504 / loot_floor_5, loot_abyss, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L500 / boss_weapon_floor_2, strong_weapon_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5, elite_floor_2</t>
         </is>
       </c>
       <c r="J13" s="95" t="inlineStr">
@@ -12631,7 +12636,7 @@
       </c>
       <c r="F14" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L527</t>
+          <t>src/base/ItemRegistry.gd#L522</t>
         </is>
       </c>
       <c r="G14" s="95" t="inlineStr">
@@ -12641,12 +12646,12 @@
       </c>
       <c r="H14" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行3 / melee_chaser</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行2 / melee_chaser</t>
         </is>
       </c>
       <c r="I14" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L527 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L522 / spawn_starter, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1</t>
         </is>
       </c>
       <c r="J14" s="95" t="inlineStr">
@@ -12718,7 +12723,7 @@
       </c>
       <c r="F15" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L547</t>
+          <t>src/base/ItemRegistry.gd#L542</t>
         </is>
       </c>
       <c r="G15" s="95" t="inlineStr">
@@ -12733,7 +12738,7 @@
       </c>
       <c r="I15" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L547 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L542 / spawn_starter, loot_floor_1_2, loot_floor_3_4, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J15" s="95" t="inlineStr">
@@ -12805,7 +12810,7 @@
       </c>
       <c r="F16" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L569</t>
+          <t>src/base/ItemRegistry.gd#L564</t>
         </is>
       </c>
       <c r="G16" s="95" t="inlineStr">
@@ -12820,7 +12825,7 @@
       </c>
       <c r="I16" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L569 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L564 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, combat_floor_3, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J16" s="95" t="inlineStr">
@@ -12892,7 +12897,7 @@
       </c>
       <c r="F17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1032</t>
+          <t>src/base/ItemRegistry.gd#L1027</t>
         </is>
       </c>
       <c r="G17" s="95" t="inlineStr">
@@ -12902,12 +12907,12 @@
       </c>
       <c r="H17" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行3 / melee_chaser</t>
         </is>
       </c>
       <c r="I17" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1032 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1027 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J17" s="95" t="inlineStr">
@@ -12979,7 +12984,7 @@
       </c>
       <c r="F18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1055</t>
+          <t>src/base/ItemRegistry.gd#L1050</t>
         </is>
       </c>
       <c r="G18" s="95" t="inlineStr">
@@ -12994,7 +12999,7 @@
       </c>
       <c r="I18" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1055 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1050 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J18" s="95" t="inlineStr">
@@ -13066,7 +13071,7 @@
       </c>
       <c r="F19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1078</t>
+          <t>src/base/ItemRegistry.gd#L1073</t>
         </is>
       </c>
       <c r="G19" s="95" t="inlineStr">
@@ -13076,12 +13081,12 @@
       </c>
       <c r="H19" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行6 / ranged_caster</t>
         </is>
       </c>
       <c r="I19" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1078 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1073 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J19" s="95" t="inlineStr">
@@ -13153,7 +13158,7 @@
       </c>
       <c r="F20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1107</t>
+          <t>src/base/ItemRegistry.gd#L1102</t>
         </is>
       </c>
       <c r="G20" s="95" t="inlineStr">
@@ -13163,12 +13168,12 @@
       </c>
       <c r="H20" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行6 / ranged_caster</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / ranged_caster</t>
         </is>
       </c>
       <c r="I20" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1107 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1102 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J20" s="95" t="inlineStr">
@@ -13240,7 +13245,7 @@
       </c>
       <c r="F21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1128</t>
+          <t>src/base/ItemRegistry.gd#L1123</t>
         </is>
       </c>
       <c r="G21" s="95" t="inlineStr">
@@ -13250,12 +13255,12 @@
       </c>
       <c r="H21" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / exploder</t>
         </is>
       </c>
       <c r="I21" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1128 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1123 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3</t>
         </is>
       </c>
       <c r="J21" s="95" t="inlineStr">
@@ -13327,7 +13332,7 @@
       </c>
       <c r="F22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1149</t>
+          <t>src/base/ItemRegistry.gd#L1144</t>
         </is>
       </c>
       <c r="G22" s="95" t="inlineStr">
@@ -13342,7 +13347,7 @@
       </c>
       <c r="I22" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1149 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1144 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J22" s="95" t="inlineStr">
@@ -13414,7 +13419,7 @@
       </c>
       <c r="F23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1170</t>
+          <t>src/base/ItemRegistry.gd#L1165</t>
         </is>
       </c>
       <c r="G23" s="95" t="inlineStr">
@@ -13429,7 +13434,7 @@
       </c>
       <c r="I23" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1170 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1165 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J23" s="95" t="inlineStr">
@@ -13501,7 +13506,7 @@
       </c>
       <c r="F24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1191</t>
+          <t>src/base/ItemRegistry.gd#L1186</t>
         </is>
       </c>
       <c r="G24" s="95" t="inlineStr">
@@ -13516,7 +13521,7 @@
       </c>
       <c r="I24" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1191 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L1186 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J24" s="95" t="inlineStr">
@@ -13588,7 +13593,7 @@
       </c>
       <c r="F25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1219</t>
+          <t>src/base/ItemRegistry.gd#L1214</t>
         </is>
       </c>
       <c r="G25" s="95" t="inlineStr">
@@ -13603,7 +13608,7 @@
       </c>
       <c r="I25" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1219 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1214 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J25" s="95" t="inlineStr">
@@ -13675,7 +13680,7 @@
       </c>
       <c r="F26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1244</t>
+          <t>src/base/ItemRegistry.gd#L1239</t>
         </is>
       </c>
       <c r="G26" s="95" t="inlineStr">
@@ -13690,7 +13695,7 @@
       </c>
       <c r="I26" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1244 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1239 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, spawn_starter, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J26" s="95" t="inlineStr">
@@ -13762,7 +13767,7 @@
       </c>
       <c r="F27" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1275</t>
+          <t>src/base/ItemRegistry.gd#L1270</t>
         </is>
       </c>
       <c r="G27" s="95" t="inlineStr">
@@ -13772,12 +13777,12 @@
       </c>
       <c r="H27" s="94" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行7 / ranged_caster</t>
         </is>
       </c>
       <c r="I27" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1275 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L1270 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J27" s="95" t="inlineStr">
@@ -13849,7 +13854,7 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1297</t>
+          <t>src/base/ItemRegistry.gd#L1292</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
@@ -13864,7 +13869,7 @@
       </c>
       <c r="I28" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1297 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1292 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J28" s="95" t="inlineStr">
@@ -13936,7 +13941,7 @@
       </c>
       <c r="F29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1319</t>
+          <t>src/base/ItemRegistry.gd#L1314</t>
         </is>
       </c>
       <c r="G29" s="95" t="inlineStr">
@@ -13951,7 +13956,7 @@
       </c>
       <c r="I29" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1319 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1314 / loot_floor_5, loot_abyss, boss_floor_1, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J29" s="95" t="inlineStr">
@@ -14023,7 +14028,7 @@
       </c>
       <c r="F30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1341</t>
+          <t>src/base/ItemRegistry.gd#L1336</t>
         </is>
       </c>
       <c r="G30" s="95" t="inlineStr">
@@ -14038,7 +14043,7 @@
       </c>
       <c r="I30" s="95" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1341 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L1336 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_4, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J30" s="95" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx
@@ -11679,9 +11679,6 @@
           <t>武器账本 · 背包物品调用索引</t>
         </is>
       </c>
-      <c r="B1" s="94" t="n"/>
-      <c r="C1" s="94" t="n"/>
-      <c r="D1" s="94" t="n"/>
       <c r="E1" s="94" t="n"/>
       <c r="F1" s="94" t="n"/>
       <c r="G1" s="94" t="n"/>
@@ -11702,9 +11699,6 @@
           <t>成品武器、子弹模块、枪械配件唯一归属本账本；内容ID导航页，不新增资产主表行。</t>
         </is>
       </c>
-      <c r="B2" s="94" t="n"/>
-      <c r="C2" s="94" t="n"/>
-      <c r="D2" s="94" t="n"/>
       <c r="E2" s="94" t="n"/>
       <c r="F2" s="94" t="n"/>
       <c r="G2" s="94" t="n"/>
@@ -12922,7 +12916,7 @@
       </c>
       <c r="K17" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L17" s="95" t="inlineStr">
@@ -12952,7 +12946,7 @@
       </c>
       <c r="Q17" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13003,7 @@
       </c>
       <c r="K18" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L18" s="95" t="inlineStr">
@@ -13039,7 +13033,7 @@
       </c>
       <c r="Q18" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13090,7 @@
       </c>
       <c r="K19" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L19" s="95" t="inlineStr">
@@ -13126,7 +13120,7 @@
       </c>
       <c r="Q19" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13177,7 @@
       </c>
       <c r="K20" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L20" s="95" t="inlineStr">
@@ -13213,7 +13207,7 @@
       </c>
       <c r="Q20" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13264,7 @@
       </c>
       <c r="K21" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L21" s="95" t="inlineStr">
@@ -13300,7 +13294,7 @@
       </c>
       <c r="Q21" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13351,7 @@
       </c>
       <c r="K22" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L22" s="95" t="inlineStr">
@@ -13387,7 +13381,7 @@
       </c>
       <c r="Q22" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13438,7 @@
       </c>
       <c r="K23" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L23" s="95" t="inlineStr">
@@ -13474,7 +13468,7 @@
       </c>
       <c r="Q23" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13525,7 @@
       </c>
       <c r="K24" s="95" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_install_weapon_module_from_item</t>
+          <t>src/world3d/Dungeon3D.gd#_reject_manual_bullet_module_swap</t>
         </is>
       </c>
       <c r="L24" s="95" t="inlineStr">
@@ -13561,7 +13555,7 @@
       </c>
       <c r="Q24" s="94" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；2026-10-19 起手动更换已关闭，需枪械工坊特殊流程（待实现）</t>
         </is>
       </c>
     </row>
